--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -2674,10 +2674,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119832379</v>
+        <v>119831192</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>78608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,25 +2686,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457971</v>
+        <v>458042</v>
       </c>
       <c r="R21" t="n">
-        <v>6901530</v>
+        <v>6901347</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119834170</v>
+        <v>119832322</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458123</v>
+        <v>457900</v>
       </c>
       <c r="R22" t="n">
-        <v>6901854</v>
+        <v>6901490</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2852,6 +2852,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2878,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119831192</v>
+        <v>119834170</v>
       </c>
       <c r="B23" t="n">
-        <v>78608</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,25 +2895,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458042</v>
+        <v>458123</v>
       </c>
       <c r="R23" t="n">
-        <v>6901347</v>
+        <v>6901854</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2980,7 +2985,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119832322</v>
+        <v>119832379</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3020,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457900</v>
+        <v>457971</v>
       </c>
       <c r="R24" t="n">
-        <v>6901490</v>
+        <v>6901530</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3056,11 +3061,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3495,10 +3495,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834412</v>
+        <v>119831437</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3507,25 +3507,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458147</v>
+        <v>458021</v>
       </c>
       <c r="R29" t="n">
-        <v>6901790</v>
+        <v>6901469</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3571,11 +3571,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3602,7 +3597,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119833909</v>
+        <v>119831568</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458175</v>
+        <v>457981</v>
       </c>
       <c r="R30" t="n">
-        <v>6901627</v>
+        <v>6901471</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3704,7 +3699,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119831437</v>
+        <v>119832390</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3744,10 +3739,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458021</v>
+        <v>457939</v>
       </c>
       <c r="R31" t="n">
-        <v>6901469</v>
+        <v>6901499</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3806,10 +3801,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119831568</v>
+        <v>119834412</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3818,25 +3813,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3846,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457981</v>
+        <v>458147</v>
       </c>
       <c r="R32" t="n">
-        <v>6901471</v>
+        <v>6901790</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3882,6 +3877,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,7 +3908,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119832390</v>
+        <v>119833909</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457939</v>
+        <v>458175</v>
       </c>
       <c r="R33" t="n">
-        <v>6901499</v>
+        <v>6901627</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -5647,7 +5647,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119831182</v>
+        <v>119832531</v>
       </c>
       <c r="B50" t="n">
         <v>97907</v>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>458050</v>
+        <v>457981</v>
       </c>
       <c r="R50" t="n">
-        <v>6901340</v>
+        <v>6901523</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119830906</v>
+        <v>119831182</v>
       </c>
       <c r="B51" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5761,38 +5761,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458090</v>
+        <v>458050</v>
       </c>
       <c r="R51" t="n">
-        <v>6901440</v>
+        <v>6901340</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5851,10 +5851,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119834180</v>
+        <v>119830906</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5867,34 +5867,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458123</v>
+        <v>458090</v>
       </c>
       <c r="R52" t="n">
-        <v>6901854</v>
+        <v>6901440</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119832531</v>
+        <v>119834180</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5965,25 +5965,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457981</v>
+        <v>458123</v>
       </c>
       <c r="R53" t="n">
-        <v>6901523</v>
+        <v>6901854</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6157,7 +6157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119834306</v>
+        <v>119831005</v>
       </c>
       <c r="B55" t="n">
         <v>97907</v>
@@ -6193,17 +6193,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458116</v>
+        <v>458099</v>
       </c>
       <c r="R55" t="n">
-        <v>6901806</v>
+        <v>6901390</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119831005</v>
+        <v>119834306</v>
       </c>
       <c r="B56" t="n">
         <v>97907</v>
@@ -6295,17 +6295,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458099</v>
+        <v>458116</v>
       </c>
       <c r="R56" t="n">
-        <v>6901390</v>
+        <v>6901806</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119831166</v>
+        <v>119833909</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458073</v>
+        <v>458175</v>
       </c>
       <c r="R8" t="n">
-        <v>6901343</v>
+        <v>6901627</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119830850</v>
+        <v>119831719</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1486,14 +1486,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458090</v>
+        <v>457858</v>
       </c>
       <c r="R9" t="n">
-        <v>6901440</v>
+        <v>6901422</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119831586</v>
+        <v>119831005</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1588,14 +1588,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457968</v>
+        <v>458099</v>
       </c>
       <c r="R10" t="n">
-        <v>6901445</v>
+        <v>6901390</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119832523</v>
+        <v>119831262</v>
       </c>
       <c r="B11" t="n">
         <v>79607</v>
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457981</v>
+        <v>458019</v>
       </c>
       <c r="R11" t="n">
-        <v>6901523</v>
+        <v>6901394</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,6 +1730,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119832719</v>
+        <v>119831044</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,25 +1773,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457992</v>
+        <v>458095</v>
       </c>
       <c r="R12" t="n">
-        <v>6901502</v>
+        <v>6901375</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1858,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119832972</v>
+        <v>119831593</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,25 +1875,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458029</v>
+        <v>457980</v>
       </c>
       <c r="R13" t="n">
-        <v>6901493</v>
+        <v>6901438</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1960,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119831719</v>
+        <v>119831168</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,25 +1977,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457858</v>
+        <v>458064</v>
       </c>
       <c r="R14" t="n">
-        <v>6901422</v>
+        <v>6901364</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2062,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830810</v>
+        <v>119831034</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,38 +2079,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458102</v>
+        <v>458101</v>
       </c>
       <c r="R15" t="n">
-        <v>6901455</v>
+        <v>6901379</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2164,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119831791</v>
+        <v>119830773</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,34 +2185,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457796</v>
+        <v>458081</v>
       </c>
       <c r="R16" t="n">
-        <v>6901401</v>
+        <v>6901475</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2266,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119833379</v>
+        <v>119831955</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458065</v>
+        <v>457798</v>
       </c>
       <c r="R17" t="n">
-        <v>6901429</v>
+        <v>6901409</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2368,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119832209</v>
+        <v>119834170</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,25 +2385,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2408,13 +2413,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457874</v>
+        <v>458123</v>
       </c>
       <c r="R18" t="n">
-        <v>6901494</v>
+        <v>6901854</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2470,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119831301</v>
+        <v>119830797</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,38 +2487,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458031</v>
+        <v>458092</v>
       </c>
       <c r="R19" t="n">
-        <v>6901401</v>
+        <v>6901472</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2572,7 +2577,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119832417</v>
+        <v>119831586</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457946</v>
+        <v>457968</v>
       </c>
       <c r="R20" t="n">
-        <v>6901508</v>
+        <v>6901445</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2674,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119831192</v>
+        <v>119831568</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,25 +2691,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2714,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458042</v>
+        <v>457981</v>
       </c>
       <c r="R21" t="n">
-        <v>6901347</v>
+        <v>6901471</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2776,7 +2781,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119832322</v>
+        <v>119830810</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2812,14 +2817,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457900</v>
+        <v>458102</v>
       </c>
       <c r="R22" t="n">
-        <v>6901490</v>
+        <v>6901455</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2852,11 +2857,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2883,7 +2883,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119834170</v>
+        <v>119831437</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458123</v>
+        <v>458021</v>
       </c>
       <c r="R23" t="n">
-        <v>6901854</v>
+        <v>6901469</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119832379</v>
+        <v>119834306</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457971</v>
+        <v>458116</v>
       </c>
       <c r="R24" t="n">
-        <v>6901530</v>
+        <v>6901806</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119831249</v>
+        <v>119831657</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458045</v>
+        <v>457940</v>
       </c>
       <c r="R25" t="n">
-        <v>6901417</v>
+        <v>6901428</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119833969</v>
+        <v>119831192</v>
       </c>
       <c r="B26" t="n">
-        <v>79115</v>
+        <v>78608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458185</v>
+        <v>458042</v>
       </c>
       <c r="R26" t="n">
-        <v>6901645</v>
+        <v>6901347</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119832342</v>
+        <v>119832523</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,13 +3331,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457951</v>
+        <v>457981</v>
       </c>
       <c r="R27" t="n">
-        <v>6901545</v>
+        <v>6901523</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119830863</v>
+        <v>119831791</v>
       </c>
       <c r="B28" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3409,34 +3409,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458090</v>
+        <v>457796</v>
       </c>
       <c r="R28" t="n">
-        <v>6901440</v>
+        <v>6901401</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3495,7 +3495,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119831437</v>
+        <v>119832972</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458021</v>
+        <v>458029</v>
       </c>
       <c r="R29" t="n">
-        <v>6901469</v>
+        <v>6901493</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119831568</v>
+        <v>119832379</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457981</v>
+        <v>457971</v>
       </c>
       <c r="R30" t="n">
-        <v>6901471</v>
+        <v>6901530</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119832390</v>
+        <v>119830850</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3735,14 +3735,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457939</v>
+        <v>458090</v>
       </c>
       <c r="R31" t="n">
-        <v>6901499</v>
+        <v>6901440</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119834412</v>
+        <v>119830863</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3817,34 +3817,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458147</v>
+        <v>458090</v>
       </c>
       <c r="R32" t="n">
-        <v>6901790</v>
+        <v>6901440</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3877,11 +3877,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3908,10 +3903,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119833909</v>
+        <v>119832209</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3920,25 +3915,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3948,13 +3943,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458175</v>
+        <v>457874</v>
       </c>
       <c r="R33" t="n">
-        <v>6901627</v>
+        <v>6901494</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4010,10 +4005,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119831593</v>
+        <v>119830906</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4026,34 +4021,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>457980</v>
+        <v>458090</v>
       </c>
       <c r="R34" t="n">
-        <v>6901438</v>
+        <v>6901440</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4112,10 +4107,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119831262</v>
+        <v>119831281</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4124,25 +4119,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4152,13 +4147,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458019</v>
+        <v>458034</v>
       </c>
       <c r="R35" t="n">
-        <v>6901394</v>
+        <v>6901429</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4188,11 +4183,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4219,7 +4209,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119831657</v>
+        <v>119831267</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4259,10 +4249,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457940</v>
+        <v>458019</v>
       </c>
       <c r="R36" t="n">
-        <v>6901428</v>
+        <v>6901394</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4321,7 +4311,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119834066</v>
+        <v>119832342</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4361,10 +4351,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458212</v>
+        <v>457951</v>
       </c>
       <c r="R37" t="n">
-        <v>6901767</v>
+        <v>6901545</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4423,10 +4413,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119831651</v>
+        <v>119832197</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4435,25 +4425,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4463,10 +4453,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457975</v>
+        <v>457849</v>
       </c>
       <c r="R38" t="n">
-        <v>6901409</v>
+        <v>6901500</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4525,10 +4515,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119832130</v>
+        <v>119833379</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4537,25 +4527,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4565,10 +4555,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457815</v>
+        <v>458065</v>
       </c>
       <c r="R39" t="n">
-        <v>6901466</v>
+        <v>6901429</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4627,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119831168</v>
+        <v>119832719</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4639,25 +4629,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4667,10 +4657,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458064</v>
+        <v>457992</v>
       </c>
       <c r="R40" t="n">
-        <v>6901364</v>
+        <v>6901502</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4729,7 +4719,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119831267</v>
+        <v>119833397</v>
       </c>
       <c r="B41" t="n">
         <v>97907</v>
@@ -4769,10 +4759,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458019</v>
+        <v>458066</v>
       </c>
       <c r="R41" t="n">
-        <v>6901394</v>
+        <v>6901440</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4831,10 +4821,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119830773</v>
+        <v>119832390</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4843,38 +4833,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458081</v>
+        <v>457939</v>
       </c>
       <c r="R42" t="n">
-        <v>6901475</v>
+        <v>6901499</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4933,10 +4923,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119834112</v>
+        <v>119832322</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4945,25 +4935,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4973,10 +4963,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458204</v>
+        <v>457900</v>
       </c>
       <c r="R43" t="n">
-        <v>6901795</v>
+        <v>6901490</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5009,6 +4999,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5035,10 +5030,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119833397</v>
+        <v>119832325</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5047,25 +5042,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5075,10 +5070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458066</v>
+        <v>457950</v>
       </c>
       <c r="R44" t="n">
-        <v>6901440</v>
+        <v>6901553</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5137,7 +5132,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119831564</v>
+        <v>119832531</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5177,10 +5172,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457994</v>
+        <v>457981</v>
       </c>
       <c r="R45" t="n">
-        <v>6901464</v>
+        <v>6901523</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5239,10 +5234,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119831819</v>
+        <v>119834412</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5251,25 +5246,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5279,10 +5274,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457796</v>
+        <v>458147</v>
       </c>
       <c r="R46" t="n">
-        <v>6901388</v>
+        <v>6901790</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5315,6 +5310,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5341,7 +5341,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119831281</v>
+        <v>119834066</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -5381,13 +5381,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458034</v>
+        <v>458212</v>
       </c>
       <c r="R47" t="n">
-        <v>6901429</v>
+        <v>6901767</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119833531</v>
+        <v>119831182</v>
       </c>
       <c r="B48" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5455,25 +5455,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458113</v>
+        <v>458050</v>
       </c>
       <c r="R48" t="n">
-        <v>6901438</v>
+        <v>6901340</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119833610</v>
+        <v>119831301</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5557,25 +5557,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>458139</v>
+        <v>458031</v>
       </c>
       <c r="R49" t="n">
-        <v>6901557</v>
+        <v>6901401</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5647,7 +5647,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119832531</v>
+        <v>119831651</v>
       </c>
       <c r="B50" t="n">
         <v>97907</v>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457981</v>
+        <v>457975</v>
       </c>
       <c r="R50" t="n">
-        <v>6901523</v>
+        <v>6901409</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119831182</v>
+        <v>119831564</v>
       </c>
       <c r="B51" t="n">
         <v>97907</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458050</v>
+        <v>457994</v>
       </c>
       <c r="R51" t="n">
-        <v>6901340</v>
+        <v>6901464</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5851,10 +5851,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119830906</v>
+        <v>119832417</v>
       </c>
       <c r="B52" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5863,38 +5863,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458090</v>
+        <v>457946</v>
       </c>
       <c r="R52" t="n">
-        <v>6901440</v>
+        <v>6901508</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119834180</v>
+        <v>119831249</v>
       </c>
       <c r="B53" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5965,25 +5965,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>458123</v>
+        <v>458045</v>
       </c>
       <c r="R53" t="n">
-        <v>6901854</v>
+        <v>6901417</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119834299</v>
+        <v>119834180</v>
       </c>
       <c r="B54" t="n">
         <v>79607</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>458164</v>
+        <v>458123</v>
       </c>
       <c r="R54" t="n">
-        <v>6901837</v>
+        <v>6901854</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6157,10 +6157,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119831005</v>
+        <v>119834299</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6169,38 +6169,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458099</v>
+        <v>458164</v>
       </c>
       <c r="R55" t="n">
-        <v>6901390</v>
+        <v>6901837</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119834306</v>
+        <v>119831671</v>
       </c>
       <c r="B56" t="n">
         <v>97907</v>
@@ -6299,13 +6299,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458116</v>
+        <v>457902</v>
       </c>
       <c r="R56" t="n">
-        <v>6901806</v>
+        <v>6901423</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119830797</v>
+        <v>119832130</v>
       </c>
       <c r="B57" t="n">
         <v>97907</v>
@@ -6397,14 +6397,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458092</v>
+        <v>457815</v>
       </c>
       <c r="R57" t="n">
-        <v>6901472</v>
+        <v>6901466</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119832197</v>
+        <v>119831819</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,25 +6475,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457849</v>
+        <v>457796</v>
       </c>
       <c r="R58" t="n">
-        <v>6901500</v>
+        <v>6901388</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119831034</v>
+        <v>119833969</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
+        <v>79115</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6581,34 +6581,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458101</v>
+        <v>458185</v>
       </c>
       <c r="R59" t="n">
-        <v>6901379</v>
+        <v>6901645</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119831671</v>
+        <v>119833610</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6679,25 +6679,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457902</v>
+        <v>458139</v>
       </c>
       <c r="R60" t="n">
-        <v>6901423</v>
+        <v>6901557</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119831044</v>
+        <v>119831166</v>
       </c>
       <c r="B62" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>458095</v>
+        <v>458073</v>
       </c>
       <c r="R62" t="n">
-        <v>6901375</v>
+        <v>6901343</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119832325</v>
+        <v>119834112</v>
       </c>
       <c r="B63" t="n">
         <v>79607</v>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457950</v>
+        <v>458204</v>
       </c>
       <c r="R63" t="n">
-        <v>6901553</v>
+        <v>6901795</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7075,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119831955</v>
+        <v>119833531</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,25 +7087,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457798</v>
+        <v>458113</v>
       </c>
       <c r="R64" t="n">
-        <v>6901409</v>
+        <v>6901438</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7174,6 +7174,240 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120144261</v>
+      </c>
+      <c r="B65" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>458441</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6901767</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120140016</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91128</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>760</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>458161</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6901991</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Liggande sälg nära kalhygge.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119833909</v>
+        <v>119831044</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458175</v>
+        <v>458095</v>
       </c>
       <c r="R8" t="n">
-        <v>6901627</v>
+        <v>6901375</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119831719</v>
+        <v>119831593</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457858</v>
+        <v>457980</v>
       </c>
       <c r="R9" t="n">
-        <v>6901422</v>
+        <v>6901438</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119831005</v>
+        <v>119831262</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,38 +1564,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458099</v>
+        <v>458019</v>
       </c>
       <c r="R10" t="n">
-        <v>6901390</v>
+        <v>6901394</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1628,6 +1628,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,7 +1659,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119831262</v>
+        <v>119831168</v>
       </c>
       <c r="B11" t="n">
         <v>79607</v>
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458019</v>
+        <v>458064</v>
       </c>
       <c r="R11" t="n">
-        <v>6901394</v>
+        <v>6901364</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1730,11 +1735,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119831044</v>
+        <v>119833909</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,25 +1773,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458095</v>
+        <v>458175</v>
       </c>
       <c r="R12" t="n">
-        <v>6901375</v>
+        <v>6901627</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119831593</v>
+        <v>119831719</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,25 +1875,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457980</v>
+        <v>457858</v>
       </c>
       <c r="R13" t="n">
-        <v>6901438</v>
+        <v>6901422</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119831168</v>
+        <v>119831005</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,38 +1977,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458064</v>
+        <v>458099</v>
       </c>
       <c r="R14" t="n">
-        <v>6901364</v>
+        <v>6901390</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119831034</v>
+        <v>119830773</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,34 +2083,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458101</v>
+        <v>458081</v>
       </c>
       <c r="R15" t="n">
-        <v>6901379</v>
+        <v>6901475</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830773</v>
+        <v>119831034</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,34 +2185,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458081</v>
+        <v>458101</v>
       </c>
       <c r="R16" t="n">
-        <v>6901475</v>
+        <v>6901379</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119831651</v>
+        <v>119834180</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5659,25 +5659,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457975</v>
+        <v>458123</v>
       </c>
       <c r="R50" t="n">
-        <v>6901409</v>
+        <v>6901854</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119831564</v>
+        <v>119831651</v>
       </c>
       <c r="B51" t="n">
         <v>97907</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457994</v>
+        <v>457975</v>
       </c>
       <c r="R51" t="n">
-        <v>6901464</v>
+        <v>6901409</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5851,7 +5851,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119832417</v>
+        <v>119831564</v>
       </c>
       <c r="B52" t="n">
         <v>97907</v>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457946</v>
+        <v>457994</v>
       </c>
       <c r="R52" t="n">
-        <v>6901508</v>
+        <v>6901464</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119831249</v>
+        <v>119832417</v>
       </c>
       <c r="B53" t="n">
         <v>97907</v>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>458045</v>
+        <v>457946</v>
       </c>
       <c r="R53" t="n">
-        <v>6901417</v>
+        <v>6901508</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6055,10 +6055,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119834180</v>
+        <v>119831249</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6067,25 +6067,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>458123</v>
+        <v>458045</v>
       </c>
       <c r="R54" t="n">
-        <v>6901854</v>
+        <v>6901417</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -1348,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119831044</v>
+        <v>119830863</v>
       </c>
       <c r="B8" t="n">
         <v>79608</v>
@@ -1384,14 +1384,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458095</v>
+        <v>458090</v>
       </c>
       <c r="R8" t="n">
-        <v>6901375</v>
+        <v>6901440</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119831593</v>
+        <v>119832719</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457980</v>
+        <v>457992</v>
       </c>
       <c r="R9" t="n">
-        <v>6901438</v>
+        <v>6901502</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119831262</v>
+        <v>119832523</v>
       </c>
       <c r="B10" t="n">
         <v>79607</v>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458019</v>
+        <v>457981</v>
       </c>
       <c r="R10" t="n">
-        <v>6901394</v>
+        <v>6901523</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,11 +1628,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119831168</v>
+        <v>119830906</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,34 +1670,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458064</v>
+        <v>458090</v>
       </c>
       <c r="R11" t="n">
-        <v>6901364</v>
+        <v>6901440</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1761,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119833909</v>
+        <v>119831168</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,25 +1768,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458175</v>
+        <v>458064</v>
       </c>
       <c r="R12" t="n">
-        <v>6901627</v>
+        <v>6901364</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1863,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119831719</v>
+        <v>119831791</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,25 +1870,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1903,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457858</v>
+        <v>457796</v>
       </c>
       <c r="R13" t="n">
-        <v>6901422</v>
+        <v>6901401</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1965,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119831005</v>
+        <v>119832325</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,38 +1972,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458099</v>
+        <v>457950</v>
       </c>
       <c r="R14" t="n">
-        <v>6901390</v>
+        <v>6901553</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2067,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119830773</v>
+        <v>119834180</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,34 +2078,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458081</v>
+        <v>458123</v>
       </c>
       <c r="R15" t="n">
-        <v>6901475</v>
+        <v>6901854</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2169,7 +2164,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119831034</v>
+        <v>119834412</v>
       </c>
       <c r="B16" t="n">
         <v>79607</v>
@@ -2205,14 +2200,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458101</v>
+        <v>458147</v>
       </c>
       <c r="R16" t="n">
-        <v>6901379</v>
+        <v>6901790</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2245,6 +2240,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,7 +2271,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119831955</v>
+        <v>119831281</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457798</v>
+        <v>458034</v>
       </c>
       <c r="R17" t="n">
-        <v>6901409</v>
+        <v>6901429</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119834170</v>
+        <v>119831568</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458123</v>
+        <v>457981</v>
       </c>
       <c r="R18" t="n">
-        <v>6901854</v>
+        <v>6901471</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119830797</v>
+        <v>119833909</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2511,14 +2511,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458092</v>
+        <v>458175</v>
       </c>
       <c r="R19" t="n">
-        <v>6901472</v>
+        <v>6901627</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119831586</v>
+        <v>119833610</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457968</v>
+        <v>458139</v>
       </c>
       <c r="R20" t="n">
-        <v>6901445</v>
+        <v>6901557</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119831568</v>
+        <v>119832342</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457981</v>
+        <v>457951</v>
       </c>
       <c r="R21" t="n">
-        <v>6901471</v>
+        <v>6901545</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830810</v>
+        <v>119832379</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2817,14 +2817,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458102</v>
+        <v>457971</v>
       </c>
       <c r="R22" t="n">
-        <v>6901455</v>
+        <v>6901530</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2883,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119831437</v>
+        <v>119832197</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2895,25 +2895,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458021</v>
+        <v>457849</v>
       </c>
       <c r="R23" t="n">
-        <v>6901469</v>
+        <v>6901500</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119834306</v>
+        <v>119831719</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458116</v>
+        <v>457858</v>
       </c>
       <c r="R24" t="n">
-        <v>6901806</v>
+        <v>6901422</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119831657</v>
+        <v>119832531</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457940</v>
+        <v>457981</v>
       </c>
       <c r="R25" t="n">
-        <v>6901428</v>
+        <v>6901523</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119831192</v>
+        <v>119831586</v>
       </c>
       <c r="B26" t="n">
-        <v>78608</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,25 +3201,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458042</v>
+        <v>457968</v>
       </c>
       <c r="R26" t="n">
-        <v>6901347</v>
+        <v>6901445</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119832523</v>
+        <v>119834170</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,13 +3331,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457981</v>
+        <v>458123</v>
       </c>
       <c r="R27" t="n">
-        <v>6901523</v>
+        <v>6901854</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119831791</v>
+        <v>119831267</v>
       </c>
       <c r="B28" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3405,25 +3405,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457796</v>
+        <v>458019</v>
       </c>
       <c r="R28" t="n">
-        <v>6901401</v>
+        <v>6901394</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119832972</v>
+        <v>119834299</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3507,25 +3507,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458029</v>
+        <v>458164</v>
       </c>
       <c r="R29" t="n">
-        <v>6901493</v>
+        <v>6901837</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3597,10 +3597,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119832379</v>
+        <v>119834112</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3609,25 +3609,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457971</v>
+        <v>458204</v>
       </c>
       <c r="R30" t="n">
-        <v>6901530</v>
+        <v>6901795</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119830850</v>
+        <v>119831044</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3711,38 +3711,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458090</v>
+        <v>458095</v>
       </c>
       <c r="R31" t="n">
-        <v>6901440</v>
+        <v>6901375</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119830863</v>
+        <v>119831651</v>
       </c>
       <c r="B32" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3813,38 +3813,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458090</v>
+        <v>457975</v>
       </c>
       <c r="R32" t="n">
-        <v>6901440</v>
+        <v>6901409</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119832209</v>
+        <v>119831005</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3915,41 +3915,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>457874</v>
+        <v>458099</v>
       </c>
       <c r="R33" t="n">
-        <v>6901494</v>
+        <v>6901390</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4005,10 +4005,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119830906</v>
+        <v>119830773</v>
       </c>
       <c r="B34" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458090</v>
+        <v>458081</v>
       </c>
       <c r="R34" t="n">
-        <v>6901440</v>
+        <v>6901475</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119831281</v>
+        <v>119830850</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4143,17 +4143,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458034</v>
+        <v>458090</v>
       </c>
       <c r="R35" t="n">
-        <v>6901429</v>
+        <v>6901440</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119831267</v>
+        <v>119833397</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458019</v>
+        <v>458066</v>
       </c>
       <c r="R36" t="n">
-        <v>6901394</v>
+        <v>6901440</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119832342</v>
+        <v>119832390</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457951</v>
+        <v>457939</v>
       </c>
       <c r="R37" t="n">
-        <v>6901545</v>
+        <v>6901499</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4413,10 +4413,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119832197</v>
+        <v>119831249</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4425,25 +4425,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457849</v>
+        <v>458045</v>
       </c>
       <c r="R38" t="n">
-        <v>6901500</v>
+        <v>6901417</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4515,10 +4515,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119833379</v>
+        <v>119831657</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4527,25 +4527,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>458065</v>
+        <v>457940</v>
       </c>
       <c r="R39" t="n">
-        <v>6901429</v>
+        <v>6901428</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4617,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119832719</v>
+        <v>119831301</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4629,25 +4629,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457992</v>
+        <v>458031</v>
       </c>
       <c r="R40" t="n">
-        <v>6901502</v>
+        <v>6901401</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119833397</v>
+        <v>119833379</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458066</v>
+        <v>458065</v>
       </c>
       <c r="R41" t="n">
-        <v>6901440</v>
+        <v>6901429</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4821,10 +4821,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119832390</v>
+        <v>119832209</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4833,25 +4833,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457939</v>
+        <v>457874</v>
       </c>
       <c r="R42" t="n">
-        <v>6901499</v>
+        <v>6901494</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119832322</v>
+        <v>119831955</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457900</v>
+        <v>457798</v>
       </c>
       <c r="R43" t="n">
-        <v>6901490</v>
+        <v>6901409</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4999,11 +4999,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5030,10 +5025,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119832325</v>
+        <v>119832130</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5042,25 +5037,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5070,10 +5065,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457950</v>
+        <v>457815</v>
       </c>
       <c r="R44" t="n">
-        <v>6901553</v>
+        <v>6901466</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5132,7 +5127,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119832531</v>
+        <v>119830810</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5168,14 +5163,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457981</v>
+        <v>458102</v>
       </c>
       <c r="R45" t="n">
-        <v>6901523</v>
+        <v>6901455</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5234,10 +5229,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119834412</v>
+        <v>119830797</v>
       </c>
       <c r="B46" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5246,38 +5241,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458147</v>
+        <v>458092</v>
       </c>
       <c r="R46" t="n">
-        <v>6901790</v>
+        <v>6901472</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5310,11 +5305,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5341,10 +5331,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119834066</v>
+        <v>119833531</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5353,25 +5343,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458212</v>
+        <v>458113</v>
       </c>
       <c r="R47" t="n">
-        <v>6901767</v>
+        <v>6901438</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5443,7 +5433,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119831182</v>
+        <v>119832322</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5483,10 +5473,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458050</v>
+        <v>457900</v>
       </c>
       <c r="R48" t="n">
-        <v>6901340</v>
+        <v>6901490</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5519,6 +5509,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5545,10 +5540,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119831301</v>
+        <v>119831564</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5557,25 +5552,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5585,10 +5580,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>458031</v>
+        <v>457994</v>
       </c>
       <c r="R49" t="n">
-        <v>6901401</v>
+        <v>6901464</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5647,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119834180</v>
+        <v>119834306</v>
       </c>
       <c r="B50" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5659,25 +5654,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5687,13 +5682,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>458123</v>
+        <v>458116</v>
       </c>
       <c r="R50" t="n">
-        <v>6901854</v>
+        <v>6901806</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5749,10 +5744,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119831651</v>
+        <v>119830940</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5761,38 +5756,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457975</v>
+        <v>458107</v>
       </c>
       <c r="R51" t="n">
-        <v>6901409</v>
+        <v>6901417</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5851,7 +5846,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119831564</v>
+        <v>119831182</v>
       </c>
       <c r="B52" t="n">
         <v>97907</v>
@@ -5891,10 +5886,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>457994</v>
+        <v>458050</v>
       </c>
       <c r="R52" t="n">
-        <v>6901464</v>
+        <v>6901340</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5953,10 +5948,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119832417</v>
+        <v>119833969</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
+        <v>79115</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5965,25 +5960,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5993,10 +5988,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457946</v>
+        <v>458185</v>
       </c>
       <c r="R53" t="n">
-        <v>6901508</v>
+        <v>6901645</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6055,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119831249</v>
+        <v>119831034</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6067,38 +6062,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>458045</v>
+        <v>458101</v>
       </c>
       <c r="R54" t="n">
-        <v>6901417</v>
+        <v>6901379</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6157,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119834299</v>
+        <v>119832972</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6169,25 +6164,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6197,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458164</v>
+        <v>458029</v>
       </c>
       <c r="R55" t="n">
-        <v>6901837</v>
+        <v>6901493</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6361,7 +6356,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119832130</v>
+        <v>119832417</v>
       </c>
       <c r="B57" t="n">
         <v>97907</v>
@@ -6401,10 +6396,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457815</v>
+        <v>457946</v>
       </c>
       <c r="R57" t="n">
-        <v>6901466</v>
+        <v>6901508</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6565,10 +6560,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119833969</v>
+        <v>119831593</v>
       </c>
       <c r="B59" t="n">
-        <v>79115</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6581,21 +6576,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6605,10 +6600,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458185</v>
+        <v>457980</v>
       </c>
       <c r="R59" t="n">
-        <v>6901645</v>
+        <v>6901438</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6667,10 +6662,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119833610</v>
+        <v>119831262</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6679,25 +6674,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6707,10 +6702,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458139</v>
+        <v>458019</v>
       </c>
       <c r="R60" t="n">
-        <v>6901557</v>
+        <v>6901394</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6743,6 +6738,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6769,10 +6769,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119830940</v>
+        <v>119831192</v>
       </c>
       <c r="B61" t="n">
-        <v>91852</v>
+        <v>78608</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6781,38 +6781,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4366</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458107</v>
+        <v>458042</v>
       </c>
       <c r="R61" t="n">
-        <v>6901417</v>
+        <v>6901347</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6973,10 +6973,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119834112</v>
+        <v>119831437</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6985,25 +6985,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>458204</v>
+        <v>458021</v>
       </c>
       <c r="R63" t="n">
-        <v>6901795</v>
+        <v>6901469</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7075,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119833531</v>
+        <v>119834066</v>
       </c>
       <c r="B64" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,25 +7087,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>458113</v>
+        <v>458212</v>
       </c>
       <c r="R64" t="n">
-        <v>6901438</v>
+        <v>6901767</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7177,10 +7177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120144261</v>
+        <v>120140016</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>91128</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7193,35 +7193,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7229,10 +7228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>458441</v>
+        <v>458161</v>
       </c>
       <c r="R65" t="n">
-        <v>6901767</v>
+        <v>6901991</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7265,6 +7264,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Liggande sälg nära kalhygge.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7292,10 +7296,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120140016</v>
+        <v>120144261</v>
       </c>
       <c r="B66" t="n">
-        <v>91128</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7308,34 +7312,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7343,10 +7348,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458161</v>
+        <v>458441</v>
       </c>
       <c r="R66" t="n">
-        <v>6901991</v>
+        <v>6901767</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7379,11 +7384,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Liggande sälg nära kalhygge.</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -5331,10 +5331,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119833531</v>
+        <v>119832322</v>
       </c>
       <c r="B47" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5343,25 +5343,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458113</v>
+        <v>457900</v>
       </c>
       <c r="R47" t="n">
-        <v>6901438</v>
+        <v>6901490</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5407,6 +5407,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5433,7 +5438,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119832322</v>
+        <v>119831564</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5473,10 +5478,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457900</v>
+        <v>457994</v>
       </c>
       <c r="R48" t="n">
-        <v>6901490</v>
+        <v>6901464</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5509,11 +5514,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5540,7 +5540,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119831564</v>
+        <v>119834306</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457994</v>
+        <v>458116</v>
       </c>
       <c r="R49" t="n">
-        <v>6901464</v>
+        <v>6901806</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119834306</v>
+        <v>119833531</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5654,25 +5654,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5682,13 +5682,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>458116</v>
+        <v>458113</v>
       </c>
       <c r="R50" t="n">
-        <v>6901806</v>
+        <v>6901438</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6152,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119832972</v>
+        <v>119831262</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6164,25 +6164,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458029</v>
+        <v>458019</v>
       </c>
       <c r="R55" t="n">
-        <v>6901493</v>
+        <v>6901394</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6228,6 +6228,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6254,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119831671</v>
+        <v>119831192</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
+        <v>78608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6266,25 +6271,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6294,10 +6299,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457902</v>
+        <v>458042</v>
       </c>
       <c r="R56" t="n">
-        <v>6901423</v>
+        <v>6901347</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6356,7 +6361,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119832417</v>
+        <v>119832972</v>
       </c>
       <c r="B57" t="n">
         <v>97907</v>
@@ -6396,10 +6401,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457946</v>
+        <v>458029</v>
       </c>
       <c r="R57" t="n">
-        <v>6901508</v>
+        <v>6901493</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6458,7 +6463,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119831819</v>
+        <v>119831671</v>
       </c>
       <c r="B58" t="n">
         <v>97907</v>
@@ -6498,10 +6503,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457796</v>
+        <v>457902</v>
       </c>
       <c r="R58" t="n">
-        <v>6901388</v>
+        <v>6901423</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6560,10 +6565,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119831593</v>
+        <v>119832417</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6572,25 +6577,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6600,10 +6605,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457980</v>
+        <v>457946</v>
       </c>
       <c r="R59" t="n">
-        <v>6901438</v>
+        <v>6901508</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6662,10 +6667,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119831262</v>
+        <v>119831819</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6674,25 +6679,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6702,10 +6707,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458019</v>
+        <v>457796</v>
       </c>
       <c r="R60" t="n">
-        <v>6901394</v>
+        <v>6901388</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6738,11 +6743,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6769,10 +6769,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119831192</v>
+        <v>119831593</v>
       </c>
       <c r="B61" t="n">
-        <v>78608</v>
+        <v>79607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6785,21 +6785,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458042</v>
+        <v>457980</v>
       </c>
       <c r="R61" t="n">
-        <v>6901347</v>
+        <v>6901438</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119830863</v>
+        <v>119833909</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,38 +1360,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458090</v>
+        <v>458175</v>
       </c>
       <c r="R8" t="n">
-        <v>6901440</v>
+        <v>6901627</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119832719</v>
+        <v>119832130</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457992</v>
+        <v>457815</v>
       </c>
       <c r="R9" t="n">
-        <v>6901502</v>
+        <v>6901466</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119832523</v>
+        <v>119831719</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,25 +1564,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457981</v>
+        <v>457858</v>
       </c>
       <c r="R10" t="n">
-        <v>6901523</v>
+        <v>6901422</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830906</v>
+        <v>119832531</v>
       </c>
       <c r="B11" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,38 +1666,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458090</v>
+        <v>457981</v>
       </c>
       <c r="R11" t="n">
-        <v>6901440</v>
+        <v>6901523</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119831168</v>
+        <v>119831005</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,38 +1768,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458064</v>
+        <v>458099</v>
       </c>
       <c r="R12" t="n">
-        <v>6901364</v>
+        <v>6901390</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119831791</v>
+        <v>119830797</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,38 +1870,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457796</v>
+        <v>458092</v>
       </c>
       <c r="R13" t="n">
-        <v>6901401</v>
+        <v>6901472</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119832325</v>
+        <v>119834412</v>
       </c>
       <c r="B14" t="n">
         <v>79607</v>
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457950</v>
+        <v>458147</v>
       </c>
       <c r="R14" t="n">
-        <v>6901553</v>
+        <v>6901790</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2036,6 +2036,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,7 +2067,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119834180</v>
+        <v>119831593</v>
       </c>
       <c r="B15" t="n">
         <v>79607</v>
@@ -2102,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458123</v>
+        <v>457980</v>
       </c>
       <c r="R15" t="n">
-        <v>6901854</v>
+        <v>6901438</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2164,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119834412</v>
+        <v>119834112</v>
       </c>
       <c r="B16" t="n">
         <v>79607</v>
@@ -2204,10 +2209,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458147</v>
+        <v>458204</v>
       </c>
       <c r="R16" t="n">
-        <v>6901790</v>
+        <v>6901795</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2240,11 +2245,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119831281</v>
+        <v>119831791</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458034</v>
+        <v>457796</v>
       </c>
       <c r="R17" t="n">
-        <v>6901429</v>
+        <v>6901401</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119831568</v>
+        <v>119834306</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457981</v>
+        <v>458116</v>
       </c>
       <c r="R18" t="n">
-        <v>6901471</v>
+        <v>6901806</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119833909</v>
+        <v>119834066</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458175</v>
+        <v>458212</v>
       </c>
       <c r="R19" t="n">
-        <v>6901627</v>
+        <v>6901767</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119833610</v>
+        <v>119830850</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,38 +2589,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458139</v>
+        <v>458090</v>
       </c>
       <c r="R20" t="n">
-        <v>6901557</v>
+        <v>6901440</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119832342</v>
+        <v>119832719</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457951</v>
+        <v>457992</v>
       </c>
       <c r="R21" t="n">
-        <v>6901545</v>
+        <v>6901502</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119832379</v>
+        <v>119831586</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457971</v>
+        <v>457968</v>
       </c>
       <c r="R22" t="n">
-        <v>6901530</v>
+        <v>6901445</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2883,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119832197</v>
+        <v>119831564</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2895,25 +2895,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457849</v>
+        <v>457994</v>
       </c>
       <c r="R23" t="n">
-        <v>6901500</v>
+        <v>6901464</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119831719</v>
+        <v>119834170</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>457858</v>
+        <v>458123</v>
       </c>
       <c r="R24" t="n">
-        <v>6901422</v>
+        <v>6901854</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3087,7 +3087,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119832531</v>
+        <v>119831249</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3127,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>457981</v>
+        <v>458045</v>
       </c>
       <c r="R25" t="n">
-        <v>6901523</v>
+        <v>6901417</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119831586</v>
+        <v>119831301</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,25 +3201,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457968</v>
+        <v>458031</v>
       </c>
       <c r="R26" t="n">
-        <v>6901445</v>
+        <v>6901401</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3291,7 +3291,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119834170</v>
+        <v>119831657</v>
       </c>
       <c r="B27" t="n">
         <v>97907</v>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458123</v>
+        <v>457940</v>
       </c>
       <c r="R27" t="n">
-        <v>6901854</v>
+        <v>6901428</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3393,7 +3393,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119831267</v>
+        <v>119832322</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458019</v>
+        <v>457900</v>
       </c>
       <c r="R28" t="n">
-        <v>6901394</v>
+        <v>6901490</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3469,6 +3469,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3495,10 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119834299</v>
+        <v>119832342</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3507,25 +3512,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3540,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>458164</v>
+        <v>457951</v>
       </c>
       <c r="R29" t="n">
-        <v>6901837</v>
+        <v>6901545</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3597,10 +3602,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119834112</v>
+        <v>119833397</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3609,25 +3614,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3637,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458204</v>
+        <v>458066</v>
       </c>
       <c r="R30" t="n">
-        <v>6901795</v>
+        <v>6901440</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3699,10 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119831044</v>
+        <v>119833610</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3711,25 +3716,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,10 +3744,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458095</v>
+        <v>458139</v>
       </c>
       <c r="R31" t="n">
-        <v>6901375</v>
+        <v>6901557</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3801,7 +3806,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119831651</v>
+        <v>119831819</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -3841,10 +3846,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457975</v>
+        <v>457796</v>
       </c>
       <c r="R32" t="n">
-        <v>6901409</v>
+        <v>6901388</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3903,10 +3908,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119831005</v>
+        <v>119833969</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>79115</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3915,38 +3920,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458099</v>
+        <v>458185</v>
       </c>
       <c r="R33" t="n">
-        <v>6901390</v>
+        <v>6901645</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4005,10 +4010,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119830773</v>
+        <v>119831267</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4017,38 +4022,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458081</v>
+        <v>458019</v>
       </c>
       <c r="R34" t="n">
-        <v>6901475</v>
+        <v>6901394</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4107,10 +4112,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119830850</v>
+        <v>119834299</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4119,38 +4124,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458090</v>
+        <v>458164</v>
       </c>
       <c r="R35" t="n">
-        <v>6901440</v>
+        <v>6901837</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4209,10 +4214,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119833397</v>
+        <v>119831034</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4221,38 +4226,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458066</v>
+        <v>458101</v>
       </c>
       <c r="R36" t="n">
-        <v>6901440</v>
+        <v>6901379</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4413,7 +4418,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119831249</v>
+        <v>119831671</v>
       </c>
       <c r="B38" t="n">
         <v>97907</v>
@@ -4453,10 +4458,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>458045</v>
+        <v>457902</v>
       </c>
       <c r="R38" t="n">
-        <v>6901417</v>
+        <v>6901423</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4515,10 +4520,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119831657</v>
+        <v>119832197</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4527,25 +4532,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4555,10 +4560,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457940</v>
+        <v>457849</v>
       </c>
       <c r="R39" t="n">
-        <v>6901428</v>
+        <v>6901500</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4617,7 +4622,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119831301</v>
+        <v>119832325</v>
       </c>
       <c r="B40" t="n">
         <v>79607</v>
@@ -4657,10 +4662,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458031</v>
+        <v>457950</v>
       </c>
       <c r="R40" t="n">
-        <v>6901401</v>
+        <v>6901553</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4719,10 +4724,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119833379</v>
+        <v>119830940</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>91852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4731,38 +4736,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458065</v>
+        <v>458107</v>
       </c>
       <c r="R41" t="n">
-        <v>6901429</v>
+        <v>6901417</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4821,10 +4826,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119832209</v>
+        <v>119831168</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4833,25 +4838,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4861,13 +4866,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>457874</v>
+        <v>458064</v>
       </c>
       <c r="R42" t="n">
-        <v>6901494</v>
+        <v>6901364</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4923,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119831955</v>
+        <v>119831192</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>78608</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4935,25 +4940,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4963,10 +4968,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457798</v>
+        <v>458042</v>
       </c>
       <c r="R43" t="n">
-        <v>6901409</v>
+        <v>6901347</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5025,10 +5030,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119832130</v>
+        <v>119831262</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5037,25 +5042,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5065,10 +5070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457815</v>
+        <v>458019</v>
       </c>
       <c r="R44" t="n">
-        <v>6901466</v>
+        <v>6901394</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5101,6 +5106,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5127,7 +5137,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119830810</v>
+        <v>119831281</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5163,17 +5173,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>458102</v>
+        <v>458034</v>
       </c>
       <c r="R45" t="n">
-        <v>6901455</v>
+        <v>6901429</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5229,10 +5239,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119830797</v>
+        <v>119830863</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5241,25 +5251,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5269,10 +5279,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458092</v>
+        <v>458090</v>
       </c>
       <c r="R46" t="n">
-        <v>6901472</v>
+        <v>6901440</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5331,7 +5341,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119832322</v>
+        <v>119832972</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -5371,10 +5381,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457900</v>
+        <v>458029</v>
       </c>
       <c r="R47" t="n">
-        <v>6901490</v>
+        <v>6901493</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5407,11 +5417,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5438,7 +5443,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119831564</v>
+        <v>119832417</v>
       </c>
       <c r="B48" t="n">
         <v>97907</v>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457994</v>
+        <v>457946</v>
       </c>
       <c r="R48" t="n">
-        <v>6901464</v>
+        <v>6901508</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5540,10 +5545,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119834306</v>
+        <v>119834180</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5552,25 +5557,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5580,13 +5585,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>458116</v>
+        <v>458123</v>
       </c>
       <c r="R49" t="n">
-        <v>6901806</v>
+        <v>6901854</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5642,10 +5647,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119833531</v>
+        <v>119830810</v>
       </c>
       <c r="B50" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5654,38 +5659,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>458113</v>
+        <v>458102</v>
       </c>
       <c r="R50" t="n">
-        <v>6901438</v>
+        <v>6901455</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5744,10 +5749,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119830940</v>
+        <v>119831955</v>
       </c>
       <c r="B51" t="n">
-        <v>91852</v>
+        <v>97907</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5756,38 +5761,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458107</v>
+        <v>457798</v>
       </c>
       <c r="R51" t="n">
-        <v>6901417</v>
+        <v>6901409</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5948,10 +5953,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119833969</v>
+        <v>119832523</v>
       </c>
       <c r="B53" t="n">
-        <v>79115</v>
+        <v>79607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5964,21 +5969,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5988,13 +5993,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>458185</v>
+        <v>457981</v>
       </c>
       <c r="R53" t="n">
-        <v>6901645</v>
+        <v>6901523</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6050,10 +6055,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119831034</v>
+        <v>119830906</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6066,34 +6071,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>458101</v>
+        <v>458090</v>
       </c>
       <c r="R54" t="n">
-        <v>6901379</v>
+        <v>6901440</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6152,7 +6157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119831262</v>
+        <v>119833379</v>
       </c>
       <c r="B55" t="n">
         <v>79607</v>
@@ -6192,10 +6197,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458019</v>
+        <v>458065</v>
       </c>
       <c r="R55" t="n">
-        <v>6901394</v>
+        <v>6901429</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6228,11 +6233,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6259,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119831192</v>
+        <v>119832379</v>
       </c>
       <c r="B56" t="n">
-        <v>78608</v>
+        <v>97907</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,25 +6271,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458042</v>
+        <v>457971</v>
       </c>
       <c r="R56" t="n">
-        <v>6901347</v>
+        <v>6901530</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119832972</v>
+        <v>119832209</v>
       </c>
       <c r="B57" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6373,25 +6373,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458029</v>
+        <v>457874</v>
       </c>
       <c r="R57" t="n">
-        <v>6901493</v>
+        <v>6901494</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119831671</v>
+        <v>119833531</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,25 +6475,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457902</v>
+        <v>458113</v>
       </c>
       <c r="R58" t="n">
-        <v>6901423</v>
+        <v>6901438</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119832417</v>
+        <v>119831651</v>
       </c>
       <c r="B59" t="n">
         <v>97907</v>
@@ -6605,10 +6605,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457946</v>
+        <v>457975</v>
       </c>
       <c r="R59" t="n">
-        <v>6901508</v>
+        <v>6901409</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6667,7 +6667,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119831819</v>
+        <v>119831568</v>
       </c>
       <c r="B60" t="n">
         <v>97907</v>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457796</v>
+        <v>457981</v>
       </c>
       <c r="R60" t="n">
-        <v>6901388</v>
+        <v>6901471</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6769,10 +6769,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119831593</v>
+        <v>119831437</v>
       </c>
       <c r="B61" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457980</v>
+        <v>458021</v>
       </c>
       <c r="R61" t="n">
-        <v>6901438</v>
+        <v>6901469</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119831166</v>
+        <v>119831044</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>458073</v>
+        <v>458095</v>
       </c>
       <c r="R62" t="n">
-        <v>6901343</v>
+        <v>6901375</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6973,10 +6973,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119831437</v>
+        <v>119831166</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6985,25 +6985,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>458021</v>
+        <v>458073</v>
       </c>
       <c r="R63" t="n">
-        <v>6901469</v>
+        <v>6901343</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7075,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119834066</v>
+        <v>119830773</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,38 +7087,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>458212</v>
+        <v>458081</v>
       </c>
       <c r="R64" t="n">
-        <v>6901767</v>
+        <v>6901475</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -3189,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119831301</v>
+        <v>119831657</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,25 +3201,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458031</v>
+        <v>457940</v>
       </c>
       <c r="R26" t="n">
-        <v>6901401</v>
+        <v>6901428</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119831657</v>
+        <v>119831301</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457940</v>
+        <v>458031</v>
       </c>
       <c r="R27" t="n">
-        <v>6901428</v>
+        <v>6901401</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -4520,10 +4520,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119832197</v>
+        <v>119832325</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4532,25 +4532,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457849</v>
+        <v>457950</v>
       </c>
       <c r="R39" t="n">
-        <v>6901500</v>
+        <v>6901553</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119832325</v>
+        <v>119832197</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4634,25 +4634,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457950</v>
+        <v>457849</v>
       </c>
       <c r="R40" t="n">
-        <v>6901553</v>
+        <v>6901500</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5030,10 +5030,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119831262</v>
+        <v>119831281</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5042,25 +5042,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5070,13 +5070,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458019</v>
+        <v>458034</v>
       </c>
       <c r="R44" t="n">
-        <v>6901394</v>
+        <v>6901429</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5106,11 +5106,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5137,10 +5132,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119831281</v>
+        <v>119831262</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5149,25 +5144,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5177,13 +5172,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>458034</v>
+        <v>458019</v>
       </c>
       <c r="R45" t="n">
-        <v>6901429</v>
+        <v>6901394</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5213,6 +5208,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -3189,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119831657</v>
+        <v>119831301</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,25 +3201,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457940</v>
+        <v>458031</v>
       </c>
       <c r="R26" t="n">
-        <v>6901428</v>
+        <v>6901401</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119831301</v>
+        <v>119831657</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458031</v>
+        <v>457940</v>
       </c>
       <c r="R27" t="n">
-        <v>6901401</v>
+        <v>6901428</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -5030,10 +5030,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119831281</v>
+        <v>119831262</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5042,25 +5042,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5070,13 +5070,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458034</v>
+        <v>458019</v>
       </c>
       <c r="R44" t="n">
-        <v>6901429</v>
+        <v>6901394</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5106,6 +5106,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5132,10 +5137,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119831262</v>
+        <v>119831281</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5144,25 +5149,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5172,13 +5177,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>458019</v>
+        <v>458034</v>
       </c>
       <c r="R45" t="n">
-        <v>6901394</v>
+        <v>6901429</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5208,11 +5213,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -4520,10 +4520,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119832325</v>
+        <v>119832197</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4532,25 +4532,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457950</v>
+        <v>457849</v>
       </c>
       <c r="R39" t="n">
-        <v>6901553</v>
+        <v>6901500</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119832197</v>
+        <v>119832325</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4634,25 +4634,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457849</v>
+        <v>457950</v>
       </c>
       <c r="R40" t="n">
-        <v>6901500</v>
+        <v>6901553</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5030,10 +5030,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119831262</v>
+        <v>119831281</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5042,25 +5042,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5070,13 +5070,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458019</v>
+        <v>458034</v>
       </c>
       <c r="R44" t="n">
-        <v>6901394</v>
+        <v>6901429</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5106,11 +5106,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5137,10 +5132,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119831281</v>
+        <v>119831262</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5149,25 +5144,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5177,13 +5172,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>458034</v>
+        <v>458019</v>
       </c>
       <c r="R45" t="n">
-        <v>6901429</v>
+        <v>6901394</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5213,6 +5208,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5239,10 +5239,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119830863</v>
+        <v>119832972</v>
       </c>
       <c r="B46" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5251,38 +5251,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458090</v>
+        <v>458029</v>
       </c>
       <c r="R46" t="n">
-        <v>6901440</v>
+        <v>6901493</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119832972</v>
+        <v>119832417</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458029</v>
+        <v>457946</v>
       </c>
       <c r="R47" t="n">
-        <v>6901493</v>
+        <v>6901508</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119832417</v>
+        <v>119830863</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5455,38 +5455,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457946</v>
+        <v>458090</v>
       </c>
       <c r="R48" t="n">
-        <v>6901508</v>
+        <v>6901440</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2373,7 +2373,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119834306</v>
+        <v>119834066</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458116</v>
+        <v>458212</v>
       </c>
       <c r="R18" t="n">
-        <v>6901806</v>
+        <v>6901767</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119834066</v>
+        <v>119834306</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2515,13 +2515,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458212</v>
+        <v>458116</v>
       </c>
       <c r="R19" t="n">
-        <v>6901767</v>
+        <v>6901806</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119832197</v>
+        <v>119832325</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4532,25 +4532,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457849</v>
+        <v>457950</v>
       </c>
       <c r="R39" t="n">
-        <v>6901500</v>
+        <v>6901553</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119832325</v>
+        <v>119832197</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4634,25 +4634,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457950</v>
+        <v>457849</v>
       </c>
       <c r="R40" t="n">
-        <v>6901553</v>
+        <v>6901500</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5239,10 +5239,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119832972</v>
+        <v>119830863</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>79608</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5251,38 +5251,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458029</v>
+        <v>458090</v>
       </c>
       <c r="R46" t="n">
-        <v>6901493</v>
+        <v>6901440</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119832417</v>
+        <v>119832972</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>457946</v>
+        <v>458029</v>
       </c>
       <c r="R47" t="n">
-        <v>6901508</v>
+        <v>6901493</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119830863</v>
+        <v>119832417</v>
       </c>
       <c r="B48" t="n">
-        <v>79608</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5455,38 +5455,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>458090</v>
+        <v>457946</v>
       </c>
       <c r="R48" t="n">
-        <v>6901440</v>
+        <v>6901508</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119832379</v>
+        <v>119832209</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,25 +6271,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6299,13 +6299,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457971</v>
+        <v>457874</v>
       </c>
       <c r="R56" t="n">
-        <v>6901530</v>
+        <v>6901494</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119832209</v>
+        <v>119833531</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6373,25 +6373,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457874</v>
+        <v>458113</v>
       </c>
       <c r="R57" t="n">
-        <v>6901494</v>
+        <v>6901438</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119833531</v>
+        <v>119832379</v>
       </c>
       <c r="B58" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,25 +6475,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458113</v>
+        <v>457971</v>
       </c>
       <c r="R58" t="n">
-        <v>6901438</v>
+        <v>6901530</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7409,6 +7409,1657 @@
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120306766</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>458277</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6901755</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120306650</v>
+      </c>
+      <c r="B68" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>458284</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6901758</v>
+      </c>
+      <c r="S68" t="n">
+        <v>20</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120306201</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>458128</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6901635</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120306914</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>458253</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6901772</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120306893</v>
+      </c>
+      <c r="B71" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>458263</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6901765</v>
+      </c>
+      <c r="S71" t="n">
+        <v>20</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120306521</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>458295</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6901764</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120306992</v>
+      </c>
+      <c r="B73" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>458181</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6901756</v>
+      </c>
+      <c r="S73" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120306966</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>458234</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6901764</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120306670</v>
+      </c>
+      <c r="B75" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>458280</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6901772</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120307076</v>
+      </c>
+      <c r="B76" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>458140</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6901768</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120306257</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78171</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>353</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>458154</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6901662</v>
+      </c>
+      <c r="S77" t="n">
+        <v>20</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120306901</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>458271</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6901756</v>
+      </c>
+      <c r="S78" t="n">
+        <v>20</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120306592</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>458290</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6901742</v>
+      </c>
+      <c r="S79" t="n">
+        <v>20</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120306799</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>458258</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6901747</v>
+      </c>
+      <c r="S80" t="n">
+        <v>20</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120306846</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>458248</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6901744</v>
+      </c>
+      <c r="S81" t="n">
+        <v>20</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Tät matta av kraftiga rosetter.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120306511</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>458306</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6901772</v>
+      </c>
+      <c r="S82" t="n">
+        <v>20</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -3189,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119831301</v>
+        <v>119831657</v>
       </c>
       <c r="B26" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,25 +3201,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458031</v>
+        <v>457940</v>
       </c>
       <c r="R26" t="n">
-        <v>6901401</v>
+        <v>6901428</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119831657</v>
+        <v>119831301</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,25 +3303,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>457940</v>
+        <v>458031</v>
       </c>
       <c r="R27" t="n">
-        <v>6901428</v>
+        <v>6901401</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -8640,7 +8640,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306592</v>
+        <v>120306799</v>
       </c>
       <c r="B79" t="n">
         <v>97907</v>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458290</v>
+        <v>458258</v>
       </c>
       <c r="R79" t="n">
-        <v>6901742</v>
+        <v>6901747</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8742,7 +8742,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120306799</v>
+        <v>120306592</v>
       </c>
       <c r="B80" t="n">
         <v>97907</v>
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458258</v>
+        <v>458290</v>
       </c>
       <c r="R80" t="n">
-        <v>6901747</v>
+        <v>6901742</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -8640,7 +8640,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306799</v>
+        <v>120306592</v>
       </c>
       <c r="B79" t="n">
         <v>97907</v>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458258</v>
+        <v>458290</v>
       </c>
       <c r="R79" t="n">
-        <v>6901747</v>
+        <v>6901742</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8742,7 +8742,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120306592</v>
+        <v>120306799</v>
       </c>
       <c r="B80" t="n">
         <v>97907</v>
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458290</v>
+        <v>458258</v>
       </c>
       <c r="R80" t="n">
-        <v>6901742</v>
+        <v>6901747</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119833909</v>
+        <v>119834412</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458175</v>
+        <v>458147</v>
       </c>
       <c r="R8" t="n">
-        <v>6901627</v>
+        <v>6901790</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1424,6 +1424,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119832130</v>
+        <v>119832209</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1467,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,13 +1495,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457815</v>
+        <v>457874</v>
       </c>
       <c r="R9" t="n">
-        <v>6901466</v>
+        <v>6901494</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119831719</v>
+        <v>119831955</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457858</v>
+        <v>457798</v>
       </c>
       <c r="R10" t="n">
-        <v>6901422</v>
+        <v>6901409</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1654,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119832531</v>
+        <v>119832379</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457981</v>
+        <v>457971</v>
       </c>
       <c r="R11" t="n">
-        <v>6901523</v>
+        <v>6901530</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1756,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119831005</v>
+        <v>119831819</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,14 +1797,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458099</v>
+        <v>457796</v>
       </c>
       <c r="R12" t="n">
-        <v>6901390</v>
+        <v>6901388</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1861,7 +1866,7 @@
         <v>119830797</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119834412</v>
+        <v>119831267</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,25 +1977,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458147</v>
+        <v>458019</v>
       </c>
       <c r="R14" t="n">
-        <v>6901790</v>
+        <v>6901394</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2036,11 +2041,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119831593</v>
+        <v>119833379</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457980</v>
+        <v>458065</v>
       </c>
       <c r="R15" t="n">
-        <v>6901438</v>
+        <v>6901429</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119834112</v>
+        <v>119830773</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,34 +2185,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458204</v>
+        <v>458081</v>
       </c>
       <c r="R16" t="n">
-        <v>6901795</v>
+        <v>6901475</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119831791</v>
+        <v>119833610</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457796</v>
+        <v>458139</v>
       </c>
       <c r="R17" t="n">
-        <v>6901401</v>
+        <v>6901557</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2373,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119834066</v>
+        <v>119834180</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2385,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458212</v>
+        <v>458123</v>
       </c>
       <c r="R18" t="n">
-        <v>6901767</v>
+        <v>6901854</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2475,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119834306</v>
+        <v>119831719</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,13 +2515,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458116</v>
+        <v>457858</v>
       </c>
       <c r="R19" t="n">
-        <v>6901806</v>
+        <v>6901422</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119830850</v>
+        <v>119831301</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,38 +2589,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458090</v>
+        <v>458031</v>
       </c>
       <c r="R20" t="n">
-        <v>6901440</v>
+        <v>6901401</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119832719</v>
+        <v>119832197</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,25 +2691,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457992</v>
+        <v>457849</v>
       </c>
       <c r="R21" t="n">
-        <v>6901502</v>
+        <v>6901500</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119831586</v>
+        <v>119830863</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2793,38 +2793,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>457968</v>
+        <v>458090</v>
       </c>
       <c r="R22" t="n">
-        <v>6901445</v>
+        <v>6901440</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2883,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119831564</v>
+        <v>119832322</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457994</v>
+        <v>457900</v>
       </c>
       <c r="R23" t="n">
-        <v>6901464</v>
+        <v>6901490</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2959,6 +2959,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2985,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119834170</v>
+        <v>119833397</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458123</v>
+        <v>458066</v>
       </c>
       <c r="R24" t="n">
-        <v>6901854</v>
+        <v>6901440</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3087,10 +3092,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119831249</v>
+        <v>119830850</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,14 +3128,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458045</v>
+        <v>458090</v>
       </c>
       <c r="R25" t="n">
-        <v>6901417</v>
+        <v>6901440</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3189,10 +3194,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119831657</v>
+        <v>119830940</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>91870</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,38 +3206,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>457940</v>
+        <v>458107</v>
       </c>
       <c r="R26" t="n">
-        <v>6901428</v>
+        <v>6901417</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3291,10 +3296,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119831301</v>
+        <v>119831192</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>78624</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3307,21 +3312,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3331,10 +3336,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458031</v>
+        <v>458042</v>
       </c>
       <c r="R27" t="n">
-        <v>6901401</v>
+        <v>6901347</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3393,10 +3398,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119832322</v>
+        <v>119832417</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457900</v>
+        <v>457946</v>
       </c>
       <c r="R28" t="n">
-        <v>6901490</v>
+        <v>6901508</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3469,11 +3474,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3500,10 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119832342</v>
+        <v>119832531</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457951</v>
+        <v>457981</v>
       </c>
       <c r="R29" t="n">
-        <v>6901545</v>
+        <v>6901523</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119833397</v>
+        <v>119834299</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3614,25 +3614,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458066</v>
+        <v>458164</v>
       </c>
       <c r="R30" t="n">
-        <v>6901440</v>
+        <v>6901837</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119833610</v>
+        <v>119831586</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3716,25 +3716,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458139</v>
+        <v>457968</v>
       </c>
       <c r="R31" t="n">
-        <v>6901557</v>
+        <v>6901445</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119831819</v>
+        <v>119833969</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>79131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3818,25 +3818,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>457796</v>
+        <v>458185</v>
       </c>
       <c r="R32" t="n">
-        <v>6901388</v>
+        <v>6901645</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119833969</v>
+        <v>119834066</v>
       </c>
       <c r="B33" t="n">
-        <v>79115</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3920,25 +3920,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458185</v>
+        <v>458212</v>
       </c>
       <c r="R33" t="n">
-        <v>6901645</v>
+        <v>6901767</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119831267</v>
+        <v>119830906</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4022,38 +4022,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458019</v>
+        <v>458090</v>
       </c>
       <c r="R34" t="n">
-        <v>6901394</v>
+        <v>6901440</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119834299</v>
+        <v>119831034</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4148,14 +4148,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458164</v>
+        <v>458101</v>
       </c>
       <c r="R35" t="n">
-        <v>6901837</v>
+        <v>6901379</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4214,10 +4214,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119831034</v>
+        <v>119831044</v>
       </c>
       <c r="B36" t="n">
-        <v>79607</v>
+        <v>79624</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4230,34 +4230,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458101</v>
+        <v>458095</v>
       </c>
       <c r="R36" t="n">
-        <v>6901379</v>
+        <v>6901375</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119832390</v>
+        <v>119832325</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4328,25 +4328,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457939</v>
+        <v>457950</v>
       </c>
       <c r="R37" t="n">
-        <v>6901499</v>
+        <v>6901553</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119831671</v>
+        <v>119832342</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457902</v>
+        <v>457951</v>
       </c>
       <c r="R38" t="n">
-        <v>6901423</v>
+        <v>6901545</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4520,10 +4520,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119832325</v>
+        <v>119832130</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4532,25 +4532,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457950</v>
+        <v>457815</v>
       </c>
       <c r="R39" t="n">
-        <v>6901553</v>
+        <v>6901466</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119832197</v>
+        <v>119831671</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4634,25 +4634,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457849</v>
+        <v>457902</v>
       </c>
       <c r="R40" t="n">
-        <v>6901500</v>
+        <v>6901423</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4724,10 +4724,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119830940</v>
+        <v>119831564</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4736,38 +4736,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458107</v>
+        <v>457994</v>
       </c>
       <c r="R41" t="n">
-        <v>6901417</v>
+        <v>6901464</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119831168</v>
+        <v>119831166</v>
       </c>
       <c r="B42" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4842,21 +4842,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458064</v>
+        <v>458073</v>
       </c>
       <c r="R42" t="n">
-        <v>6901364</v>
+        <v>6901343</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4928,10 +4928,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119831192</v>
+        <v>119831262</v>
       </c>
       <c r="B43" t="n">
-        <v>78608</v>
+        <v>79623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458042</v>
+        <v>458019</v>
       </c>
       <c r="R43" t="n">
-        <v>6901347</v>
+        <v>6901394</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5004,6 +5004,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5030,10 +5035,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119831281</v>
+        <v>119833531</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5042,25 +5047,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5070,13 +5075,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458034</v>
+        <v>458113</v>
       </c>
       <c r="R44" t="n">
-        <v>6901429</v>
+        <v>6901438</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5132,10 +5137,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119831262</v>
+        <v>119831657</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5144,25 +5149,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5172,10 +5177,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>458019</v>
+        <v>457940</v>
       </c>
       <c r="R45" t="n">
-        <v>6901394</v>
+        <v>6901428</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5208,11 +5213,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5239,10 +5239,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119830863</v>
+        <v>119831568</v>
       </c>
       <c r="B46" t="n">
-        <v>79608</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5251,38 +5251,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>458090</v>
+        <v>457981</v>
       </c>
       <c r="R46" t="n">
-        <v>6901440</v>
+        <v>6901471</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119832972</v>
+        <v>119834112</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5353,25 +5353,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458029</v>
+        <v>458204</v>
       </c>
       <c r="R47" t="n">
-        <v>6901493</v>
+        <v>6901795</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119832417</v>
+        <v>119831651</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457946</v>
+        <v>457975</v>
       </c>
       <c r="R48" t="n">
-        <v>6901508</v>
+        <v>6901409</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119834180</v>
+        <v>119833909</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5557,25 +5557,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>458123</v>
+        <v>458175</v>
       </c>
       <c r="R49" t="n">
-        <v>6901854</v>
+        <v>6901627</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5650,7 +5650,7 @@
         <v>119830810</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119831955</v>
+        <v>119831182</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457798</v>
+        <v>458050</v>
       </c>
       <c r="R51" t="n">
-        <v>6901409</v>
+        <v>6901340</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5851,10 +5851,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119831182</v>
+        <v>119831281</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5891,13 +5891,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458050</v>
+        <v>458034</v>
       </c>
       <c r="R52" t="n">
-        <v>6901340</v>
+        <v>6901429</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119832523</v>
+        <v>119831791</v>
       </c>
       <c r="B53" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5993,13 +5993,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457981</v>
+        <v>457796</v>
       </c>
       <c r="R53" t="n">
-        <v>6901523</v>
+        <v>6901401</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6055,10 +6055,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119830906</v>
+        <v>119832719</v>
       </c>
       <c r="B54" t="n">
-        <v>78262</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6067,38 +6067,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>458090</v>
+        <v>457992</v>
       </c>
       <c r="R54" t="n">
-        <v>6901440</v>
+        <v>6901502</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6157,10 +6157,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119833379</v>
+        <v>119832390</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6169,25 +6169,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>458065</v>
+        <v>457939</v>
       </c>
       <c r="R55" t="n">
-        <v>6901429</v>
+        <v>6901499</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119832209</v>
+        <v>119831437</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,25 +6271,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6299,13 +6299,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457874</v>
+        <v>458021</v>
       </c>
       <c r="R56" t="n">
-        <v>6901494</v>
+        <v>6901469</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119833531</v>
+        <v>119832523</v>
       </c>
       <c r="B57" t="n">
-        <v>78262</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6377,21 +6377,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6401,13 +6401,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458113</v>
+        <v>457981</v>
       </c>
       <c r="R57" t="n">
-        <v>6901438</v>
+        <v>6901523</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119832379</v>
+        <v>119831168</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,25 +6475,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457971</v>
+        <v>458064</v>
       </c>
       <c r="R58" t="n">
-        <v>6901530</v>
+        <v>6901364</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119831651</v>
+        <v>119831249</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6605,10 +6605,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>457975</v>
+        <v>458045</v>
       </c>
       <c r="R59" t="n">
-        <v>6901409</v>
+        <v>6901417</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119831568</v>
+        <v>119832972</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>457981</v>
+        <v>458029</v>
       </c>
       <c r="R60" t="n">
-        <v>6901471</v>
+        <v>6901493</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6769,10 +6769,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119831437</v>
+        <v>119831593</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>458021</v>
+        <v>457980</v>
       </c>
       <c r="R61" t="n">
-        <v>6901469</v>
+        <v>6901438</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119831044</v>
+        <v>119834306</v>
       </c>
       <c r="B62" t="n">
-        <v>79608</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6883,25 +6883,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6911,13 +6911,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>458095</v>
+        <v>458116</v>
       </c>
       <c r="R62" t="n">
-        <v>6901375</v>
+        <v>6901806</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6973,10 +6973,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119831166</v>
+        <v>119834170</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6985,25 +6985,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>458073</v>
+        <v>458123</v>
       </c>
       <c r="R63" t="n">
-        <v>6901343</v>
+        <v>6901854</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7075,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119830773</v>
+        <v>119831005</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,38 +7087,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>458081</v>
+        <v>458099</v>
       </c>
       <c r="R64" t="n">
-        <v>6901475</v>
+        <v>6901390</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7180,7 +7180,7 @@
         <v>120140016</v>
       </c>
       <c r="B65" t="n">
-        <v>91128</v>
+        <v>91146</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>120144261</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7411,10 +7411,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120306766</v>
+        <v>120306592</v>
       </c>
       <c r="B67" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458277</v>
+        <v>458290</v>
       </c>
       <c r="R67" t="n">
-        <v>6901755</v>
+        <v>6901742</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120306650</v>
+        <v>120306201</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>78279</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7525,25 +7525,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7553,13 +7553,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458284</v>
+        <v>458128</v>
       </c>
       <c r="R68" t="n">
-        <v>6901758</v>
+        <v>6901635</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7615,10 +7615,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120306201</v>
+        <v>120306846</v>
       </c>
       <c r="B69" t="n">
-        <v>78263</v>
+        <v>97930</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7627,41 +7627,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458128</v>
+        <v>458248</v>
       </c>
       <c r="R69" t="n">
-        <v>6901635</v>
+        <v>6901744</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7691,6 +7700,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7717,10 +7731,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120306914</v>
+        <v>120306670</v>
       </c>
       <c r="B70" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7757,13 +7771,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458253</v>
+        <v>458280</v>
       </c>
       <c r="R70" t="n">
         <v>6901772</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7793,6 +7807,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7819,10 +7838,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120306893</v>
+        <v>120307076</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7855,14 +7874,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458263</v>
+        <v>458140</v>
       </c>
       <c r="R71" t="n">
-        <v>6901765</v>
+        <v>6901768</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7921,10 +7940,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120306521</v>
+        <v>120306650</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7961,10 +7980,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458295</v>
+        <v>458284</v>
       </c>
       <c r="R72" t="n">
-        <v>6901764</v>
+        <v>6901758</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8023,10 +8042,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120306992</v>
+        <v>120306511</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8059,14 +8078,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458181</v>
+        <v>458306</v>
       </c>
       <c r="R73" t="n">
-        <v>6901756</v>
+        <v>6901772</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8125,10 +8144,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120306966</v>
+        <v>120306992</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8161,14 +8180,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>458234</v>
+        <v>458181</v>
       </c>
       <c r="R74" t="n">
-        <v>6901764</v>
+        <v>6901756</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8227,10 +8246,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120306670</v>
+        <v>120306893</v>
       </c>
       <c r="B75" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8267,10 +8286,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>458280</v>
+        <v>458263</v>
       </c>
       <c r="R75" t="n">
-        <v>6901772</v>
+        <v>6901765</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8303,11 +8322,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8334,10 +8348,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120307076</v>
+        <v>120306914</v>
       </c>
       <c r="B76" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8370,17 +8384,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458140</v>
+        <v>458253</v>
       </c>
       <c r="R76" t="n">
-        <v>6901768</v>
+        <v>6901772</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8436,10 +8450,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120306257</v>
+        <v>120306521</v>
       </c>
       <c r="B77" t="n">
-        <v>78171</v>
+        <v>97930</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8448,25 +8462,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8476,10 +8490,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458154</v>
+        <v>458295</v>
       </c>
       <c r="R77" t="n">
-        <v>6901662</v>
+        <v>6901764</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8538,10 +8552,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120306901</v>
+        <v>120306766</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8578,10 +8592,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458271</v>
+        <v>458277</v>
       </c>
       <c r="R78" t="n">
-        <v>6901756</v>
+        <v>6901755</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8640,10 +8654,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306592</v>
+        <v>120306799</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8680,10 +8694,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458290</v>
+        <v>458258</v>
       </c>
       <c r="R79" t="n">
-        <v>6901742</v>
+        <v>6901747</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8742,10 +8756,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120306799</v>
+        <v>120306901</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8782,10 +8796,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458258</v>
+        <v>458271</v>
       </c>
       <c r="R80" t="n">
-        <v>6901747</v>
+        <v>6901756</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8844,10 +8858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120306846</v>
+        <v>120306966</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8877,26 +8891,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458248</v>
+        <v>458234</v>
       </c>
       <c r="R81" t="n">
-        <v>6901744</v>
+        <v>6901764</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8929,11 +8934,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8960,10 +8960,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120306511</v>
+        <v>120306257</v>
       </c>
       <c r="B82" t="n">
-        <v>97907</v>
+        <v>78187</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8972,25 +8972,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458306</v>
+        <v>458154</v>
       </c>
       <c r="R82" t="n">
-        <v>6901772</v>
+        <v>6901662</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119834412</v>
+        <v>119831955</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458147</v>
+        <v>457798</v>
       </c>
       <c r="R8" t="n">
-        <v>6901790</v>
+        <v>6901409</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1424,11 +1424,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119832209</v>
+        <v>119832379</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,13 +1490,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457874</v>
+        <v>457971</v>
       </c>
       <c r="R9" t="n">
-        <v>6901494</v>
+        <v>6901530</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119831955</v>
+        <v>119831819</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457798</v>
+        <v>457796</v>
       </c>
       <c r="R10" t="n">
-        <v>6901409</v>
+        <v>6901388</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1659,7 +1654,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119832379</v>
+        <v>119830797</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1695,14 +1690,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457971</v>
+        <v>458092</v>
       </c>
       <c r="R11" t="n">
-        <v>6901530</v>
+        <v>6901472</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1761,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119831819</v>
+        <v>119832209</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,25 +1768,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457796</v>
+        <v>457874</v>
       </c>
       <c r="R12" t="n">
-        <v>6901388</v>
+        <v>6901494</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119830797</v>
+        <v>119834412</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,38 +1870,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458092</v>
+        <v>458147</v>
       </c>
       <c r="R13" t="n">
-        <v>6901472</v>
+        <v>6901790</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1939,6 +1934,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119833379</v>
+        <v>119833610</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,25 +2079,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458065</v>
+        <v>458139</v>
       </c>
       <c r="R15" t="n">
-        <v>6901429</v>
+        <v>6901557</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119833610</v>
+        <v>119833379</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2283,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458139</v>
+        <v>458065</v>
       </c>
       <c r="R17" t="n">
-        <v>6901557</v>
+        <v>6901429</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -3908,10 +3908,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119834066</v>
+        <v>119831034</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3920,38 +3920,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458212</v>
+        <v>458101</v>
       </c>
       <c r="R33" t="n">
-        <v>6901767</v>
+        <v>6901379</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119830906</v>
+        <v>119831044</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>79624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4026,34 +4026,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458090</v>
+        <v>458095</v>
       </c>
       <c r="R34" t="n">
-        <v>6901440</v>
+        <v>6901375</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4112,10 +4112,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119831034</v>
+        <v>119830906</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4128,34 +4128,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458101</v>
+        <v>458090</v>
       </c>
       <c r="R35" t="n">
-        <v>6901379</v>
+        <v>6901440</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4214,10 +4214,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119831044</v>
+        <v>119834066</v>
       </c>
       <c r="B36" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4226,25 +4226,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458095</v>
+        <v>458212</v>
       </c>
       <c r="R36" t="n">
-        <v>6901375</v>
+        <v>6901767</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120306201</v>
+        <v>120306670</v>
       </c>
       <c r="B68" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7525,25 +7525,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7553,13 +7553,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458128</v>
+        <v>458280</v>
       </c>
       <c r="R68" t="n">
-        <v>6901635</v>
+        <v>6901772</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7589,6 +7589,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7615,10 +7620,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120306846</v>
+        <v>120306201</v>
       </c>
       <c r="B69" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7627,50 +7632,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458248</v>
+        <v>458128</v>
       </c>
       <c r="R69" t="n">
-        <v>6901744</v>
+        <v>6901635</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7700,11 +7696,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,7 +7722,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120306670</v>
+        <v>120306846</v>
       </c>
       <c r="B70" t="n">
         <v>97930</v>
@@ -7764,17 +7755,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458280</v>
+        <v>458248</v>
       </c>
       <c r="R70" t="n">
-        <v>6901772</v>
+        <v>6901744</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Tät förekomst inom avverkningsanmälan.</t>
+          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119831955</v>
+        <v>119831034</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,38 +1360,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457798</v>
+        <v>458101</v>
       </c>
       <c r="R8" t="n">
-        <v>6901409</v>
+        <v>6901379</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119832379</v>
+        <v>119832209</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457971</v>
+        <v>457874</v>
       </c>
       <c r="R9" t="n">
-        <v>6901530</v>
+        <v>6901494</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119831819</v>
+        <v>119831281</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457796</v>
+        <v>458034</v>
       </c>
       <c r="R10" t="n">
-        <v>6901388</v>
+        <v>6901429</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119830797</v>
+        <v>119831593</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,38 +1666,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458092</v>
+        <v>457980</v>
       </c>
       <c r="R11" t="n">
-        <v>6901472</v>
+        <v>6901438</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119832209</v>
+        <v>119832972</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,25 +1768,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457874</v>
+        <v>458029</v>
       </c>
       <c r="R12" t="n">
-        <v>6901494</v>
+        <v>6901493</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119834412</v>
+        <v>119833379</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458147</v>
+        <v>458065</v>
       </c>
       <c r="R13" t="n">
-        <v>6901790</v>
+        <v>6901429</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1934,11 +1934,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119833610</v>
+        <v>119831671</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,25 +2074,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458139</v>
+        <v>457902</v>
       </c>
       <c r="R15" t="n">
-        <v>6901557</v>
+        <v>6901423</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2169,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119830773</v>
+        <v>119831955</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,38 +2176,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458081</v>
+        <v>457798</v>
       </c>
       <c r="R16" t="n">
-        <v>6901475</v>
+        <v>6901409</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2271,7 +2266,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119833379</v>
+        <v>119832523</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2311,13 +2306,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458065</v>
+        <v>457981</v>
       </c>
       <c r="R17" t="n">
-        <v>6901429</v>
+        <v>6901523</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119834180</v>
+        <v>119834170</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2380,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,7 +2470,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119831719</v>
+        <v>119831657</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2515,10 +2510,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457858</v>
+        <v>457940</v>
       </c>
       <c r="R19" t="n">
-        <v>6901422</v>
+        <v>6901428</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2577,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119831301</v>
+        <v>119831005</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,38 +2584,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458031</v>
+        <v>458099</v>
       </c>
       <c r="R20" t="n">
-        <v>6901401</v>
+        <v>6901390</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2679,10 +2674,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119832197</v>
+        <v>119831166</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,25 +2686,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2719,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457849</v>
+        <v>458073</v>
       </c>
       <c r="R21" t="n">
-        <v>6901500</v>
+        <v>6901343</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2781,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119830863</v>
+        <v>119834299</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2797,34 +2792,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458090</v>
+        <v>458164</v>
       </c>
       <c r="R22" t="n">
-        <v>6901440</v>
+        <v>6901837</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2883,10 +2878,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119832322</v>
+        <v>119831301</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2895,25 +2890,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2923,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>457900</v>
+        <v>458031</v>
       </c>
       <c r="R23" t="n">
-        <v>6901490</v>
+        <v>6901401</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2959,11 +2954,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119833397</v>
+        <v>119831044</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>79624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3002,25 +2992,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3030,10 +3020,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458066</v>
+        <v>458095</v>
       </c>
       <c r="R24" t="n">
-        <v>6901440</v>
+        <v>6901375</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3092,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830850</v>
+        <v>119830773</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3104,25 +3094,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3132,10 +3122,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458090</v>
+        <v>458081</v>
       </c>
       <c r="R25" t="n">
-        <v>6901440</v>
+        <v>6901475</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3194,10 +3184,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830940</v>
+        <v>119834066</v>
       </c>
       <c r="B26" t="n">
-        <v>91870</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3206,38 +3196,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458107</v>
+        <v>458212</v>
       </c>
       <c r="R26" t="n">
-        <v>6901417</v>
+        <v>6901767</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3296,10 +3286,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119831192</v>
+        <v>119830797</v>
       </c>
       <c r="B27" t="n">
-        <v>78624</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3308,38 +3298,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458042</v>
+        <v>458092</v>
       </c>
       <c r="R27" t="n">
-        <v>6901347</v>
+        <v>6901472</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3398,10 +3388,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119832417</v>
+        <v>119834412</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3410,25 +3400,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3438,10 +3428,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>457946</v>
+        <v>458147</v>
       </c>
       <c r="R28" t="n">
-        <v>6901508</v>
+        <v>6901790</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3474,6 +3464,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3500,7 +3495,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119832531</v>
+        <v>119831819</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3540,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457981</v>
+        <v>457796</v>
       </c>
       <c r="R29" t="n">
-        <v>6901523</v>
+        <v>6901388</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3602,10 +3597,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119834299</v>
+        <v>119832531</v>
       </c>
       <c r="B30" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3614,25 +3609,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>458164</v>
+        <v>457981</v>
       </c>
       <c r="R30" t="n">
-        <v>6901837</v>
+        <v>6901523</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3704,10 +3699,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119831586</v>
+        <v>119833969</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3716,25 +3711,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3744,10 +3739,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>457968</v>
+        <v>458185</v>
       </c>
       <c r="R31" t="n">
-        <v>6901445</v>
+        <v>6901645</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3806,10 +3801,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119833969</v>
+        <v>119833531</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3822,21 +3817,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3846,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458185</v>
+        <v>458113</v>
       </c>
       <c r="R32" t="n">
-        <v>6901645</v>
+        <v>6901438</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3908,10 +3903,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119831034</v>
+        <v>119830810</v>
       </c>
       <c r="B33" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3920,38 +3915,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458101</v>
+        <v>458102</v>
       </c>
       <c r="R33" t="n">
-        <v>6901379</v>
+        <v>6901455</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4010,10 +4005,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119831044</v>
+        <v>119834306</v>
       </c>
       <c r="B34" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4022,25 +4017,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4050,13 +4045,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458095</v>
+        <v>458116</v>
       </c>
       <c r="R34" t="n">
-        <v>6901375</v>
+        <v>6901806</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4112,10 +4107,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119830906</v>
+        <v>119831262</v>
       </c>
       <c r="B35" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4128,34 +4123,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458090</v>
+        <v>458019</v>
       </c>
       <c r="R35" t="n">
-        <v>6901440</v>
+        <v>6901394</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4188,6 +4183,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4214,7 +4214,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119834066</v>
+        <v>119831586</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458212</v>
+        <v>457968</v>
       </c>
       <c r="R36" t="n">
-        <v>6901767</v>
+        <v>6901445</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119832325</v>
+        <v>119833610</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4328,25 +4328,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457950</v>
+        <v>458139</v>
       </c>
       <c r="R37" t="n">
-        <v>6901553</v>
+        <v>6901557</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4418,7 +4418,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119832342</v>
+        <v>119833397</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>457951</v>
+        <v>458066</v>
       </c>
       <c r="R38" t="n">
-        <v>6901545</v>
+        <v>6901440</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119832130</v>
+        <v>119831249</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>457815</v>
+        <v>458045</v>
       </c>
       <c r="R39" t="n">
-        <v>6901466</v>
+        <v>6901417</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119831671</v>
+        <v>119832325</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4634,25 +4634,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457902</v>
+        <v>457950</v>
       </c>
       <c r="R40" t="n">
-        <v>6901423</v>
+        <v>6901553</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4724,10 +4724,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119831564</v>
+        <v>119831192</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>78624</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4736,25 +4736,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>457994</v>
+        <v>458042</v>
       </c>
       <c r="R41" t="n">
-        <v>6901464</v>
+        <v>6901347</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119831166</v>
+        <v>119830906</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4842,34 +4842,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458073</v>
+        <v>458090</v>
       </c>
       <c r="R42" t="n">
-        <v>6901343</v>
+        <v>6901440</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4928,7 +4928,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119831262</v>
+        <v>119831791</v>
       </c>
       <c r="B43" t="n">
         <v>79623</v>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>458019</v>
+        <v>457796</v>
       </c>
       <c r="R43" t="n">
-        <v>6901394</v>
+        <v>6901401</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5004,11 +5004,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5035,10 +5030,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119833531</v>
+        <v>119832390</v>
       </c>
       <c r="B44" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5047,25 +5042,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5075,10 +5070,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>458113</v>
+        <v>457939</v>
       </c>
       <c r="R44" t="n">
-        <v>6901438</v>
+        <v>6901499</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5137,7 +5132,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119831657</v>
+        <v>119832719</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5177,10 +5172,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457940</v>
+        <v>457992</v>
       </c>
       <c r="R45" t="n">
-        <v>6901428</v>
+        <v>6901502</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5239,7 +5234,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119831568</v>
+        <v>119831564</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5279,10 +5274,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457981</v>
+        <v>457994</v>
       </c>
       <c r="R46" t="n">
-        <v>6901471</v>
+        <v>6901464</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5341,10 +5336,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119834112</v>
+        <v>119831437</v>
       </c>
       <c r="B47" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5353,25 +5348,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5381,10 +5376,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458204</v>
+        <v>458021</v>
       </c>
       <c r="R47" t="n">
-        <v>6901795</v>
+        <v>6901469</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5443,7 +5438,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119831651</v>
+        <v>119831719</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457975</v>
+        <v>457858</v>
       </c>
       <c r="R48" t="n">
-        <v>6901409</v>
+        <v>6901422</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5545,7 +5540,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119833909</v>
+        <v>119831568</v>
       </c>
       <c r="B49" t="n">
         <v>97930</v>
@@ -5585,10 +5580,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>458175</v>
+        <v>457981</v>
       </c>
       <c r="R49" t="n">
-        <v>6901627</v>
+        <v>6901471</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5647,7 +5642,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119830810</v>
+        <v>119832322</v>
       </c>
       <c r="B50" t="n">
         <v>97930</v>
@@ -5683,14 +5678,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>458102</v>
+        <v>457900</v>
       </c>
       <c r="R50" t="n">
-        <v>6901455</v>
+        <v>6901490</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5723,6 +5718,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5749,7 +5749,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119831182</v>
+        <v>119832379</v>
       </c>
       <c r="B51" t="n">
         <v>97930</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>458050</v>
+        <v>457971</v>
       </c>
       <c r="R51" t="n">
-        <v>6901340</v>
+        <v>6901530</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5851,10 +5851,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119831281</v>
+        <v>119831168</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5863,25 +5863,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5891,13 +5891,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458034</v>
+        <v>458064</v>
       </c>
       <c r="R52" t="n">
-        <v>6901429</v>
+        <v>6901364</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119831791</v>
+        <v>119834112</v>
       </c>
       <c r="B53" t="n">
         <v>79623</v>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457796</v>
+        <v>458204</v>
       </c>
       <c r="R53" t="n">
-        <v>6901401</v>
+        <v>6901795</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6055,10 +6055,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119832719</v>
+        <v>119834180</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6067,25 +6067,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457992</v>
+        <v>458123</v>
       </c>
       <c r="R54" t="n">
-        <v>6901502</v>
+        <v>6901854</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6157,7 +6157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119832390</v>
+        <v>119832417</v>
       </c>
       <c r="B55" t="n">
         <v>97930</v>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457939</v>
+        <v>457946</v>
       </c>
       <c r="R55" t="n">
-        <v>6901499</v>
+        <v>6901508</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119831437</v>
+        <v>119832342</v>
       </c>
       <c r="B56" t="n">
         <v>97930</v>
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>458021</v>
+        <v>457951</v>
       </c>
       <c r="R56" t="n">
-        <v>6901469</v>
+        <v>6901545</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119832523</v>
+        <v>119830863</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6377,37 +6377,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>457981</v>
+        <v>458090</v>
       </c>
       <c r="R57" t="n">
-        <v>6901523</v>
+        <v>6901440</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119831168</v>
+        <v>119832197</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,25 +6475,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>458064</v>
+        <v>457849</v>
       </c>
       <c r="R58" t="n">
-        <v>6901364</v>
+        <v>6901500</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119831249</v>
+        <v>119833909</v>
       </c>
       <c r="B59" t="n">
         <v>97930</v>
@@ -6605,10 +6605,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458045</v>
+        <v>458175</v>
       </c>
       <c r="R59" t="n">
-        <v>6901417</v>
+        <v>6901627</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119832972</v>
+        <v>119830940</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
+        <v>91870</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6679,38 +6679,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458029</v>
+        <v>458107</v>
       </c>
       <c r="R60" t="n">
-        <v>6901493</v>
+        <v>6901417</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6769,10 +6769,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119831593</v>
+        <v>119831651</v>
       </c>
       <c r="B61" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457980</v>
+        <v>457975</v>
       </c>
       <c r="R61" t="n">
-        <v>6901438</v>
+        <v>6901409</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119834306</v>
+        <v>119831182</v>
       </c>
       <c r="B62" t="n">
         <v>97930</v>
@@ -6911,13 +6911,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>458116</v>
+        <v>458050</v>
       </c>
       <c r="R62" t="n">
-        <v>6901806</v>
+        <v>6901340</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119834170</v>
+        <v>119832130</v>
       </c>
       <c r="B63" t="n">
         <v>97930</v>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>458123</v>
+        <v>457815</v>
       </c>
       <c r="R63" t="n">
-        <v>6901854</v>
+        <v>6901466</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7075,7 +7075,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119831005</v>
+        <v>119830850</v>
       </c>
       <c r="B64" t="n">
         <v>97930</v>
@@ -7111,14 +7111,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>458099</v>
+        <v>458090</v>
       </c>
       <c r="R64" t="n">
-        <v>6901390</v>
+        <v>6901440</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7177,10 +7177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120140016</v>
+        <v>120144261</v>
       </c>
       <c r="B65" t="n">
-        <v>91146</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7193,34 +7193,35 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7228,10 +7229,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>458161</v>
+        <v>458441</v>
       </c>
       <c r="R65" t="n">
-        <v>6901991</v>
+        <v>6901767</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7264,11 +7265,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Liggande sälg nära kalhygge.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7296,10 +7292,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120144261</v>
+        <v>120140016</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7312,35 +7308,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7348,10 +7343,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458441</v>
+        <v>458161</v>
       </c>
       <c r="R66" t="n">
-        <v>6901767</v>
+        <v>6901991</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7384,6 +7379,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Liggande sälg nära kalhygge.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,7 +7411,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120306592</v>
+        <v>120306766</v>
       </c>
       <c r="B67" t="n">
         <v>97930</v>
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458290</v>
+        <v>458277</v>
       </c>
       <c r="R67" t="n">
-        <v>6901742</v>
+        <v>6901755</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7513,7 +7513,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120306670</v>
+        <v>120306592</v>
       </c>
       <c r="B68" t="n">
         <v>97930</v>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458280</v>
+        <v>458290</v>
       </c>
       <c r="R68" t="n">
-        <v>6901772</v>
+        <v>6901742</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7589,11 +7589,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7620,10 +7615,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120306201</v>
+        <v>120307076</v>
       </c>
       <c r="B69" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7632,41 +7627,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458128</v>
+        <v>458140</v>
       </c>
       <c r="R69" t="n">
-        <v>6901635</v>
+        <v>6901768</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7722,7 +7717,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120306846</v>
+        <v>120306521</v>
       </c>
       <c r="B70" t="n">
         <v>97930</v>
@@ -7755,26 +7750,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458248</v>
+        <v>458295</v>
       </c>
       <c r="R70" t="n">
-        <v>6901744</v>
+        <v>6901764</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7807,11 +7793,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7838,10 +7819,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120307076</v>
+        <v>120306257</v>
       </c>
       <c r="B71" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7850,38 +7831,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458140</v>
+        <v>458154</v>
       </c>
       <c r="R71" t="n">
-        <v>6901768</v>
+        <v>6901662</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8042,7 +8023,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120306511</v>
+        <v>120306846</v>
       </c>
       <c r="B73" t="n">
         <v>97930</v>
@@ -8075,17 +8056,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458306</v>
+        <v>458248</v>
       </c>
       <c r="R73" t="n">
-        <v>6901772</v>
+        <v>6901744</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8118,6 +8108,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8144,7 +8139,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120306992</v>
+        <v>120306799</v>
       </c>
       <c r="B74" t="n">
         <v>97930</v>
@@ -8180,14 +8175,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>458181</v>
+        <v>458258</v>
       </c>
       <c r="R74" t="n">
-        <v>6901756</v>
+        <v>6901747</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8450,7 +8445,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120306521</v>
+        <v>120306966</v>
       </c>
       <c r="B77" t="n">
         <v>97930</v>
@@ -8490,7 +8485,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458295</v>
+        <v>458234</v>
       </c>
       <c r="R77" t="n">
         <v>6901764</v>
@@ -8552,7 +8547,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120306766</v>
+        <v>120306670</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -8592,10 +8587,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458277</v>
+        <v>458280</v>
       </c>
       <c r="R78" t="n">
-        <v>6901755</v>
+        <v>6901772</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8628,6 +8623,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8654,10 +8654,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306799</v>
+        <v>120306201</v>
       </c>
       <c r="B79" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8666,25 +8666,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8694,13 +8694,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458258</v>
+        <v>458128</v>
       </c>
       <c r="R79" t="n">
-        <v>6901747</v>
+        <v>6901635</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120306901</v>
+        <v>120306511</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458271</v>
+        <v>458306</v>
       </c>
       <c r="R80" t="n">
-        <v>6901756</v>
+        <v>6901772</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120306966</v>
+        <v>120306992</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -8894,14 +8894,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458234</v>
+        <v>458181</v>
       </c>
       <c r="R81" t="n">
-        <v>6901764</v>
+        <v>6901756</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8960,10 +8960,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120306257</v>
+        <v>120306901</v>
       </c>
       <c r="B82" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8972,25 +8972,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458154</v>
+        <v>458271</v>
       </c>
       <c r="R82" t="n">
-        <v>6901662</v>
+        <v>6901756</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119831955</v>
+        <v>119832523</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,13 +2204,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457798</v>
+        <v>457981</v>
       </c>
       <c r="R16" t="n">
-        <v>6901409</v>
+        <v>6901523</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119832523</v>
+        <v>119831955</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,25 +2278,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457981</v>
+        <v>457798</v>
       </c>
       <c r="R17" t="n">
-        <v>6901523</v>
+        <v>6901409</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119833610</v>
+        <v>119832325</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4328,25 +4328,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>458139</v>
+        <v>457950</v>
       </c>
       <c r="R37" t="n">
-        <v>6901557</v>
+        <v>6901553</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119832325</v>
+        <v>119833610</v>
       </c>
       <c r="B40" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4634,25 +4634,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>457950</v>
+        <v>458139</v>
       </c>
       <c r="R40" t="n">
-        <v>6901553</v>
+        <v>6901557</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119831034</v>
+        <v>119831044</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,34 +1364,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458101</v>
+        <v>458095</v>
       </c>
       <c r="R8" t="n">
-        <v>6901379</v>
+        <v>6901375</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119832209</v>
+        <v>119833610</v>
       </c>
       <c r="B9" t="n">
         <v>91858</v>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457874</v>
+        <v>458139</v>
       </c>
       <c r="R9" t="n">
-        <v>6901494</v>
+        <v>6901557</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119831281</v>
+        <v>119831005</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1588,17 +1588,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458034</v>
+        <v>458099</v>
       </c>
       <c r="R10" t="n">
-        <v>6901429</v>
+        <v>6901390</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119831593</v>
+        <v>119834412</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457980</v>
+        <v>458147</v>
       </c>
       <c r="R11" t="n">
-        <v>6901438</v>
+        <v>6901790</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1730,6 +1730,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119832972</v>
+        <v>119830940</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>91870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,38 +1773,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458029</v>
+        <v>458107</v>
       </c>
       <c r="R12" t="n">
-        <v>6901493</v>
+        <v>6901417</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1858,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119833379</v>
+        <v>119832130</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,25 +1875,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458065</v>
+        <v>457815</v>
       </c>
       <c r="R13" t="n">
-        <v>6901429</v>
+        <v>6901466</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1960,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119831267</v>
+        <v>119833379</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,25 +1977,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458019</v>
+        <v>458065</v>
       </c>
       <c r="R14" t="n">
-        <v>6901394</v>
+        <v>6901429</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2062,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119831671</v>
+        <v>119831192</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>78624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,25 +2079,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457902</v>
+        <v>458042</v>
       </c>
       <c r="R15" t="n">
-        <v>6901423</v>
+        <v>6901347</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2164,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119832523</v>
+        <v>119831568</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2212,10 @@
         <v>457981</v>
       </c>
       <c r="R16" t="n">
-        <v>6901523</v>
+        <v>6901471</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2266,7 +2271,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119831955</v>
+        <v>119831586</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2306,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457798</v>
+        <v>457968</v>
       </c>
       <c r="R17" t="n">
-        <v>6901409</v>
+        <v>6901445</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2368,7 +2373,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119834170</v>
+        <v>119831267</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2408,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458123</v>
+        <v>458019</v>
       </c>
       <c r="R18" t="n">
-        <v>6901854</v>
+        <v>6901394</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2470,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119831657</v>
+        <v>119833531</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2510,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457940</v>
+        <v>458113</v>
       </c>
       <c r="R19" t="n">
-        <v>6901428</v>
+        <v>6901438</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2572,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119831005</v>
+        <v>119831034</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2584,25 +2589,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458099</v>
+        <v>458101</v>
       </c>
       <c r="R20" t="n">
-        <v>6901390</v>
+        <v>6901379</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2674,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119831166</v>
+        <v>119831791</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2690,21 +2695,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2714,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458073</v>
+        <v>457796</v>
       </c>
       <c r="R21" t="n">
-        <v>6901343</v>
+        <v>6901401</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2776,10 +2781,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119834299</v>
+        <v>119832417</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,25 +2793,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2821,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458164</v>
+        <v>457946</v>
       </c>
       <c r="R22" t="n">
-        <v>6901837</v>
+        <v>6901508</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2878,10 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119831301</v>
+        <v>119831166</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,21 +2899,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2923,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458031</v>
+        <v>458073</v>
       </c>
       <c r="R23" t="n">
-        <v>6901401</v>
+        <v>6901343</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2980,10 +2985,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119831044</v>
+        <v>119830850</v>
       </c>
       <c r="B24" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2992,38 +2997,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>458095</v>
+        <v>458090</v>
       </c>
       <c r="R24" t="n">
-        <v>6901375</v>
+        <v>6901440</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3082,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119830773</v>
+        <v>119832379</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3094,38 +3099,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>458081</v>
+        <v>457971</v>
       </c>
       <c r="R25" t="n">
-        <v>6901475</v>
+        <v>6901530</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3184,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119834066</v>
+        <v>119830906</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3196,38 +3201,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458212</v>
+        <v>458090</v>
       </c>
       <c r="R26" t="n">
-        <v>6901767</v>
+        <v>6901440</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3286,7 +3291,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119830797</v>
+        <v>119834306</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3322,17 +3327,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458092</v>
+        <v>458116</v>
       </c>
       <c r="R27" t="n">
-        <v>6901472</v>
+        <v>6901806</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3388,7 +3393,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119834412</v>
+        <v>119834299</v>
       </c>
       <c r="B28" t="n">
         <v>79623</v>
@@ -3428,10 +3433,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458147</v>
+        <v>458164</v>
       </c>
       <c r="R28" t="n">
-        <v>6901790</v>
+        <v>6901837</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3464,11 +3469,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>En makalös sälgkontinuitet i området och mycket knärot tillika.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3495,10 +3495,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119831819</v>
+        <v>119832209</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3507,25 +3507,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,13 +3535,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>457796</v>
+        <v>457874</v>
       </c>
       <c r="R29" t="n">
-        <v>6901388</v>
+        <v>6901494</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119832531</v>
+        <v>119834170</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>457981</v>
+        <v>458123</v>
       </c>
       <c r="R30" t="n">
-        <v>6901523</v>
+        <v>6901854</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119833969</v>
+        <v>119834112</v>
       </c>
       <c r="B31" t="n">
-        <v>79131</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>458185</v>
+        <v>458204</v>
       </c>
       <c r="R31" t="n">
-        <v>6901645</v>
+        <v>6901795</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119833531</v>
+        <v>119831719</v>
       </c>
       <c r="B32" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3813,25 +3813,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>458113</v>
+        <v>457858</v>
       </c>
       <c r="R32" t="n">
-        <v>6901438</v>
+        <v>6901422</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119830810</v>
+        <v>119833909</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -3939,14 +3939,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>458102</v>
+        <v>458175</v>
       </c>
       <c r="R33" t="n">
-        <v>6901455</v>
+        <v>6901627</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119834306</v>
+        <v>119831437</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>458116</v>
+        <v>458021</v>
       </c>
       <c r="R34" t="n">
-        <v>6901806</v>
+        <v>6901469</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119831262</v>
+        <v>119831564</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4119,25 +4119,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>458019</v>
+        <v>457994</v>
       </c>
       <c r="R35" t="n">
-        <v>6901394</v>
+        <v>6901464</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4183,11 +4183,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4214,7 +4209,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119831586</v>
+        <v>119831671</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4254,10 +4249,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>457968</v>
+        <v>457902</v>
       </c>
       <c r="R36" t="n">
-        <v>6901445</v>
+        <v>6901423</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4316,10 +4311,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119832325</v>
+        <v>119832390</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4328,25 +4323,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4356,10 +4351,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>457950</v>
+        <v>457939</v>
       </c>
       <c r="R37" t="n">
-        <v>6901553</v>
+        <v>6901499</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4520,10 +4515,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119831249</v>
+        <v>119832523</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4532,25 +4527,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4560,13 +4555,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>458045</v>
+        <v>457981</v>
       </c>
       <c r="R39" t="n">
-        <v>6901417</v>
+        <v>6901523</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4622,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119833610</v>
+        <v>119831301</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4634,25 +4629,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4662,10 +4657,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>458139</v>
+        <v>458031</v>
       </c>
       <c r="R40" t="n">
-        <v>6901557</v>
+        <v>6901401</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4724,10 +4719,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119831192</v>
+        <v>119831168</v>
       </c>
       <c r="B41" t="n">
-        <v>78624</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4740,21 +4735,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4764,10 +4759,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>458042</v>
+        <v>458064</v>
       </c>
       <c r="R41" t="n">
-        <v>6901347</v>
+        <v>6901364</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4826,10 +4821,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119830906</v>
+        <v>119834180</v>
       </c>
       <c r="B42" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4842,34 +4837,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>458090</v>
+        <v>458123</v>
       </c>
       <c r="R42" t="n">
-        <v>6901440</v>
+        <v>6901854</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4928,10 +4923,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119831791</v>
+        <v>119830810</v>
       </c>
       <c r="B43" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4940,38 +4935,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>457796</v>
+        <v>458102</v>
       </c>
       <c r="R43" t="n">
-        <v>6901401</v>
+        <v>6901455</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5030,10 +5025,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119832390</v>
+        <v>119830773</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5042,38 +5037,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>457939</v>
+        <v>458081</v>
       </c>
       <c r="R44" t="n">
-        <v>6901499</v>
+        <v>6901475</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5132,10 +5127,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119832719</v>
+        <v>119832325</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5144,25 +5139,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5172,10 +5167,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>457992</v>
+        <v>457950</v>
       </c>
       <c r="R45" t="n">
-        <v>6901502</v>
+        <v>6901553</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5234,10 +5229,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119831564</v>
+        <v>119830863</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>79624</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5246,38 +5241,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>457994</v>
+        <v>458090</v>
       </c>
       <c r="R46" t="n">
-        <v>6901464</v>
+        <v>6901440</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5336,7 +5331,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119831437</v>
+        <v>119832342</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5376,10 +5371,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>458021</v>
+        <v>457951</v>
       </c>
       <c r="R47" t="n">
-        <v>6901469</v>
+        <v>6901545</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5438,7 +5433,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119831719</v>
+        <v>119831249</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -5478,10 +5473,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>457858</v>
+        <v>458045</v>
       </c>
       <c r="R48" t="n">
-        <v>6901422</v>
+        <v>6901417</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5540,7 +5535,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119831568</v>
+        <v>119832972</v>
       </c>
       <c r="B49" t="n">
         <v>97930</v>
@@ -5580,10 +5575,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>457981</v>
+        <v>458029</v>
       </c>
       <c r="R49" t="n">
-        <v>6901471</v>
+        <v>6901493</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5642,7 +5637,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119832322</v>
+        <v>119831281</v>
       </c>
       <c r="B50" t="n">
         <v>97930</v>
@@ -5682,13 +5677,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>457900</v>
+        <v>458034</v>
       </c>
       <c r="R50" t="n">
-        <v>6901490</v>
+        <v>6901429</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5718,11 +5713,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5749,10 +5739,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119832379</v>
+        <v>119831262</v>
       </c>
       <c r="B51" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5761,25 +5751,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5789,10 +5779,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>457971</v>
+        <v>458019</v>
       </c>
       <c r="R51" t="n">
-        <v>6901530</v>
+        <v>6901394</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5825,6 +5815,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Lunglav på björk.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5851,10 +5846,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119831168</v>
+        <v>119830797</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5863,38 +5858,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>458064</v>
+        <v>458092</v>
       </c>
       <c r="R52" t="n">
-        <v>6901364</v>
+        <v>6901472</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5953,10 +5948,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119834112</v>
+        <v>119832197</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5965,25 +5960,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5993,10 +5988,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>458204</v>
+        <v>457849</v>
       </c>
       <c r="R53" t="n">
-        <v>6901795</v>
+        <v>6901500</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6055,10 +6050,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119834180</v>
+        <v>119831955</v>
       </c>
       <c r="B54" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6067,25 +6062,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6095,10 +6090,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>458123</v>
+        <v>457798</v>
       </c>
       <c r="R54" t="n">
-        <v>6901854</v>
+        <v>6901409</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6157,7 +6152,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119832417</v>
+        <v>119832531</v>
       </c>
       <c r="B55" t="n">
         <v>97930</v>
@@ -6197,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457946</v>
+        <v>457981</v>
       </c>
       <c r="R55" t="n">
-        <v>6901508</v>
+        <v>6901523</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6259,7 +6254,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119832342</v>
+        <v>119832719</v>
       </c>
       <c r="B56" t="n">
         <v>97930</v>
@@ -6299,10 +6294,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>457951</v>
+        <v>457992</v>
       </c>
       <c r="R56" t="n">
-        <v>6901545</v>
+        <v>6901502</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6361,10 +6356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119830863</v>
+        <v>119831182</v>
       </c>
       <c r="B57" t="n">
-        <v>79624</v>
+        <v>97930</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6373,38 +6368,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458090</v>
+        <v>458050</v>
       </c>
       <c r="R57" t="n">
-        <v>6901440</v>
+        <v>6901340</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6463,10 +6458,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119832197</v>
+        <v>119831657</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,25 +6470,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6503,10 +6498,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>457849</v>
+        <v>457940</v>
       </c>
       <c r="R58" t="n">
-        <v>6901500</v>
+        <v>6901428</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6565,7 +6560,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119833909</v>
+        <v>119832322</v>
       </c>
       <c r="B59" t="n">
         <v>97930</v>
@@ -6605,10 +6600,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>458175</v>
+        <v>457900</v>
       </c>
       <c r="R59" t="n">
-        <v>6901627</v>
+        <v>6901490</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6641,6 +6636,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Stor förekomst. 60 rosetter.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6667,10 +6667,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119830940</v>
+        <v>119834066</v>
       </c>
       <c r="B60" t="n">
-        <v>91870</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6679,38 +6679,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>458107</v>
+        <v>458212</v>
       </c>
       <c r="R60" t="n">
-        <v>6901417</v>
+        <v>6901767</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119831651</v>
+        <v>119831819</v>
       </c>
       <c r="B61" t="n">
         <v>97930</v>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>457975</v>
+        <v>457796</v>
       </c>
       <c r="R61" t="n">
-        <v>6901409</v>
+        <v>6901388</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119831182</v>
+        <v>119833969</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>79131</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6883,25 +6883,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>458050</v>
+        <v>458185</v>
       </c>
       <c r="R62" t="n">
-        <v>6901340</v>
+        <v>6901645</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6973,7 +6973,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119832130</v>
+        <v>119831651</v>
       </c>
       <c r="B63" t="n">
         <v>97930</v>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457815</v>
+        <v>457975</v>
       </c>
       <c r="R63" t="n">
-        <v>6901466</v>
+        <v>6901409</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7075,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119830850</v>
+        <v>119831593</v>
       </c>
       <c r="B64" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,38 +7087,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>458090</v>
+        <v>457980</v>
       </c>
       <c r="R64" t="n">
-        <v>6901440</v>
+        <v>6901438</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7177,10 +7177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120144261</v>
+        <v>120140016</v>
       </c>
       <c r="B65" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7193,35 +7193,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7229,10 +7228,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>458441</v>
+        <v>458161</v>
       </c>
       <c r="R65" t="n">
-        <v>6901767</v>
+        <v>6901991</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7265,6 +7264,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Liggande sälg nära kalhygge.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7292,10 +7296,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120140016</v>
+        <v>120144261</v>
       </c>
       <c r="B66" t="n">
-        <v>91146</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7308,34 +7312,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7343,10 +7348,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458161</v>
+        <v>458441</v>
       </c>
       <c r="R66" t="n">
-        <v>6901991</v>
+        <v>6901767</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7379,11 +7384,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Liggande sälg nära kalhygge.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7411,7 +7411,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120306766</v>
+        <v>120306521</v>
       </c>
       <c r="B67" t="n">
         <v>97930</v>
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458277</v>
+        <v>458295</v>
       </c>
       <c r="R67" t="n">
-        <v>6901755</v>
+        <v>6901764</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7513,7 +7513,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120306592</v>
+        <v>120307076</v>
       </c>
       <c r="B68" t="n">
         <v>97930</v>
@@ -7549,14 +7549,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458290</v>
+        <v>458140</v>
       </c>
       <c r="R68" t="n">
-        <v>6901742</v>
+        <v>6901768</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7615,7 +7615,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120307076</v>
+        <v>120306914</v>
       </c>
       <c r="B69" t="n">
         <v>97930</v>
@@ -7651,17 +7651,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458140</v>
+        <v>458253</v>
       </c>
       <c r="R69" t="n">
-        <v>6901768</v>
+        <v>6901772</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120306521</v>
+        <v>120306670</v>
       </c>
       <c r="B70" t="n">
         <v>97930</v>
@@ -7757,10 +7757,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458295</v>
+        <v>458280</v>
       </c>
       <c r="R70" t="n">
-        <v>6901764</v>
+        <v>6901772</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7793,6 +7793,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7819,10 +7824,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120306257</v>
+        <v>120306650</v>
       </c>
       <c r="B71" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7831,25 +7836,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7859,10 +7864,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458154</v>
+        <v>458284</v>
       </c>
       <c r="R71" t="n">
-        <v>6901662</v>
+        <v>6901758</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7921,7 +7926,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120306650</v>
+        <v>120306846</v>
       </c>
       <c r="B72" t="n">
         <v>97930</v>
@@ -7954,17 +7959,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458284</v>
+        <v>458248</v>
       </c>
       <c r="R72" t="n">
-        <v>6901758</v>
+        <v>6901744</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -7997,6 +8011,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8023,7 +8042,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120306846</v>
+        <v>120306966</v>
       </c>
       <c r="B73" t="n">
         <v>97930</v>
@@ -8056,26 +8075,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458248</v>
+        <v>458234</v>
       </c>
       <c r="R73" t="n">
-        <v>6901744</v>
+        <v>6901764</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8108,11 +8118,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8139,10 +8144,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120306799</v>
+        <v>120306201</v>
       </c>
       <c r="B74" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8151,25 +8156,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8179,13 +8184,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>458258</v>
+        <v>458128</v>
       </c>
       <c r="R74" t="n">
-        <v>6901747</v>
+        <v>6901635</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8241,7 +8246,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120306893</v>
+        <v>120306592</v>
       </c>
       <c r="B75" t="n">
         <v>97930</v>
@@ -8281,10 +8286,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>458263</v>
+        <v>458290</v>
       </c>
       <c r="R75" t="n">
-        <v>6901765</v>
+        <v>6901742</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8343,7 +8348,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120306914</v>
+        <v>120306992</v>
       </c>
       <c r="B76" t="n">
         <v>97930</v>
@@ -8379,17 +8384,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458253</v>
+        <v>458181</v>
       </c>
       <c r="R76" t="n">
-        <v>6901772</v>
+        <v>6901756</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8445,7 +8450,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120306966</v>
+        <v>120306893</v>
       </c>
       <c r="B77" t="n">
         <v>97930</v>
@@ -8485,10 +8490,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458234</v>
+        <v>458263</v>
       </c>
       <c r="R77" t="n">
-        <v>6901764</v>
+        <v>6901765</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8547,7 +8552,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120306670</v>
+        <v>120306766</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -8587,10 +8592,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458280</v>
+        <v>458277</v>
       </c>
       <c r="R78" t="n">
-        <v>6901772</v>
+        <v>6901755</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8623,11 +8628,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8654,10 +8654,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306201</v>
+        <v>120306901</v>
       </c>
       <c r="B79" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8666,25 +8666,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8694,13 +8694,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458128</v>
+        <v>458271</v>
       </c>
       <c r="R79" t="n">
-        <v>6901635</v>
+        <v>6901756</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120306511</v>
+        <v>120306799</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458306</v>
+        <v>458258</v>
       </c>
       <c r="R80" t="n">
-        <v>6901772</v>
+        <v>6901747</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8858,10 +8858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120306992</v>
+        <v>120306257</v>
       </c>
       <c r="B81" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8870,38 +8870,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458181</v>
+        <v>458154</v>
       </c>
       <c r="R81" t="n">
-        <v>6901756</v>
+        <v>6901662</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8960,7 +8960,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120306901</v>
+        <v>120306511</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458271</v>
+        <v>458306</v>
       </c>
       <c r="R82" t="n">
-        <v>6901756</v>
+        <v>6901772</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -3189,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119830906</v>
+        <v>119834306</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,41 +3201,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>458090</v>
+        <v>458116</v>
       </c>
       <c r="R26" t="n">
-        <v>6901440</v>
+        <v>6901806</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119834306</v>
+        <v>119830906</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3303,41 +3303,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>458116</v>
+        <v>458090</v>
       </c>
       <c r="R27" t="n">
-        <v>6901806</v>
+        <v>6901440</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -5948,10 +5948,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119832197</v>
+        <v>119832531</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5960,25 +5960,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>457849</v>
+        <v>457981</v>
       </c>
       <c r="R53" t="n">
-        <v>6901500</v>
+        <v>6901523</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6050,7 +6050,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119831955</v>
+        <v>119831182</v>
       </c>
       <c r="B54" t="n">
         <v>97930</v>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>457798</v>
+        <v>458050</v>
       </c>
       <c r="R54" t="n">
-        <v>6901409</v>
+        <v>6901340</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119832531</v>
+        <v>119831955</v>
       </c>
       <c r="B55" t="n">
         <v>97930</v>
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>457981</v>
+        <v>457798</v>
       </c>
       <c r="R55" t="n">
-        <v>6901523</v>
+        <v>6901409</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119831182</v>
+        <v>119832197</v>
       </c>
       <c r="B57" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6368,25 +6368,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>458050</v>
+        <v>457849</v>
       </c>
       <c r="R57" t="n">
-        <v>6901340</v>
+        <v>6901500</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6973,10 +6973,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119831651</v>
+        <v>119831593</v>
       </c>
       <c r="B63" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6985,25 +6985,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>457975</v>
+        <v>457980</v>
       </c>
       <c r="R63" t="n">
-        <v>6901409</v>
+        <v>6901438</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7075,10 +7075,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119831593</v>
+        <v>119831651</v>
       </c>
       <c r="B64" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,25 +7087,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>457980</v>
+        <v>457975</v>
       </c>
       <c r="R64" t="n">
-        <v>6901438</v>
+        <v>6901409</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7177,10 +7177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120140016</v>
+        <v>120144261</v>
       </c>
       <c r="B65" t="n">
-        <v>91146</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7193,34 +7193,35 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7228,10 +7229,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>458161</v>
+        <v>458441</v>
       </c>
       <c r="R65" t="n">
-        <v>6901991</v>
+        <v>6901767</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7264,11 +7265,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Liggande sälg nära kalhygge.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7296,10 +7292,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120144261</v>
+        <v>120140016</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7312,35 +7308,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7348,10 +7343,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>458441</v>
+        <v>458161</v>
       </c>
       <c r="R66" t="n">
-        <v>6901767</v>
+        <v>6901991</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7384,6 +7379,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Liggande sälg nära kalhygge.</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120306521</v>
+        <v>120306650</v>
       </c>
       <c r="B67" t="n">
         <v>97930</v>
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458295</v>
+        <v>458284</v>
       </c>
       <c r="R67" t="n">
-        <v>6901764</v>
+        <v>6901758</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7513,7 +7513,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120307076</v>
+        <v>120306592</v>
       </c>
       <c r="B68" t="n">
         <v>97930</v>
@@ -7549,14 +7549,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458140</v>
+        <v>458290</v>
       </c>
       <c r="R68" t="n">
-        <v>6901768</v>
+        <v>6901742</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7615,10 +7615,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120306914</v>
+        <v>120306257</v>
       </c>
       <c r="B69" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7627,25 +7627,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458253</v>
+        <v>458154</v>
       </c>
       <c r="R69" t="n">
-        <v>6901772</v>
+        <v>6901662</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120306670</v>
+        <v>120306846</v>
       </c>
       <c r="B70" t="n">
         <v>97930</v>
@@ -7750,17 +7750,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458280</v>
+        <v>458248</v>
       </c>
       <c r="R70" t="n">
-        <v>6901772</v>
+        <v>6901744</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7797,7 +7806,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Tät förekomst inom avverkningsanmälan.</t>
+          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7824,7 +7833,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120306650</v>
+        <v>120306901</v>
       </c>
       <c r="B71" t="n">
         <v>97930</v>
@@ -7864,10 +7873,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458284</v>
+        <v>458271</v>
       </c>
       <c r="R71" t="n">
-        <v>6901758</v>
+        <v>6901756</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7926,10 +7935,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120306846</v>
+        <v>120306201</v>
       </c>
       <c r="B72" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7938,50 +7947,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458248</v>
+        <v>458128</v>
       </c>
       <c r="R72" t="n">
-        <v>6901744</v>
+        <v>6901635</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8011,11 +8011,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8144,10 +8139,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120306201</v>
+        <v>120306766</v>
       </c>
       <c r="B74" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8156,25 +8151,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8184,13 +8179,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>458128</v>
+        <v>458277</v>
       </c>
       <c r="R74" t="n">
-        <v>6901635</v>
+        <v>6901755</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8246,7 +8241,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120306592</v>
+        <v>120306670</v>
       </c>
       <c r="B75" t="n">
         <v>97930</v>
@@ -8286,10 +8281,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>458290</v>
+        <v>458280</v>
       </c>
       <c r="R75" t="n">
-        <v>6901742</v>
+        <v>6901772</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8322,6 +8317,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,7 +8348,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120306992</v>
+        <v>120306799</v>
       </c>
       <c r="B76" t="n">
         <v>97930</v>
@@ -8384,14 +8384,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458181</v>
+        <v>458258</v>
       </c>
       <c r="R76" t="n">
-        <v>6901756</v>
+        <v>6901747</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120306766</v>
+        <v>120306914</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458277</v>
+        <v>458253</v>
       </c>
       <c r="R78" t="n">
-        <v>6901755</v>
+        <v>6901772</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306901</v>
+        <v>120306521</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458271</v>
+        <v>458295</v>
       </c>
       <c r="R79" t="n">
-        <v>6901756</v>
+        <v>6901764</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8756,7 +8756,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120306799</v>
+        <v>120307076</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -8792,14 +8792,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458258</v>
+        <v>458140</v>
       </c>
       <c r="R80" t="n">
-        <v>6901747</v>
+        <v>6901768</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8858,10 +8858,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120306257</v>
+        <v>120306511</v>
       </c>
       <c r="B81" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8870,25 +8870,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458154</v>
+        <v>458306</v>
       </c>
       <c r="R81" t="n">
-        <v>6901662</v>
+        <v>6901772</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8960,7 +8960,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120306511</v>
+        <v>120306992</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -8996,14 +8996,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458306</v>
+        <v>458181</v>
       </c>
       <c r="R82" t="n">
-        <v>6901772</v>
+        <v>6901756</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120306650</v>
+        <v>120306670</v>
       </c>
       <c r="B67" t="n">
         <v>97930</v>
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458284</v>
+        <v>458280</v>
       </c>
       <c r="R67" t="n">
-        <v>6901758</v>
+        <v>6901772</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7487,6 +7487,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7513,7 +7518,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120306592</v>
+        <v>120306901</v>
       </c>
       <c r="B68" t="n">
         <v>97930</v>
@@ -7553,10 +7558,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458290</v>
+        <v>458271</v>
       </c>
       <c r="R68" t="n">
-        <v>6901742</v>
+        <v>6901756</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7615,10 +7620,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120306257</v>
+        <v>120306846</v>
       </c>
       <c r="B69" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7627,38 +7632,47 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458154</v>
+        <v>458248</v>
       </c>
       <c r="R69" t="n">
-        <v>6901662</v>
+        <v>6901744</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7691,6 +7705,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7717,7 +7736,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120306846</v>
+        <v>120306893</v>
       </c>
       <c r="B70" t="n">
         <v>97930</v>
@@ -7750,26 +7769,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458248</v>
+        <v>458263</v>
       </c>
       <c r="R70" t="n">
-        <v>6901744</v>
+        <v>6901765</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7802,11 +7812,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7833,7 +7838,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120306901</v>
+        <v>120307076</v>
       </c>
       <c r="B71" t="n">
         <v>97930</v>
@@ -7869,14 +7874,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458271</v>
+        <v>458140</v>
       </c>
       <c r="R71" t="n">
-        <v>6901756</v>
+        <v>6901768</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7935,10 +7940,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120306201</v>
+        <v>120306521</v>
       </c>
       <c r="B72" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7947,25 +7952,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7975,13 +7980,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458128</v>
+        <v>458295</v>
       </c>
       <c r="R72" t="n">
-        <v>6901635</v>
+        <v>6901764</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8037,10 +8042,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120306966</v>
+        <v>120306201</v>
       </c>
       <c r="B73" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8049,25 +8054,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8077,13 +8082,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458234</v>
+        <v>458128</v>
       </c>
       <c r="R73" t="n">
-        <v>6901764</v>
+        <v>6901635</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8139,7 +8144,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120306766</v>
+        <v>120306992</v>
       </c>
       <c r="B74" t="n">
         <v>97930</v>
@@ -8175,14 +8180,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>458277</v>
+        <v>458181</v>
       </c>
       <c r="R74" t="n">
-        <v>6901755</v>
+        <v>6901756</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8241,7 +8246,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120306670</v>
+        <v>120306650</v>
       </c>
       <c r="B75" t="n">
         <v>97930</v>
@@ -8281,10 +8286,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>458280</v>
+        <v>458284</v>
       </c>
       <c r="R75" t="n">
-        <v>6901772</v>
+        <v>6901758</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8317,11 +8322,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,7 +8348,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120306799</v>
+        <v>120306914</v>
       </c>
       <c r="B76" t="n">
         <v>97930</v>
@@ -8388,13 +8388,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458258</v>
+        <v>458253</v>
       </c>
       <c r="R76" t="n">
-        <v>6901747</v>
+        <v>6901772</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120306893</v>
+        <v>120306966</v>
       </c>
       <c r="B77" t="n">
         <v>97930</v>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458263</v>
+        <v>458234</v>
       </c>
       <c r="R77" t="n">
-        <v>6901765</v>
+        <v>6901764</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120306914</v>
+        <v>120306592</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458253</v>
+        <v>458290</v>
       </c>
       <c r="R78" t="n">
-        <v>6901772</v>
+        <v>6901742</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306521</v>
+        <v>120306799</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458295</v>
+        <v>458258</v>
       </c>
       <c r="R79" t="n">
-        <v>6901764</v>
+        <v>6901747</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8756,10 +8756,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120307076</v>
+        <v>120306257</v>
       </c>
       <c r="B80" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8768,38 +8768,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458140</v>
+        <v>458154</v>
       </c>
       <c r="R80" t="n">
-        <v>6901768</v>
+        <v>6901662</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120306511</v>
+        <v>120306766</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458306</v>
+        <v>458277</v>
       </c>
       <c r="R81" t="n">
-        <v>6901772</v>
+        <v>6901755</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8960,7 +8960,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120306992</v>
+        <v>120306511</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -8996,14 +8996,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458181</v>
+        <v>458306</v>
       </c>
       <c r="R82" t="n">
-        <v>6901756</v>
+        <v>6901772</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -8756,10 +8756,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120306257</v>
+        <v>120306766</v>
       </c>
       <c r="B80" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8768,25 +8768,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458154</v>
+        <v>458277</v>
       </c>
       <c r="R80" t="n">
-        <v>6901662</v>
+        <v>6901755</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120306766</v>
+        <v>120306511</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458277</v>
+        <v>458306</v>
       </c>
       <c r="R81" t="n">
-        <v>6901755</v>
+        <v>6901772</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8960,10 +8960,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120306511</v>
+        <v>120306257</v>
       </c>
       <c r="B82" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8972,25 +8972,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458306</v>
+        <v>458154</v>
       </c>
       <c r="R82" t="n">
-        <v>6901772</v>
+        <v>6901662</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120306670</v>
+        <v>120306846</v>
       </c>
       <c r="B67" t="n">
         <v>97930</v>
@@ -7444,17 +7444,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458280</v>
+        <v>458248</v>
       </c>
       <c r="R67" t="n">
-        <v>6901772</v>
+        <v>6901744</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7491,7 +7500,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Tät förekomst inom avverkningsanmälan.</t>
+          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7518,7 +7527,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120306901</v>
+        <v>120306511</v>
       </c>
       <c r="B68" t="n">
         <v>97930</v>
@@ -7558,10 +7567,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458271</v>
+        <v>458306</v>
       </c>
       <c r="R68" t="n">
-        <v>6901756</v>
+        <v>6901772</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7620,7 +7629,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120306846</v>
+        <v>120306799</v>
       </c>
       <c r="B69" t="n">
         <v>97930</v>
@@ -7653,26 +7662,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458248</v>
+        <v>458258</v>
       </c>
       <c r="R69" t="n">
-        <v>6901744</v>
+        <v>6901747</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7705,11 +7705,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7736,10 +7731,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120306893</v>
+        <v>120306257</v>
       </c>
       <c r="B70" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7748,25 +7743,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7776,10 +7771,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458263</v>
+        <v>458154</v>
       </c>
       <c r="R70" t="n">
-        <v>6901765</v>
+        <v>6901662</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7838,7 +7833,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120307076</v>
+        <v>120306893</v>
       </c>
       <c r="B71" t="n">
         <v>97930</v>
@@ -7874,14 +7869,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458140</v>
+        <v>458263</v>
       </c>
       <c r="R71" t="n">
-        <v>6901768</v>
+        <v>6901765</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7940,10 +7935,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120306521</v>
+        <v>120306201</v>
       </c>
       <c r="B72" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7952,25 +7947,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7980,13 +7975,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458295</v>
+        <v>458128</v>
       </c>
       <c r="R72" t="n">
-        <v>6901764</v>
+        <v>6901635</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8042,10 +8037,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120306201</v>
+        <v>120306992</v>
       </c>
       <c r="B73" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8054,41 +8049,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458128</v>
+        <v>458181</v>
       </c>
       <c r="R73" t="n">
-        <v>6901635</v>
+        <v>6901756</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8144,7 +8139,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120306992</v>
+        <v>120307076</v>
       </c>
       <c r="B74" t="n">
         <v>97930</v>
@@ -8184,10 +8179,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>458181</v>
+        <v>458140</v>
       </c>
       <c r="R74" t="n">
-        <v>6901756</v>
+        <v>6901768</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8246,7 +8241,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120306650</v>
+        <v>120306670</v>
       </c>
       <c r="B75" t="n">
         <v>97930</v>
@@ -8286,10 +8281,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>458284</v>
+        <v>458280</v>
       </c>
       <c r="R75" t="n">
-        <v>6901758</v>
+        <v>6901772</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8322,6 +8317,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,7 +8348,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120306914</v>
+        <v>120306966</v>
       </c>
       <c r="B76" t="n">
         <v>97930</v>
@@ -8388,13 +8388,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458253</v>
+        <v>458234</v>
       </c>
       <c r="R76" t="n">
-        <v>6901772</v>
+        <v>6901764</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120306966</v>
+        <v>120306901</v>
       </c>
       <c r="B77" t="n">
         <v>97930</v>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458234</v>
+        <v>458271</v>
       </c>
       <c r="R77" t="n">
-        <v>6901764</v>
+        <v>6901756</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120306592</v>
+        <v>120306914</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458290</v>
+        <v>458253</v>
       </c>
       <c r="R78" t="n">
-        <v>6901742</v>
+        <v>6901772</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306799</v>
+        <v>120306521</v>
       </c>
       <c r="B79" t="n">
         <v>97930</v>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458258</v>
+        <v>458295</v>
       </c>
       <c r="R79" t="n">
-        <v>6901747</v>
+        <v>6901764</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120306511</v>
+        <v>120306650</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458306</v>
+        <v>458284</v>
       </c>
       <c r="R81" t="n">
-        <v>6901772</v>
+        <v>6901758</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8960,10 +8960,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120306257</v>
+        <v>120306592</v>
       </c>
       <c r="B82" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8972,25 +8972,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458154</v>
+        <v>458290</v>
       </c>
       <c r="R82" t="n">
-        <v>6901662</v>
+        <v>6901742</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -7411,7 +7411,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120306846</v>
+        <v>120306670</v>
       </c>
       <c r="B67" t="n">
         <v>97930</v>
@@ -7444,26 +7444,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>458248</v>
+        <v>458280</v>
       </c>
       <c r="R67" t="n">
-        <v>6901744</v>
+        <v>6901772</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7500,7 +7491,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Tät matta av kraftiga rosetter.</t>
+          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,7 +7518,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120306511</v>
+        <v>120306901</v>
       </c>
       <c r="B68" t="n">
         <v>97930</v>
@@ -7567,10 +7558,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>458306</v>
+        <v>458271</v>
       </c>
       <c r="R68" t="n">
-        <v>6901772</v>
+        <v>6901756</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7629,7 +7620,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120306799</v>
+        <v>120306846</v>
       </c>
       <c r="B69" t="n">
         <v>97930</v>
@@ -7662,17 +7653,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>458258</v>
+        <v>458248</v>
       </c>
       <c r="R69" t="n">
-        <v>6901747</v>
+        <v>6901744</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7705,6 +7705,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Tät matta av kraftiga rosetter.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,10 +7736,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120306257</v>
+        <v>120306992</v>
       </c>
       <c r="B70" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7743,38 +7748,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>458154</v>
+        <v>458181</v>
       </c>
       <c r="R70" t="n">
-        <v>6901662</v>
+        <v>6901756</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7833,7 +7838,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120306893</v>
+        <v>120306592</v>
       </c>
       <c r="B71" t="n">
         <v>97930</v>
@@ -7873,10 +7878,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>458263</v>
+        <v>458290</v>
       </c>
       <c r="R71" t="n">
-        <v>6901765</v>
+        <v>6901742</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7935,10 +7940,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120306201</v>
+        <v>120306650</v>
       </c>
       <c r="B72" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7947,25 +7952,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7975,13 +7980,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>458128</v>
+        <v>458284</v>
       </c>
       <c r="R72" t="n">
-        <v>6901635</v>
+        <v>6901758</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8037,7 +8042,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120306992</v>
+        <v>120306766</v>
       </c>
       <c r="B73" t="n">
         <v>97930</v>
@@ -8073,14 +8078,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>458181</v>
+        <v>458277</v>
       </c>
       <c r="R73" t="n">
-        <v>6901756</v>
+        <v>6901755</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8139,7 +8144,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120307076</v>
+        <v>120306799</v>
       </c>
       <c r="B74" t="n">
         <v>97930</v>
@@ -8175,14 +8180,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>458140</v>
+        <v>458258</v>
       </c>
       <c r="R74" t="n">
-        <v>6901768</v>
+        <v>6901747</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8241,10 +8246,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120306670</v>
+        <v>120306201</v>
       </c>
       <c r="B75" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8253,25 +8258,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8281,13 +8286,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>458280</v>
+        <v>458128</v>
       </c>
       <c r="R75" t="n">
-        <v>6901772</v>
+        <v>6901635</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8317,11 +8322,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Tät förekomst inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,7 +8348,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120306966</v>
+        <v>120307076</v>
       </c>
       <c r="B76" t="n">
         <v>97930</v>
@@ -8384,14 +8384,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>458234</v>
+        <v>458140</v>
       </c>
       <c r="R76" t="n">
-        <v>6901764</v>
+        <v>6901768</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120306901</v>
+        <v>120306511</v>
       </c>
       <c r="B77" t="n">
         <v>97930</v>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>458271</v>
+        <v>458306</v>
       </c>
       <c r="R77" t="n">
-        <v>6901756</v>
+        <v>6901772</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120306914</v>
+        <v>120306893</v>
       </c>
       <c r="B78" t="n">
         <v>97930</v>
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>458253</v>
+        <v>458263</v>
       </c>
       <c r="R78" t="n">
-        <v>6901772</v>
+        <v>6901765</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8654,10 +8654,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120306521</v>
+        <v>120306257</v>
       </c>
       <c r="B79" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8666,25 +8666,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>458295</v>
+        <v>458154</v>
       </c>
       <c r="R79" t="n">
-        <v>6901764</v>
+        <v>6901662</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8756,7 +8756,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120306766</v>
+        <v>120306521</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -8796,10 +8796,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>458277</v>
+        <v>458295</v>
       </c>
       <c r="R80" t="n">
-        <v>6901755</v>
+        <v>6901764</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120306650</v>
+        <v>120306914</v>
       </c>
       <c r="B81" t="n">
         <v>97930</v>
@@ -8898,13 +8898,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>458284</v>
+        <v>458253</v>
       </c>
       <c r="R81" t="n">
-        <v>6901758</v>
+        <v>6901772</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120306592</v>
+        <v>120306966</v>
       </c>
       <c r="B82" t="n">
         <v>97930</v>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>458290</v>
+        <v>458234</v>
       </c>
       <c r="R82" t="n">
-        <v>6901742</v>
+        <v>6901764</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -8144,10 +8144,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120306799</v>
+        <v>120306201</v>
       </c>
       <c r="B74" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8156,25 +8156,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8184,13 +8184,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>458258</v>
+        <v>458128</v>
       </c>
       <c r="R74" t="n">
-        <v>6901747</v>
+        <v>6901635</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8246,10 +8246,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120306201</v>
+        <v>120306799</v>
       </c>
       <c r="B75" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8258,25 +8258,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8286,13 +8286,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>458128</v>
+        <v>458258</v>
       </c>
       <c r="R75" t="n">
-        <v>6901635</v>
+        <v>6901747</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9060,6 +9060,3596 @@
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125633679</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>458175</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6901690</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125635066</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98186</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>458157</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6901685</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125634700</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>458148</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6901749</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125634932</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>458109</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6901719</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125633234</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>458228</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6901676</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>125633201</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>458238</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6901671</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125634843</v>
+      </c>
+      <c r="B89" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>458100</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6901727</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125632850</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>458285</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6901673</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125633982</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>458164</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6901708</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125632589</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>458272</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6901664</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>125633222</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79932</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>458233</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6901669</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>125633316</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>458200</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6901685</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>125634596</v>
+      </c>
+      <c r="B95" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>458160</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6901743</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>125632818</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>458284</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6901672</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>125632993</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>458270</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6901687</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>125633262</v>
+      </c>
+      <c r="B98" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>458200</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6901673</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>125634677</v>
+      </c>
+      <c r="B99" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>458159</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6901759</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>125634527</v>
+      </c>
+      <c r="B100" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>458171</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6901736</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>125634627</v>
+      </c>
+      <c r="B101" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>458166</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6901741</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>125634763</v>
+      </c>
+      <c r="B102" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>458117</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6901750</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>125632572</v>
+      </c>
+      <c r="B103" t="n">
+        <v>98290</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>458275</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6901664</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>10 exemplar.</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>125634785</v>
+      </c>
+      <c r="B104" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>458123</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6901748</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>125633081</v>
+      </c>
+      <c r="B105" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>458252</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6901694</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>125633245</v>
+      </c>
+      <c r="B106" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>458224</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6901685</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>125634921</v>
+      </c>
+      <c r="B107" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>458109</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6901715</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>125633306</v>
+      </c>
+      <c r="B108" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>458200</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6901697</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>125633045</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78684</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>458247</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6901689</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>125632950</v>
+      </c>
+      <c r="B110" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>458282</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6901706</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>125633151</v>
+      </c>
+      <c r="B111" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>458249</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6901668</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>50 exemplar.</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>125632670</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>458288</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6901663</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>125634585</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>458155</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6901741</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>125634050</v>
+      </c>
+      <c r="B114" t="n">
+        <v>98290</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>458161</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6901715</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>125635101</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>458152</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6901693</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>125633359</v>
+      </c>
+      <c r="B116" t="n">
+        <v>98290</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>458174</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6901705</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>125632788</v>
+      </c>
+      <c r="B117" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>458290</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6901669</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Vanlig i området.</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9373,7 +9373,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125634932</v>
+        <v>125633234</v>
       </c>
       <c r="B86" t="n">
         <v>98269</v>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458109</v>
+        <v>458228</v>
       </c>
       <c r="R86" t="n">
-        <v>6901719</v>
+        <v>6901676</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9475,7 +9475,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125633234</v>
+        <v>125634932</v>
       </c>
       <c r="B87" t="n">
         <v>98269</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>458228</v>
+        <v>458109</v>
       </c>
       <c r="R87" t="n">
-        <v>6901676</v>
+        <v>6901719</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125633201</v>
+        <v>125634843</v>
       </c>
       <c r="B88" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9589,25 +9589,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458238</v>
+        <v>458100</v>
       </c>
       <c r="R88" t="n">
-        <v>6901671</v>
+        <v>6901727</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9679,10 +9679,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125634843</v>
+        <v>125633201</v>
       </c>
       <c r="B89" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9691,25 +9691,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9719,10 +9719,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458100</v>
+        <v>458238</v>
       </c>
       <c r="R89" t="n">
-        <v>6901727</v>
+        <v>6901671</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10495,10 +10495,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125632993</v>
+        <v>125634677</v>
       </c>
       <c r="B97" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10507,25 +10507,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10535,10 +10535,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458270</v>
+        <v>458159</v>
       </c>
       <c r="R97" t="n">
-        <v>6901687</v>
+        <v>6901759</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10597,7 +10597,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125633262</v>
+        <v>125632993</v>
       </c>
       <c r="B98" t="n">
         <v>98269</v>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>458200</v>
+        <v>458270</v>
       </c>
       <c r="R98" t="n">
-        <v>6901673</v>
+        <v>6901687</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10699,10 +10699,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125634677</v>
+        <v>125633262</v>
       </c>
       <c r="B99" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10711,25 +10711,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10739,10 +10739,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458159</v>
+        <v>458200</v>
       </c>
       <c r="R99" t="n">
-        <v>6901759</v>
+        <v>6901673</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9062,15 +9062,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125633679</v>
+        <v>125632589</v>
       </c>
       <c r="B83" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9102,10 +9097,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>458175</v>
+        <v>458272</v>
       </c>
       <c r="R83" t="n">
-        <v>6901690</v>
+        <v>6901664</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9138,11 +9133,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9169,37 +9159,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125635066</v>
+        <v>125633316</v>
       </c>
       <c r="B84" t="n">
-        <v>98186</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9209,7 +9194,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>458157</v>
+        <v>458200</v>
       </c>
       <c r="R84" t="n">
         <v>6901685</v>
@@ -9271,37 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634700</v>
+        <v>125634843</v>
       </c>
       <c r="B85" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9311,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458148</v>
+        <v>458100</v>
       </c>
       <c r="R85" t="n">
-        <v>6901749</v>
+        <v>6901727</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9373,37 +9353,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125633234</v>
+        <v>125634921</v>
       </c>
       <c r="B86" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9413,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458228</v>
+        <v>458109</v>
       </c>
       <c r="R86" t="n">
-        <v>6901676</v>
+        <v>6901715</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9475,15 +9450,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125634932</v>
+        <v>125634700</v>
       </c>
       <c r="B87" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9515,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>458109</v>
+        <v>458148</v>
       </c>
       <c r="R87" t="n">
-        <v>6901719</v>
+        <v>6901749</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9577,37 +9547,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125634843</v>
+        <v>125634527</v>
       </c>
       <c r="B88" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9617,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458100</v>
+        <v>458171</v>
       </c>
       <c r="R88" t="n">
-        <v>6901727</v>
+        <v>6901736</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9679,15 +9644,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125633201</v>
+        <v>125632818</v>
       </c>
       <c r="B89" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9719,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458238</v>
+        <v>458284</v>
       </c>
       <c r="R89" t="n">
-        <v>6901671</v>
+        <v>6901672</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9781,15 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125632850</v>
+        <v>125634585</v>
       </c>
       <c r="B90" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9821,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458285</v>
+        <v>458155</v>
       </c>
       <c r="R90" t="n">
-        <v>6901673</v>
+        <v>6901741</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9883,37 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125633982</v>
+        <v>125635066</v>
       </c>
       <c r="B91" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98241</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9923,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458164</v>
+        <v>458157</v>
       </c>
       <c r="R91" t="n">
-        <v>6901708</v>
+        <v>6901685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9985,37 +9935,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125632589</v>
+        <v>125633222</v>
       </c>
       <c r="B92" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10025,10 +9970,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>458272</v>
+        <v>458233</v>
       </c>
       <c r="R92" t="n">
-        <v>6901664</v>
+        <v>6901669</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10087,37 +10032,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633222</v>
+        <v>125633679</v>
       </c>
       <c r="B93" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10127,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458233</v>
+        <v>458175</v>
       </c>
       <c r="R93" t="n">
-        <v>6901669</v>
+        <v>6901690</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10163,6 +10103,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10189,15 +10134,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125633316</v>
+        <v>125632850</v>
       </c>
       <c r="B94" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10229,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458200</v>
+        <v>458285</v>
       </c>
       <c r="R94" t="n">
-        <v>6901685</v>
+        <v>6901673</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10291,37 +10231,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125634596</v>
+        <v>125633245</v>
       </c>
       <c r="B95" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10331,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458160</v>
+        <v>458224</v>
       </c>
       <c r="R95" t="n">
-        <v>6901743</v>
+        <v>6901685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10393,15 +10328,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632818</v>
+        <v>125632993</v>
       </c>
       <c r="B96" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10433,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>458284</v>
+        <v>458270</v>
       </c>
       <c r="R96" t="n">
-        <v>6901672</v>
+        <v>6901687</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10495,37 +10425,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125634677</v>
+        <v>125632788</v>
       </c>
       <c r="B97" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10535,10 +10460,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458159</v>
+        <v>458290</v>
       </c>
       <c r="R97" t="n">
-        <v>6901759</v>
+        <v>6901669</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10571,6 +10496,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10597,37 +10527,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632993</v>
+        <v>125634050</v>
       </c>
       <c r="B98" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10637,10 +10562,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>458270</v>
+        <v>458161</v>
       </c>
       <c r="R98" t="n">
-        <v>6901687</v>
+        <v>6901715</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10699,15 +10624,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125633262</v>
+        <v>125633306</v>
       </c>
       <c r="B99" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10742,7 +10662,7 @@
         <v>458200</v>
       </c>
       <c r="R99" t="n">
-        <v>6901673</v>
+        <v>6901697</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10801,37 +10721,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125634527</v>
+        <v>125632572</v>
       </c>
       <c r="B100" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10841,10 +10756,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>458171</v>
+        <v>458275</v>
       </c>
       <c r="R100" t="n">
-        <v>6901736</v>
+        <v>6901664</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10877,6 +10792,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10903,37 +10823,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125634627</v>
+        <v>125633262</v>
       </c>
       <c r="B101" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10943,10 +10858,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458166</v>
+        <v>458200</v>
       </c>
       <c r="R101" t="n">
-        <v>6901741</v>
+        <v>6901673</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11005,37 +10920,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125634763</v>
+        <v>125633045</v>
       </c>
       <c r="B102" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11045,10 +10955,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458117</v>
+        <v>458247</v>
       </c>
       <c r="R102" t="n">
-        <v>6901750</v>
+        <v>6901689</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11107,37 +11017,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632572</v>
+        <v>125634677</v>
       </c>
       <c r="B103" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11147,10 +11052,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458275</v>
+        <v>458159</v>
       </c>
       <c r="R103" t="n">
-        <v>6901664</v>
+        <v>6901759</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11183,11 +11088,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11217,12 +11117,7 @@
         <v>125634785</v>
       </c>
       <c r="B104" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11316,15 +11211,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125633081</v>
+        <v>125632670</v>
       </c>
       <c r="B105" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11356,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458252</v>
+        <v>458288</v>
       </c>
       <c r="R105" t="n">
-        <v>6901694</v>
+        <v>6901663</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11418,15 +11308,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125633245</v>
+        <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11458,10 +11343,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>458224</v>
+        <v>458164</v>
       </c>
       <c r="R106" t="n">
-        <v>6901685</v>
+        <v>6901708</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11520,37 +11405,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125634921</v>
+        <v>125633234</v>
       </c>
       <c r="B107" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11560,10 +11440,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>458109</v>
+        <v>458228</v>
       </c>
       <c r="R107" t="n">
-        <v>6901715</v>
+        <v>6901676</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11622,15 +11502,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125633306</v>
+        <v>125634932</v>
       </c>
       <c r="B108" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11662,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>458200</v>
+        <v>458109</v>
       </c>
       <c r="R108" t="n">
-        <v>6901697</v>
+        <v>6901719</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11724,15 +11599,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125633045</v>
+        <v>125634596</v>
       </c>
       <c r="B109" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11740,21 +11610,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11764,10 +11634,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>458247</v>
+        <v>458160</v>
       </c>
       <c r="R109" t="n">
-        <v>6901689</v>
+        <v>6901743</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11826,37 +11696,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125632950</v>
+        <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11866,10 +11731,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458282</v>
+        <v>458174</v>
       </c>
       <c r="R110" t="n">
-        <v>6901706</v>
+        <v>6901705</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11931,12 +11796,7 @@
         <v>125633151</v>
       </c>
       <c r="B111" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12035,15 +11895,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632670</v>
+        <v>125632950</v>
       </c>
       <c r="B112" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12075,10 +11930,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458288</v>
+        <v>458282</v>
       </c>
       <c r="R112" t="n">
-        <v>6901663</v>
+        <v>6901706</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12137,15 +11992,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125634585</v>
+        <v>125633081</v>
       </c>
       <c r="B113" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12177,10 +12027,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458155</v>
+        <v>458252</v>
       </c>
       <c r="R113" t="n">
-        <v>6901741</v>
+        <v>6901694</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12239,37 +12089,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125634050</v>
+        <v>125633201</v>
       </c>
       <c r="B114" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12279,10 +12124,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458161</v>
+        <v>458238</v>
       </c>
       <c r="R114" t="n">
-        <v>6901715</v>
+        <v>6901671</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12344,12 +12189,7 @@
         <v>125635101</v>
       </c>
       <c r="B115" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12443,37 +12283,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125633359</v>
+        <v>125634627</v>
       </c>
       <c r="B116" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12483,10 +12318,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>458174</v>
+        <v>458166</v>
       </c>
       <c r="R116" t="n">
-        <v>6901705</v>
+        <v>6901741</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12545,15 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125632788</v>
+        <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12585,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>458290</v>
+        <v>458117</v>
       </c>
       <c r="R117" t="n">
-        <v>6901669</v>
+        <v>6901750</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12623,11 +12453,6 @@
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Vanlig i området.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12649,6 +12474,1894 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>125886795</v>
+      </c>
+      <c r="B118" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>458121</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6901956</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>125886362</v>
+      </c>
+      <c r="B119" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>458177</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6901895</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>125886789</v>
+      </c>
+      <c r="B120" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>458121</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6901961</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>125886858</v>
+      </c>
+      <c r="B121" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>458097</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6901952</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>125886889</v>
+      </c>
+      <c r="B122" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>458041</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6901924</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>125886605</v>
+      </c>
+      <c r="B123" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>458150</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6901939</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>125886318</v>
+      </c>
+      <c r="B124" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>458189</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6901872</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>125886385</v>
+      </c>
+      <c r="B125" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>458168</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6901896</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125886497</v>
+      </c>
+      <c r="B126" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>458166</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6901906</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125886761</v>
+      </c>
+      <c r="B127" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>458101</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6901974</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>125886459</v>
+      </c>
+      <c r="B128" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>458138</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6901895</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>125886245</v>
+      </c>
+      <c r="B129" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>458205</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6901832</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>125886409</v>
+      </c>
+      <c r="B130" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>458145</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6901874</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>125886855</v>
+      </c>
+      <c r="B131" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>458106</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6901940</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>125886879</v>
+      </c>
+      <c r="B132" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>458051</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6901935</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>125886299</v>
+      </c>
+      <c r="B133" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>458182</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6901855</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>125886532</v>
+      </c>
+      <c r="B134" t="n">
+        <v>98345</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>458151</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6901933</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>125886850</v>
+      </c>
+      <c r="B135" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>458110</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6901931</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>125886472</v>
+      </c>
+      <c r="B136" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>458146</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6901904</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9547,32 +9547,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125634527</v>
+        <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98324</v>
+        <v>98241</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458171</v>
+        <v>458157</v>
       </c>
       <c r="R88" t="n">
-        <v>6901736</v>
+        <v>6901685</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,7 +9644,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125632818</v>
+        <v>125634527</v>
       </c>
       <c r="B89" t="n">
         <v>98324</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458284</v>
+        <v>458171</v>
       </c>
       <c r="R89" t="n">
-        <v>6901672</v>
+        <v>6901736</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,7 +9741,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125634585</v>
+        <v>125632818</v>
       </c>
       <c r="B90" t="n">
         <v>98324</v>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458155</v>
+        <v>458284</v>
       </c>
       <c r="R90" t="n">
-        <v>6901741</v>
+        <v>6901672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125635066</v>
+        <v>125634585</v>
       </c>
       <c r="B91" t="n">
-        <v>98241</v>
+        <v>98324</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458157</v>
+        <v>458155</v>
       </c>
       <c r="R91" t="n">
-        <v>6901685</v>
+        <v>6901741</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10328,32 +10328,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632993</v>
+        <v>125634050</v>
       </c>
       <c r="B96" t="n">
-        <v>98324</v>
+        <v>98345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>458270</v>
+        <v>458161</v>
       </c>
       <c r="R96" t="n">
-        <v>6901687</v>
+        <v>6901715</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10425,7 +10425,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125632788</v>
+        <v>125632993</v>
       </c>
       <c r="B97" t="n">
         <v>98324</v>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458290</v>
+        <v>458270</v>
       </c>
       <c r="R97" t="n">
-        <v>6901669</v>
+        <v>6901687</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10496,11 +10496,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10527,32 +10522,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125634050</v>
+        <v>125632788</v>
       </c>
       <c r="B98" t="n">
-        <v>98345</v>
+        <v>98324</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>458161</v>
+        <v>458290</v>
       </c>
       <c r="R98" t="n">
-        <v>6901715</v>
+        <v>6901669</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10598,6 +10593,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10823,32 +10823,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125633262</v>
+        <v>125633045</v>
       </c>
       <c r="B101" t="n">
-        <v>98324</v>
+        <v>78726</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458200</v>
+        <v>458247</v>
       </c>
       <c r="R101" t="n">
-        <v>6901673</v>
+        <v>6901689</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125633045</v>
+        <v>125633262</v>
       </c>
       <c r="B102" t="n">
-        <v>78726</v>
+        <v>98324</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458247</v>
+        <v>458200</v>
       </c>
       <c r="R102" t="n">
-        <v>6901689</v>
+        <v>6901673</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9065,7 +9065,7 @@
         <v>125632589</v>
       </c>
       <c r="B83" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>125633316</v>
       </c>
       <c r="B84" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>125634700</v>
       </c>
       <c r="B87" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98241</v>
+        <v>98248</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>125634527</v>
       </c>
       <c r="B89" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>125632818</v>
       </c>
       <c r="B90" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>125634585</v>
       </c>
       <c r="B91" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>125633679</v>
       </c>
       <c r="B93" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>125632850</v>
       </c>
       <c r="B94" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>125633245</v>
       </c>
       <c r="B95" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10328,32 +10328,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125634050</v>
+        <v>125632993</v>
       </c>
       <c r="B96" t="n">
-        <v>98345</v>
+        <v>98331</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>458161</v>
+        <v>458270</v>
       </c>
       <c r="R96" t="n">
-        <v>6901715</v>
+        <v>6901687</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125632993</v>
+        <v>125632788</v>
       </c>
       <c r="B97" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458270</v>
+        <v>458290</v>
       </c>
       <c r="R97" t="n">
-        <v>6901687</v>
+        <v>6901669</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10496,6 +10496,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10522,32 +10527,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632788</v>
+        <v>125634050</v>
       </c>
       <c r="B98" t="n">
-        <v>98324</v>
+        <v>98352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10557,10 +10562,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>458290</v>
+        <v>458161</v>
       </c>
       <c r="R98" t="n">
-        <v>6901669</v>
+        <v>6901715</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10593,11 +10598,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10627,7 +10627,7 @@
         <v>125633306</v>
       </c>
       <c r="B99" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>125632572</v>
       </c>
       <c r="B100" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10823,32 +10823,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125633045</v>
+        <v>125633262</v>
       </c>
       <c r="B101" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458247</v>
+        <v>458200</v>
       </c>
       <c r="R101" t="n">
-        <v>6901689</v>
+        <v>6901673</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125633262</v>
+        <v>125633045</v>
       </c>
       <c r="B102" t="n">
-        <v>98324</v>
+        <v>78726</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458200</v>
+        <v>458247</v>
       </c>
       <c r="R102" t="n">
-        <v>6901673</v>
+        <v>6901689</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11017,32 +11017,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125634677</v>
+        <v>125632670</v>
       </c>
       <c r="B103" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458159</v>
+        <v>458288</v>
       </c>
       <c r="R103" t="n">
-        <v>6901759</v>
+        <v>6901663</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125634785</v>
+        <v>125634677</v>
       </c>
       <c r="B104" t="n">
         <v>80070</v>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458123</v>
+        <v>458159</v>
       </c>
       <c r="R104" t="n">
-        <v>6901748</v>
+        <v>6901759</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125632670</v>
+        <v>125634785</v>
       </c>
       <c r="B105" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458288</v>
+        <v>458123</v>
       </c>
       <c r="R105" t="n">
-        <v>6901663</v>
+        <v>6901748</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>125633234</v>
       </c>
       <c r="B107" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>125634932</v>
       </c>
       <c r="B108" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11599,32 +11599,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125634596</v>
+        <v>125633359</v>
       </c>
       <c r="B109" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>458160</v>
+        <v>458174</v>
       </c>
       <c r="R109" t="n">
-        <v>6901743</v>
+        <v>6901705</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11696,32 +11696,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125633359</v>
+        <v>125634596</v>
       </c>
       <c r="B110" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458174</v>
+        <v>458160</v>
       </c>
       <c r="R110" t="n">
-        <v>6901705</v>
+        <v>6901743</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11796,7 +11796,7 @@
         <v>125633151</v>
       </c>
       <c r="B111" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>125632950</v>
       </c>
       <c r="B112" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>125633081</v>
       </c>
       <c r="B113" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>125633201</v>
       </c>
       <c r="B114" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>125635101</v>
       </c>
       <c r="B115" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>125886318</v>
       </c>
       <c r="B124" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>125886385</v>
       </c>
       <c r="B125" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B127" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R127" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B128" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R128" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13862,10 +13862,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125886879</v>
+        <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13906,10 +13906,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>458051</v>
+        <v>458182</v>
       </c>
       <c r="R132" t="n">
-        <v>6901935</v>
+        <v>6901855</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13968,10 +13968,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125886299</v>
+        <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14012,10 +14012,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>458182</v>
+        <v>458051</v>
       </c>
       <c r="R133" t="n">
-        <v>6901855</v>
+        <v>6901935</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9256,7 +9256,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634843</v>
+        <v>125634921</v>
       </c>
       <c r="B85" t="n">
         <v>80070</v>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458100</v>
+        <v>458109</v>
       </c>
       <c r="R85" t="n">
-        <v>6901727</v>
+        <v>6901715</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125634921</v>
+        <v>125634843</v>
       </c>
       <c r="B86" t="n">
         <v>80070</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458109</v>
+        <v>458100</v>
       </c>
       <c r="R86" t="n">
-        <v>6901715</v>
+        <v>6901727</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9547,32 +9547,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125635066</v>
+        <v>125634527</v>
       </c>
       <c r="B88" t="n">
-        <v>98248</v>
+        <v>98331</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458157</v>
+        <v>458171</v>
       </c>
       <c r="R88" t="n">
-        <v>6901685</v>
+        <v>6901736</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,7 +9644,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125634527</v>
+        <v>125632818</v>
       </c>
       <c r="B89" t="n">
         <v>98331</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458171</v>
+        <v>458284</v>
       </c>
       <c r="R89" t="n">
-        <v>6901736</v>
+        <v>6901672</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,7 +9741,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125632818</v>
+        <v>125634585</v>
       </c>
       <c r="B90" t="n">
         <v>98331</v>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458284</v>
+        <v>458155</v>
       </c>
       <c r="R90" t="n">
-        <v>6901672</v>
+        <v>6901741</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125634585</v>
+        <v>125635066</v>
       </c>
       <c r="B91" t="n">
-        <v>98331</v>
+        <v>98248</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458155</v>
+        <v>458157</v>
       </c>
       <c r="R91" t="n">
-        <v>6901741</v>
+        <v>6901685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10823,32 +10823,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125633262</v>
+        <v>125633045</v>
       </c>
       <c r="B101" t="n">
-        <v>98331</v>
+        <v>78726</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458200</v>
+        <v>458247</v>
       </c>
       <c r="R101" t="n">
-        <v>6901673</v>
+        <v>6901689</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125633045</v>
+        <v>125633262</v>
       </c>
       <c r="B102" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458247</v>
+        <v>458200</v>
       </c>
       <c r="R102" t="n">
-        <v>6901689</v>
+        <v>6901673</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11017,32 +11017,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632670</v>
+        <v>125634677</v>
       </c>
       <c r="B103" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458288</v>
+        <v>458159</v>
       </c>
       <c r="R103" t="n">
-        <v>6901663</v>
+        <v>6901759</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125634677</v>
+        <v>125634785</v>
       </c>
       <c r="B104" t="n">
         <v>80070</v>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458159</v>
+        <v>458123</v>
       </c>
       <c r="R104" t="n">
-        <v>6901759</v>
+        <v>6901748</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125634785</v>
+        <v>125632670</v>
       </c>
       <c r="B105" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458123</v>
+        <v>458288</v>
       </c>
       <c r="R105" t="n">
-        <v>6901748</v>
+        <v>6901663</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11599,32 +11599,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125633359</v>
+        <v>125634596</v>
       </c>
       <c r="B109" t="n">
-        <v>98352</v>
+        <v>80070</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>458174</v>
+        <v>458160</v>
       </c>
       <c r="R109" t="n">
-        <v>6901705</v>
+        <v>6901743</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11696,32 +11696,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125634596</v>
+        <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458160</v>
+        <v>458174</v>
       </c>
       <c r="R110" t="n">
-        <v>6901743</v>
+        <v>6901705</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11793,7 +11793,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125633151</v>
+        <v>125632950</v>
       </c>
       <c r="B111" t="n">
         <v>98331</v>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458249</v>
+        <v>458282</v>
       </c>
       <c r="R111" t="n">
-        <v>6901668</v>
+        <v>6901706</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11864,11 +11864,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11895,7 +11890,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632950</v>
+        <v>125633081</v>
       </c>
       <c r="B112" t="n">
         <v>98331</v>
@@ -11930,10 +11925,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458282</v>
+        <v>458252</v>
       </c>
       <c r="R112" t="n">
-        <v>6901706</v>
+        <v>6901694</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11992,7 +11987,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125633081</v>
+        <v>125633151</v>
       </c>
       <c r="B113" t="n">
         <v>98331</v>
@@ -12027,10 +12022,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458252</v>
+        <v>458249</v>
       </c>
       <c r="R113" t="n">
-        <v>6901694</v>
+        <v>6901668</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12063,6 +12058,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9256,7 +9256,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634921</v>
+        <v>125634843</v>
       </c>
       <c r="B85" t="n">
         <v>80070</v>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458109</v>
+        <v>458100</v>
       </c>
       <c r="R85" t="n">
-        <v>6901715</v>
+        <v>6901727</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125634843</v>
+        <v>125634921</v>
       </c>
       <c r="B86" t="n">
         <v>80070</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458100</v>
+        <v>458109</v>
       </c>
       <c r="R86" t="n">
-        <v>6901727</v>
+        <v>6901715</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9547,32 +9547,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125634527</v>
+        <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98331</v>
+        <v>98248</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458171</v>
+        <v>458157</v>
       </c>
       <c r="R88" t="n">
-        <v>6901736</v>
+        <v>6901685</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,7 +9644,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125632818</v>
+        <v>125634527</v>
       </c>
       <c r="B89" t="n">
         <v>98331</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458284</v>
+        <v>458171</v>
       </c>
       <c r="R89" t="n">
-        <v>6901672</v>
+        <v>6901736</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,7 +9741,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125634585</v>
+        <v>125632818</v>
       </c>
       <c r="B90" t="n">
         <v>98331</v>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458155</v>
+        <v>458284</v>
       </c>
       <c r="R90" t="n">
-        <v>6901741</v>
+        <v>6901672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125635066</v>
+        <v>125634585</v>
       </c>
       <c r="B91" t="n">
-        <v>98248</v>
+        <v>98331</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458157</v>
+        <v>458155</v>
       </c>
       <c r="R91" t="n">
-        <v>6901685</v>
+        <v>6901741</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11599,32 +11599,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125634596</v>
+        <v>125633359</v>
       </c>
       <c r="B109" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>458160</v>
+        <v>458174</v>
       </c>
       <c r="R109" t="n">
-        <v>6901743</v>
+        <v>6901705</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11696,32 +11696,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125633359</v>
+        <v>125634596</v>
       </c>
       <c r="B110" t="n">
-        <v>98352</v>
+        <v>80070</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458174</v>
+        <v>458160</v>
       </c>
       <c r="R110" t="n">
-        <v>6901705</v>
+        <v>6901743</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12971,32 +12971,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125886605</v>
+        <v>125886318</v>
       </c>
       <c r="B123" t="n">
-        <v>80070</v>
+        <v>98332</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13006,10 +13006,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458150</v>
+        <v>458189</v>
       </c>
       <c r="R123" t="n">
-        <v>6901939</v>
+        <v>6901872</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13068,10 +13068,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125886318</v>
+        <v>125886385</v>
       </c>
       <c r="B124" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13096,17 +13096,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458189</v>
+        <v>458168</v>
       </c>
       <c r="R124" t="n">
-        <v>6901872</v>
+        <v>6901896</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13165,54 +13174,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886385</v>
+        <v>125886605</v>
       </c>
       <c r="B125" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458168</v>
+        <v>458150</v>
       </c>
       <c r="R125" t="n">
-        <v>6901896</v>
+        <v>6901939</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B127" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R127" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B128" t="n">
-        <v>80070</v>
+        <v>98332</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R128" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>125886472</v>
       </c>
       <c r="B136" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9065,7 +9065,7 @@
         <v>125632589</v>
       </c>
       <c r="B83" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>125633316</v>
       </c>
       <c r="B84" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>125634843</v>
       </c>
       <c r="B85" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>125634921</v>
       </c>
       <c r="B86" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>125634700</v>
       </c>
       <c r="B87" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98248</v>
+        <v>98251</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125634527</v>
+        <v>125634585</v>
       </c>
       <c r="B89" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458171</v>
+        <v>458155</v>
       </c>
       <c r="R89" t="n">
-        <v>6901736</v>
+        <v>6901741</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125632818</v>
+        <v>125634527</v>
       </c>
       <c r="B90" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458284</v>
+        <v>458171</v>
       </c>
       <c r="R90" t="n">
-        <v>6901672</v>
+        <v>6901736</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125634585</v>
+        <v>125632818</v>
       </c>
       <c r="B91" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458155</v>
+        <v>458284</v>
       </c>
       <c r="R91" t="n">
-        <v>6901741</v>
+        <v>6901672</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9938,7 +9938,7 @@
         <v>125633222</v>
       </c>
       <c r="B92" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633679</v>
+        <v>125633245</v>
       </c>
       <c r="B93" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458175</v>
+        <v>458224</v>
       </c>
       <c r="R93" t="n">
-        <v>6901690</v>
+        <v>6901685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10103,11 +10103,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10134,10 +10129,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632850</v>
+        <v>125633679</v>
       </c>
       <c r="B94" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10169,10 +10164,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458285</v>
+        <v>458175</v>
       </c>
       <c r="R94" t="n">
-        <v>6901673</v>
+        <v>6901690</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10205,6 +10200,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10231,10 +10231,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125633245</v>
+        <v>125632850</v>
       </c>
       <c r="B95" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458224</v>
+        <v>458285</v>
       </c>
       <c r="R95" t="n">
-        <v>6901685</v>
+        <v>6901673</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
         <v>125632993</v>
       </c>
       <c r="B96" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>125632788</v>
       </c>
       <c r="B97" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>125634050</v>
       </c>
       <c r="B98" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>125633306</v>
       </c>
       <c r="B99" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>125632572</v>
       </c>
       <c r="B100" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>125633045</v>
       </c>
       <c r="B101" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>125633262</v>
       </c>
       <c r="B102" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11017,32 +11017,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125634677</v>
+        <v>125632670</v>
       </c>
       <c r="B103" t="n">
-        <v>80070</v>
+        <v>98334</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458159</v>
+        <v>458288</v>
       </c>
       <c r="R103" t="n">
-        <v>6901759</v>
+        <v>6901663</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125634785</v>
+        <v>125634677</v>
       </c>
       <c r="B104" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458123</v>
+        <v>458159</v>
       </c>
       <c r="R104" t="n">
-        <v>6901748</v>
+        <v>6901759</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125632670</v>
+        <v>125634785</v>
       </c>
       <c r="B105" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458288</v>
+        <v>458123</v>
       </c>
       <c r="R105" t="n">
-        <v>6901663</v>
+        <v>6901748</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125633234</v>
+        <v>125634932</v>
       </c>
       <c r="B107" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>458228</v>
+        <v>458109</v>
       </c>
       <c r="R107" t="n">
-        <v>6901676</v>
+        <v>6901719</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125634932</v>
+        <v>125633234</v>
       </c>
       <c r="B108" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>458109</v>
+        <v>458228</v>
       </c>
       <c r="R108" t="n">
-        <v>6901719</v>
+        <v>6901676</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11602,7 +11602,7 @@
         <v>125633359</v>
       </c>
       <c r="B109" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>125634596</v>
       </c>
       <c r="B110" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11793,10 +11793,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632950</v>
+        <v>125633151</v>
       </c>
       <c r="B111" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458282</v>
+        <v>458249</v>
       </c>
       <c r="R111" t="n">
-        <v>6901706</v>
+        <v>6901668</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11864,6 +11864,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11890,10 +11895,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125633081</v>
+        <v>125632950</v>
       </c>
       <c r="B112" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11925,10 +11930,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458252</v>
+        <v>458282</v>
       </c>
       <c r="R112" t="n">
-        <v>6901694</v>
+        <v>6901706</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11987,10 +11992,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125633151</v>
+        <v>125633081</v>
       </c>
       <c r="B113" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12022,10 +12027,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458249</v>
+        <v>458252</v>
       </c>
       <c r="R113" t="n">
-        <v>6901668</v>
+        <v>6901694</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12058,11 +12063,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12089,10 +12089,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125633201</v>
+        <v>125635101</v>
       </c>
       <c r="B114" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12120,14 +12120,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458238</v>
+        <v>458152</v>
       </c>
       <c r="R114" t="n">
-        <v>6901671</v>
+        <v>6901693</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12186,10 +12186,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125635101</v>
+        <v>125633201</v>
       </c>
       <c r="B115" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12217,14 +12217,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458152</v>
+        <v>458238</v>
       </c>
       <c r="R115" t="n">
-        <v>6901693</v>
+        <v>6901671</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12286,7 +12286,7 @@
         <v>125634627</v>
       </c>
       <c r="B116" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12971,32 +12971,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125886318</v>
+        <v>125886605</v>
       </c>
       <c r="B123" t="n">
-        <v>98332</v>
+        <v>80071</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13006,10 +13006,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458189</v>
+        <v>458150</v>
       </c>
       <c r="R123" t="n">
-        <v>6901872</v>
+        <v>6901939</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13071,7 +13071,7 @@
         <v>125886385</v>
       </c>
       <c r="B124" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13174,32 +13174,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886605</v>
+        <v>125886318</v>
       </c>
       <c r="B125" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458150</v>
+        <v>458189</v>
       </c>
       <c r="R125" t="n">
-        <v>6901939</v>
+        <v>6901872</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>125886459</v>
       </c>
       <c r="B128" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -11114,7 +11114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125634677</v>
+        <v>125634785</v>
       </c>
       <c r="B104" t="n">
         <v>80071</v>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458159</v>
+        <v>458123</v>
       </c>
       <c r="R104" t="n">
-        <v>6901759</v>
+        <v>6901748</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,7 +11211,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125634785</v>
+        <v>125634677</v>
       </c>
       <c r="B105" t="n">
         <v>80071</v>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458123</v>
+        <v>458159</v>
       </c>
       <c r="R105" t="n">
-        <v>6901748</v>
+        <v>6901759</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12089,7 +12089,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125635101</v>
+        <v>125633201</v>
       </c>
       <c r="B114" t="n">
         <v>98334</v>
@@ -12120,14 +12120,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458152</v>
+        <v>458238</v>
       </c>
       <c r="R114" t="n">
-        <v>6901693</v>
+        <v>6901671</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12186,7 +12186,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125633201</v>
+        <v>125635101</v>
       </c>
       <c r="B115" t="n">
         <v>98334</v>
@@ -12217,14 +12217,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458238</v>
+        <v>458152</v>
       </c>
       <c r="R115" t="n">
-        <v>6901671</v>
+        <v>6901693</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9065,7 +9065,7 @@
         <v>125632589</v>
       </c>
       <c r="B83" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>125633316</v>
       </c>
       <c r="B84" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9256,32 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634843</v>
+        <v>125634700</v>
       </c>
       <c r="B85" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458100</v>
+        <v>458148</v>
       </c>
       <c r="R85" t="n">
-        <v>6901727</v>
+        <v>6901749</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125634921</v>
+        <v>125634843</v>
       </c>
       <c r="B86" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458109</v>
+        <v>458100</v>
       </c>
       <c r="R86" t="n">
-        <v>6901715</v>
+        <v>6901727</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,32 +9450,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125634700</v>
+        <v>125634921</v>
       </c>
       <c r="B87" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>458148</v>
+        <v>458109</v>
       </c>
       <c r="R87" t="n">
-        <v>6901749</v>
+        <v>6901715</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9550,7 +9550,7 @@
         <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125634585</v>
+        <v>125634527</v>
       </c>
       <c r="B89" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458155</v>
+        <v>458171</v>
       </c>
       <c r="R89" t="n">
-        <v>6901741</v>
+        <v>6901736</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125634527</v>
+        <v>125632818</v>
       </c>
       <c r="B90" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458171</v>
+        <v>458284</v>
       </c>
       <c r="R90" t="n">
-        <v>6901736</v>
+        <v>6901672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125632818</v>
+        <v>125634585</v>
       </c>
       <c r="B91" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458284</v>
+        <v>458155</v>
       </c>
       <c r="R91" t="n">
-        <v>6901672</v>
+        <v>6901741</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9938,7 +9938,7 @@
         <v>125633222</v>
       </c>
       <c r="B92" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633245</v>
+        <v>125633679</v>
       </c>
       <c r="B93" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458224</v>
+        <v>458175</v>
       </c>
       <c r="R93" t="n">
-        <v>6901685</v>
+        <v>6901690</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10103,6 +10103,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10129,10 +10134,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125633679</v>
+        <v>125632850</v>
       </c>
       <c r="B94" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10164,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458175</v>
+        <v>458285</v>
       </c>
       <c r="R94" t="n">
-        <v>6901690</v>
+        <v>6901673</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10200,11 +10205,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10231,10 +10231,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632850</v>
+        <v>125633245</v>
       </c>
       <c r="B95" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458285</v>
+        <v>458224</v>
       </c>
       <c r="R95" t="n">
-        <v>6901673</v>
+        <v>6901685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
         <v>125632993</v>
       </c>
       <c r="B96" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>125632788</v>
       </c>
       <c r="B97" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>125634050</v>
       </c>
       <c r="B98" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>125633306</v>
       </c>
       <c r="B99" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>125632572</v>
       </c>
       <c r="B100" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>125633045</v>
       </c>
       <c r="B101" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>125633262</v>
       </c>
       <c r="B102" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>125632670</v>
       </c>
       <c r="B103" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125634785</v>
+        <v>125634677</v>
       </c>
       <c r="B104" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458123</v>
+        <v>458159</v>
       </c>
       <c r="R104" t="n">
-        <v>6901748</v>
+        <v>6901759</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,10 +11211,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125634677</v>
+        <v>125634785</v>
       </c>
       <c r="B105" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458159</v>
+        <v>458123</v>
       </c>
       <c r="R105" t="n">
-        <v>6901759</v>
+        <v>6901748</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125634932</v>
+        <v>125633234</v>
       </c>
       <c r="B107" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>458109</v>
+        <v>458228</v>
       </c>
       <c r="R107" t="n">
-        <v>6901719</v>
+        <v>6901676</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125633234</v>
+        <v>125634932</v>
       </c>
       <c r="B108" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>458228</v>
+        <v>458109</v>
       </c>
       <c r="R108" t="n">
-        <v>6901676</v>
+        <v>6901719</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11599,32 +11599,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125633359</v>
+        <v>125634596</v>
       </c>
       <c r="B109" t="n">
-        <v>98355</v>
+        <v>80075</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>458174</v>
+        <v>458160</v>
       </c>
       <c r="R109" t="n">
-        <v>6901705</v>
+        <v>6901743</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11696,32 +11696,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125634596</v>
+        <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>80071</v>
+        <v>98359</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458160</v>
+        <v>458174</v>
       </c>
       <c r="R110" t="n">
-        <v>6901743</v>
+        <v>6901705</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11796,7 +11796,7 @@
         <v>125633151</v>
       </c>
       <c r="B111" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>125632950</v>
       </c>
       <c r="B112" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>125633081</v>
       </c>
       <c r="B113" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>125633201</v>
       </c>
       <c r="B114" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>125635101</v>
       </c>
       <c r="B115" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>125634627</v>
       </c>
       <c r="B116" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12971,45 +12971,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125886605</v>
+        <v>125886385</v>
       </c>
       <c r="B123" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458150</v>
+        <v>458168</v>
       </c>
       <c r="R123" t="n">
-        <v>6901939</v>
+        <v>6901896</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13068,10 +13077,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125886385</v>
+        <v>125886318</v>
       </c>
       <c r="B124" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13096,26 +13105,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458168</v>
+        <v>458189</v>
       </c>
       <c r="R124" t="n">
-        <v>6901896</v>
+        <v>6901872</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13174,32 +13174,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886318</v>
+        <v>125886605</v>
       </c>
       <c r="B125" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458189</v>
+        <v>458150</v>
       </c>
       <c r="R125" t="n">
-        <v>6901872</v>
+        <v>6901939</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B127" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R127" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B128" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R128" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>125886472</v>
       </c>
       <c r="B136" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9935,32 +9935,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125633222</v>
+        <v>125633245</v>
       </c>
       <c r="B92" t="n">
-        <v>79979</v>
+        <v>98338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>458233</v>
+        <v>458224</v>
       </c>
       <c r="R92" t="n">
-        <v>6901669</v>
+        <v>6901685</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10231,32 +10231,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125633245</v>
+        <v>125633222</v>
       </c>
       <c r="B95" t="n">
-        <v>98338</v>
+        <v>79979</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458224</v>
+        <v>458233</v>
       </c>
       <c r="R95" t="n">
-        <v>6901685</v>
+        <v>6901669</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12971,54 +12971,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125886385</v>
+        <v>125886605</v>
       </c>
       <c r="B123" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458168</v>
+        <v>458150</v>
       </c>
       <c r="R123" t="n">
-        <v>6901896</v>
+        <v>6901939</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13077,7 +13068,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125886318</v>
+        <v>125886385</v>
       </c>
       <c r="B124" t="n">
         <v>98338</v>
@@ -13105,17 +13096,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458189</v>
+        <v>458168</v>
       </c>
       <c r="R124" t="n">
-        <v>6901872</v>
+        <v>6901896</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13174,32 +13174,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886605</v>
+        <v>125886318</v>
       </c>
       <c r="B125" t="n">
-        <v>80075</v>
+        <v>98338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458150</v>
+        <v>458189</v>
       </c>
       <c r="R125" t="n">
-        <v>6901939</v>
+        <v>6901872</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9062,10 +9062,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125632589</v>
+        <v>125633316</v>
       </c>
       <c r="B83" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>458272</v>
+        <v>458200</v>
       </c>
       <c r="R83" t="n">
-        <v>6901664</v>
+        <v>6901685</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125633316</v>
+        <v>125632589</v>
       </c>
       <c r="B84" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>458200</v>
+        <v>458272</v>
       </c>
       <c r="R84" t="n">
-        <v>6901685</v>
+        <v>6901664</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9256,32 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634700</v>
+        <v>125634921</v>
       </c>
       <c r="B85" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458148</v>
+        <v>458109</v>
       </c>
       <c r="R85" t="n">
-        <v>6901749</v>
+        <v>6901715</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9450,32 +9450,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125634921</v>
+        <v>125634700</v>
       </c>
       <c r="B87" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>458109</v>
+        <v>458148</v>
       </c>
       <c r="R87" t="n">
-        <v>6901715</v>
+        <v>6901749</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,32 +9547,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125635066</v>
+        <v>125632818</v>
       </c>
       <c r="B88" t="n">
-        <v>98255</v>
+        <v>98339</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458157</v>
+        <v>458284</v>
       </c>
       <c r="R88" t="n">
-        <v>6901685</v>
+        <v>6901672</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125634527</v>
+        <v>125634585</v>
       </c>
       <c r="B89" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458171</v>
+        <v>458155</v>
       </c>
       <c r="R89" t="n">
-        <v>6901736</v>
+        <v>6901741</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125632818</v>
+        <v>125634527</v>
       </c>
       <c r="B90" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458284</v>
+        <v>458171</v>
       </c>
       <c r="R90" t="n">
-        <v>6901672</v>
+        <v>6901736</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125634585</v>
+        <v>125635066</v>
       </c>
       <c r="B91" t="n">
-        <v>98338</v>
+        <v>98256</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458155</v>
+        <v>458157</v>
       </c>
       <c r="R91" t="n">
-        <v>6901741</v>
+        <v>6901685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9938,7 +9938,7 @@
         <v>125633245</v>
       </c>
       <c r="B92" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>125633679</v>
       </c>
       <c r="B93" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>125632850</v>
       </c>
       <c r="B94" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10328,10 +10328,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632993</v>
+        <v>125632788</v>
       </c>
       <c r="B96" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>458270</v>
+        <v>458290</v>
       </c>
       <c r="R96" t="n">
-        <v>6901687</v>
+        <v>6901669</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10399,6 +10399,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10425,10 +10430,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125632788</v>
+        <v>125632993</v>
       </c>
       <c r="B97" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10460,10 +10465,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458290</v>
+        <v>458270</v>
       </c>
       <c r="R97" t="n">
-        <v>6901669</v>
+        <v>6901687</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10496,11 +10501,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10530,7 +10530,7 @@
         <v>125634050</v>
       </c>
       <c r="B98" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>125633306</v>
       </c>
       <c r="B99" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>125632572</v>
       </c>
       <c r="B100" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10823,32 +10823,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125633045</v>
+        <v>125633262</v>
       </c>
       <c r="B101" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458247</v>
+        <v>458200</v>
       </c>
       <c r="R101" t="n">
-        <v>6901689</v>
+        <v>6901673</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125633262</v>
+        <v>125633045</v>
       </c>
       <c r="B102" t="n">
-        <v>98338</v>
+        <v>78731</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458200</v>
+        <v>458247</v>
       </c>
       <c r="R102" t="n">
-        <v>6901673</v>
+        <v>6901689</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11017,32 +11017,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632670</v>
+        <v>125634785</v>
       </c>
       <c r="B103" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458288</v>
+        <v>458123</v>
       </c>
       <c r="R103" t="n">
-        <v>6901663</v>
+        <v>6901748</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125634785</v>
+        <v>125632670</v>
       </c>
       <c r="B105" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458123</v>
+        <v>458288</v>
       </c>
       <c r="R105" t="n">
-        <v>6901748</v>
+        <v>6901663</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>125633234</v>
       </c>
       <c r="B107" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>125634932</v>
       </c>
       <c r="B108" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11793,10 +11793,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125633151</v>
+        <v>125632950</v>
       </c>
       <c r="B111" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458249</v>
+        <v>458282</v>
       </c>
       <c r="R111" t="n">
-        <v>6901668</v>
+        <v>6901706</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11864,11 +11864,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11895,10 +11890,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632950</v>
+        <v>125633151</v>
       </c>
       <c r="B112" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11930,10 +11925,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458282</v>
+        <v>458249</v>
       </c>
       <c r="R112" t="n">
-        <v>6901706</v>
+        <v>6901668</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11966,6 +11961,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11995,7 +11995,7 @@
         <v>125633081</v>
       </c>
       <c r="B113" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>125633201</v>
       </c>
       <c r="B114" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>125635101</v>
       </c>
       <c r="B115" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13068,10 +13068,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125886385</v>
+        <v>125886318</v>
       </c>
       <c r="B124" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13096,26 +13096,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458168</v>
+        <v>458189</v>
       </c>
       <c r="R124" t="n">
-        <v>6901896</v>
+        <v>6901872</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13174,10 +13165,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886318</v>
+        <v>125886385</v>
       </c>
       <c r="B125" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13202,17 +13193,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458189</v>
+        <v>458168</v>
       </c>
       <c r="R125" t="n">
-        <v>6901872</v>
+        <v>6901896</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B127" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R127" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B128" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R128" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -10624,32 +10624,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125633306</v>
+        <v>125632572</v>
       </c>
       <c r="B99" t="n">
-        <v>98339</v>
+        <v>98360</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458200</v>
+        <v>458275</v>
       </c>
       <c r="R99" t="n">
-        <v>6901697</v>
+        <v>6901664</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10695,6 +10695,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10721,32 +10726,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125632572</v>
+        <v>125633306</v>
       </c>
       <c r="B100" t="n">
-        <v>98360</v>
+        <v>98339</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10756,10 +10761,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>458275</v>
+        <v>458200</v>
       </c>
       <c r="R100" t="n">
-        <v>6901664</v>
+        <v>6901697</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10792,11 +10797,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11599,32 +11599,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125634596</v>
+        <v>125633359</v>
       </c>
       <c r="B109" t="n">
-        <v>80075</v>
+        <v>98360</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>458160</v>
+        <v>458174</v>
       </c>
       <c r="R109" t="n">
-        <v>6901743</v>
+        <v>6901705</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11696,32 +11696,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125633359</v>
+        <v>125634596</v>
       </c>
       <c r="B110" t="n">
-        <v>98360</v>
+        <v>80075</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458174</v>
+        <v>458160</v>
       </c>
       <c r="R110" t="n">
-        <v>6901705</v>
+        <v>6901743</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -10624,32 +10624,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125632572</v>
+        <v>125633306</v>
       </c>
       <c r="B99" t="n">
-        <v>98360</v>
+        <v>98339</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458275</v>
+        <v>458200</v>
       </c>
       <c r="R99" t="n">
-        <v>6901664</v>
+        <v>6901697</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10695,11 +10695,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10726,32 +10721,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125633306</v>
+        <v>125632572</v>
       </c>
       <c r="B100" t="n">
-        <v>98339</v>
+        <v>98360</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10761,10 +10756,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>458200</v>
+        <v>458275</v>
       </c>
       <c r="R100" t="n">
-        <v>6901697</v>
+        <v>6901664</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10797,6 +10792,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11599,32 +11599,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125633359</v>
+        <v>125634596</v>
       </c>
       <c r="B109" t="n">
-        <v>98360</v>
+        <v>80075</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11634,10 +11634,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>458174</v>
+        <v>458160</v>
       </c>
       <c r="R109" t="n">
-        <v>6901705</v>
+        <v>6901743</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11696,32 +11696,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125634596</v>
+        <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>80075</v>
+        <v>98360</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>458160</v>
+        <v>458174</v>
       </c>
       <c r="R110" t="n">
-        <v>6901743</v>
+        <v>6901705</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9062,10 +9062,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125633316</v>
+        <v>125632589</v>
       </c>
       <c r="B83" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>458200</v>
+        <v>458272</v>
       </c>
       <c r="R83" t="n">
-        <v>6901685</v>
+        <v>6901664</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125632589</v>
+        <v>125633316</v>
       </c>
       <c r="B84" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>458272</v>
+        <v>458200</v>
       </c>
       <c r="R84" t="n">
-        <v>6901664</v>
+        <v>6901685</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634921</v>
+        <v>125634843</v>
       </c>
       <c r="B85" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458109</v>
+        <v>458100</v>
       </c>
       <c r="R85" t="n">
-        <v>6901715</v>
+        <v>6901727</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125634843</v>
+        <v>125634921</v>
       </c>
       <c r="B86" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458100</v>
+        <v>458109</v>
       </c>
       <c r="R86" t="n">
-        <v>6901727</v>
+        <v>6901715</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
         <v>125634700</v>
       </c>
       <c r="B87" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9547,32 +9547,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125632818</v>
+        <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98339</v>
+        <v>98258</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458284</v>
+        <v>458157</v>
       </c>
       <c r="R88" t="n">
-        <v>6901672</v>
+        <v>6901685</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125634585</v>
+        <v>125634527</v>
       </c>
       <c r="B89" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458155</v>
+        <v>458171</v>
       </c>
       <c r="R89" t="n">
-        <v>6901741</v>
+        <v>6901736</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125634527</v>
+        <v>125632818</v>
       </c>
       <c r="B90" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458171</v>
+        <v>458284</v>
       </c>
       <c r="R90" t="n">
-        <v>6901736</v>
+        <v>6901672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125635066</v>
+        <v>125634585</v>
       </c>
       <c r="B91" t="n">
-        <v>98256</v>
+        <v>98341</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458157</v>
+        <v>458155</v>
       </c>
       <c r="R91" t="n">
-        <v>6901685</v>
+        <v>6901741</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9935,32 +9935,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125633245</v>
+        <v>125633222</v>
       </c>
       <c r="B92" t="n">
-        <v>98339</v>
+        <v>79980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>458224</v>
+        <v>458233</v>
       </c>
       <c r="R92" t="n">
-        <v>6901685</v>
+        <v>6901669</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10035,7 +10035,7 @@
         <v>125633679</v>
       </c>
       <c r="B93" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>125632850</v>
       </c>
       <c r="B94" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10231,32 +10231,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125633222</v>
+        <v>125633245</v>
       </c>
       <c r="B95" t="n">
-        <v>79979</v>
+        <v>98341</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458233</v>
+        <v>458224</v>
       </c>
       <c r="R95" t="n">
-        <v>6901669</v>
+        <v>6901685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10328,32 +10328,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632788</v>
+        <v>125634050</v>
       </c>
       <c r="B96" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>458290</v>
+        <v>458161</v>
       </c>
       <c r="R96" t="n">
-        <v>6901669</v>
+        <v>6901715</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10399,11 +10399,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10433,7 +10428,7 @@
         <v>125632993</v>
       </c>
       <c r="B97" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10527,32 +10522,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125634050</v>
+        <v>125632788</v>
       </c>
       <c r="B98" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>458161</v>
+        <v>458290</v>
       </c>
       <c r="R98" t="n">
-        <v>6901715</v>
+        <v>6901669</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10598,6 +10593,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10624,32 +10624,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125633306</v>
+        <v>125632572</v>
       </c>
       <c r="B99" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458200</v>
+        <v>458275</v>
       </c>
       <c r="R99" t="n">
-        <v>6901697</v>
+        <v>6901664</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10695,6 +10695,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10721,32 +10726,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125632572</v>
+        <v>125633306</v>
       </c>
       <c r="B100" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10756,10 +10761,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>458275</v>
+        <v>458200</v>
       </c>
       <c r="R100" t="n">
-        <v>6901664</v>
+        <v>6901697</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10792,11 +10797,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10823,32 +10823,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125633262</v>
+        <v>125633045</v>
       </c>
       <c r="B101" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458200</v>
+        <v>458247</v>
       </c>
       <c r="R101" t="n">
-        <v>6901673</v>
+        <v>6901689</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125633045</v>
+        <v>125633262</v>
       </c>
       <c r="B102" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458247</v>
+        <v>458200</v>
       </c>
       <c r="R102" t="n">
-        <v>6901689</v>
+        <v>6901673</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11017,32 +11017,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125634785</v>
+        <v>125632670</v>
       </c>
       <c r="B103" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458123</v>
+        <v>458288</v>
       </c>
       <c r="R103" t="n">
-        <v>6901748</v>
+        <v>6901663</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11117,7 +11117,7 @@
         <v>125634677</v>
       </c>
       <c r="B104" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125632670</v>
+        <v>125634785</v>
       </c>
       <c r="B105" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458288</v>
+        <v>458123</v>
       </c>
       <c r="R105" t="n">
-        <v>6901663</v>
+        <v>6901748</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>125633234</v>
       </c>
       <c r="B107" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>125634932</v>
       </c>
       <c r="B108" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>125634596</v>
       </c>
       <c r="B109" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11793,10 +11793,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632950</v>
+        <v>125633151</v>
       </c>
       <c r="B111" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458282</v>
+        <v>458249</v>
       </c>
       <c r="R111" t="n">
-        <v>6901706</v>
+        <v>6901668</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11864,6 +11864,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11890,10 +11895,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125633151</v>
+        <v>125632950</v>
       </c>
       <c r="B112" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11925,10 +11930,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458249</v>
+        <v>458282</v>
       </c>
       <c r="R112" t="n">
-        <v>6901668</v>
+        <v>6901706</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11961,11 +11966,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11995,7 +11995,7 @@
         <v>125633081</v>
       </c>
       <c r="B113" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>125633201</v>
       </c>
       <c r="B114" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>125635101</v>
       </c>
       <c r="B115" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>125634627</v>
       </c>
       <c r="B116" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>125886605</v>
       </c>
       <c r="B123" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>125886318</v>
       </c>
       <c r="B124" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>125886385</v>
       </c>
       <c r="B125" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B127" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R127" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B128" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R128" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>125886472</v>
       </c>
       <c r="B136" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9256,32 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634843</v>
+        <v>125634700</v>
       </c>
       <c r="B85" t="n">
-        <v>80076</v>
+        <v>98341</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458100</v>
+        <v>458148</v>
       </c>
       <c r="R85" t="n">
-        <v>6901727</v>
+        <v>6901749</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125634921</v>
+        <v>125634843</v>
       </c>
       <c r="B86" t="n">
         <v>80076</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458109</v>
+        <v>458100</v>
       </c>
       <c r="R86" t="n">
-        <v>6901715</v>
+        <v>6901727</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,32 +9450,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125634700</v>
+        <v>125634921</v>
       </c>
       <c r="B87" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>458148</v>
+        <v>458109</v>
       </c>
       <c r="R87" t="n">
-        <v>6901749</v>
+        <v>6901715</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11793,7 +11793,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125633151</v>
+        <v>125633081</v>
       </c>
       <c r="B111" t="n">
         <v>98341</v>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458249</v>
+        <v>458252</v>
       </c>
       <c r="R111" t="n">
-        <v>6901668</v>
+        <v>6901694</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11864,11 +11864,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11895,7 +11890,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125632950</v>
+        <v>125633151</v>
       </c>
       <c r="B112" t="n">
         <v>98341</v>
@@ -11930,10 +11925,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458282</v>
+        <v>458249</v>
       </c>
       <c r="R112" t="n">
-        <v>6901706</v>
+        <v>6901668</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11966,6 +11961,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11992,7 +11992,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125633081</v>
+        <v>125632950</v>
       </c>
       <c r="B113" t="n">
         <v>98341</v>
@@ -12027,10 +12027,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458252</v>
+        <v>458282</v>
       </c>
       <c r="R113" t="n">
-        <v>6901694</v>
+        <v>6901706</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9065,7 +9065,7 @@
         <v>125632589</v>
       </c>
       <c r="B83" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>125633316</v>
       </c>
       <c r="B84" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9256,32 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634700</v>
+        <v>125634921</v>
       </c>
       <c r="B85" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458148</v>
+        <v>458109</v>
       </c>
       <c r="R85" t="n">
-        <v>6901749</v>
+        <v>6901715</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9450,32 +9450,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125634921</v>
+        <v>125634700</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>458109</v>
+        <v>458148</v>
       </c>
       <c r="R87" t="n">
-        <v>6901715</v>
+        <v>6901749</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,32 +9547,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125635066</v>
+        <v>125634527</v>
       </c>
       <c r="B88" t="n">
-        <v>98258</v>
+        <v>98343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458157</v>
+        <v>458171</v>
       </c>
       <c r="R88" t="n">
-        <v>6901685</v>
+        <v>6901736</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,10 +9644,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125634527</v>
+        <v>125632818</v>
       </c>
       <c r="B89" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458171</v>
+        <v>458284</v>
       </c>
       <c r="R89" t="n">
-        <v>6901736</v>
+        <v>6901672</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125632818</v>
+        <v>125634585</v>
       </c>
       <c r="B90" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458284</v>
+        <v>458155</v>
       </c>
       <c r="R90" t="n">
-        <v>6901672</v>
+        <v>6901741</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125634585</v>
+        <v>125635066</v>
       </c>
       <c r="B91" t="n">
-        <v>98341</v>
+        <v>98260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458155</v>
+        <v>458157</v>
       </c>
       <c r="R91" t="n">
-        <v>6901741</v>
+        <v>6901685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633679</v>
+        <v>125633245</v>
       </c>
       <c r="B93" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458175</v>
+        <v>458224</v>
       </c>
       <c r="R93" t="n">
-        <v>6901690</v>
+        <v>6901685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10103,11 +10103,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10134,10 +10129,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125632850</v>
+        <v>125633679</v>
       </c>
       <c r="B94" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10169,10 +10164,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458285</v>
+        <v>458175</v>
       </c>
       <c r="R94" t="n">
-        <v>6901673</v>
+        <v>6901690</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10205,6 +10200,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10231,10 +10231,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125633245</v>
+        <v>125632850</v>
       </c>
       <c r="B95" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458224</v>
+        <v>458285</v>
       </c>
       <c r="R95" t="n">
-        <v>6901685</v>
+        <v>6901673</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10328,32 +10328,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125634050</v>
+        <v>125632993</v>
       </c>
       <c r="B96" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>458161</v>
+        <v>458270</v>
       </c>
       <c r="R96" t="n">
-        <v>6901715</v>
+        <v>6901687</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125632993</v>
+        <v>125632788</v>
       </c>
       <c r="B97" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458270</v>
+        <v>458290</v>
       </c>
       <c r="R97" t="n">
-        <v>6901687</v>
+        <v>6901669</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10496,6 +10496,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10522,32 +10527,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632788</v>
+        <v>125634050</v>
       </c>
       <c r="B98" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10557,10 +10562,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>458290</v>
+        <v>458161</v>
       </c>
       <c r="R98" t="n">
-        <v>6901669</v>
+        <v>6901715</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10593,11 +10598,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10624,32 +10624,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125632572</v>
+        <v>125633306</v>
       </c>
       <c r="B99" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458275</v>
+        <v>458200</v>
       </c>
       <c r="R99" t="n">
-        <v>6901664</v>
+        <v>6901697</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10695,11 +10695,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10726,32 +10721,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125633306</v>
+        <v>125632572</v>
       </c>
       <c r="B100" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10761,10 +10756,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>458200</v>
+        <v>458275</v>
       </c>
       <c r="R100" t="n">
-        <v>6901697</v>
+        <v>6901664</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10797,6 +10792,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10923,7 +10923,7 @@
         <v>125633262</v>
       </c>
       <c r="B102" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>125632670</v>
       </c>
       <c r="B103" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125634677</v>
+        <v>125634785</v>
       </c>
       <c r="B104" t="n">
         <v>80076</v>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458159</v>
+        <v>458123</v>
       </c>
       <c r="R104" t="n">
-        <v>6901759</v>
+        <v>6901748</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,7 +11211,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125634785</v>
+        <v>125634677</v>
       </c>
       <c r="B105" t="n">
         <v>80076</v>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458123</v>
+        <v>458159</v>
       </c>
       <c r="R105" t="n">
-        <v>6901748</v>
+        <v>6901759</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>125633234</v>
       </c>
       <c r="B107" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>125634932</v>
       </c>
       <c r="B108" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11793,10 +11793,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125633081</v>
+        <v>125632950</v>
       </c>
       <c r="B111" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458252</v>
+        <v>458282</v>
       </c>
       <c r="R111" t="n">
-        <v>6901694</v>
+        <v>6901706</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11893,7 +11893,7 @@
         <v>125633151</v>
       </c>
       <c r="B112" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125632950</v>
+        <v>125633081</v>
       </c>
       <c r="B113" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12027,10 +12027,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458282</v>
+        <v>458252</v>
       </c>
       <c r="R113" t="n">
-        <v>6901706</v>
+        <v>6901694</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
         <v>125633201</v>
       </c>
       <c r="B114" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>125635101</v>
       </c>
       <c r="B115" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>125886318</v>
       </c>
       <c r="B124" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>125886385</v>
       </c>
       <c r="B125" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>125886459</v>
       </c>
       <c r="B127" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9256,32 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634921</v>
+        <v>125634700</v>
       </c>
       <c r="B85" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458109</v>
+        <v>458148</v>
       </c>
       <c r="R85" t="n">
-        <v>6901715</v>
+        <v>6901749</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125634843</v>
+        <v>125634921</v>
       </c>
       <c r="B86" t="n">
         <v>80076</v>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458100</v>
+        <v>458109</v>
       </c>
       <c r="R86" t="n">
-        <v>6901727</v>
+        <v>6901715</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,32 +9450,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125634700</v>
+        <v>125634843</v>
       </c>
       <c r="B87" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>458148</v>
+        <v>458100</v>
       </c>
       <c r="R87" t="n">
-        <v>6901749</v>
+        <v>6901727</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,32 +9547,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125634527</v>
+        <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98343</v>
+        <v>98260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>458171</v>
+        <v>458157</v>
       </c>
       <c r="R88" t="n">
-        <v>6901736</v>
+        <v>6901685</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,7 +9644,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125632818</v>
+        <v>125634527</v>
       </c>
       <c r="B89" t="n">
         <v>98343</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>458284</v>
+        <v>458171</v>
       </c>
       <c r="R89" t="n">
-        <v>6901672</v>
+        <v>6901736</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,7 +9741,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125634585</v>
+        <v>125632818</v>
       </c>
       <c r="B90" t="n">
         <v>98343</v>
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>458155</v>
+        <v>458284</v>
       </c>
       <c r="R90" t="n">
-        <v>6901741</v>
+        <v>6901672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125635066</v>
+        <v>125634585</v>
       </c>
       <c r="B91" t="n">
-        <v>98260</v>
+        <v>98343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9873,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>458157</v>
+        <v>458155</v>
       </c>
       <c r="R91" t="n">
-        <v>6901685</v>
+        <v>6901741</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10823,32 +10823,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125633045</v>
+        <v>125633262</v>
       </c>
       <c r="B101" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>458247</v>
+        <v>458200</v>
       </c>
       <c r="R101" t="n">
-        <v>6901689</v>
+        <v>6901673</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10920,32 +10920,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125633262</v>
+        <v>125633045</v>
       </c>
       <c r="B102" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10955,10 +10955,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>458200</v>
+        <v>458247</v>
       </c>
       <c r="R102" t="n">
-        <v>6901673</v>
+        <v>6901689</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11017,32 +11017,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125632670</v>
+        <v>125634785</v>
       </c>
       <c r="B103" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458288</v>
+        <v>458123</v>
       </c>
       <c r="R103" t="n">
-        <v>6901663</v>
+        <v>6901748</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11114,7 +11114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125634785</v>
+        <v>125634677</v>
       </c>
       <c r="B104" t="n">
         <v>80076</v>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458123</v>
+        <v>458159</v>
       </c>
       <c r="R104" t="n">
-        <v>6901748</v>
+        <v>6901759</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125634677</v>
+        <v>125632670</v>
       </c>
       <c r="B105" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458159</v>
+        <v>458288</v>
       </c>
       <c r="R105" t="n">
-        <v>6901759</v>
+        <v>6901663</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B127" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R127" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B128" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R128" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9065,7 +9065,7 @@
         <v>125632589</v>
       </c>
       <c r="B83" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>125633316</v>
       </c>
       <c r="B84" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9256,32 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634700</v>
+        <v>125634843</v>
       </c>
       <c r="B85" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458148</v>
+        <v>458100</v>
       </c>
       <c r="R85" t="n">
-        <v>6901749</v>
+        <v>6901727</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9450,32 +9450,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125634843</v>
+        <v>125634700</v>
       </c>
       <c r="B87" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>458100</v>
+        <v>458148</v>
       </c>
       <c r="R87" t="n">
-        <v>6901727</v>
+        <v>6901749</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9550,7 +9550,7 @@
         <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>125634527</v>
       </c>
       <c r="B89" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>125632818</v>
       </c>
       <c r="B90" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>125634585</v>
       </c>
       <c r="B91" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9935,32 +9935,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125633222</v>
+        <v>125633679</v>
       </c>
       <c r="B92" t="n">
-        <v>79980</v>
+        <v>98345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>458233</v>
+        <v>458175</v>
       </c>
       <c r="R92" t="n">
-        <v>6901669</v>
+        <v>6901690</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10006,6 +10006,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10032,10 +10037,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633245</v>
+        <v>125632850</v>
       </c>
       <c r="B93" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10067,10 +10072,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458224</v>
+        <v>458285</v>
       </c>
       <c r="R93" t="n">
-        <v>6901685</v>
+        <v>6901673</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10129,10 +10134,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125633679</v>
+        <v>125633245</v>
       </c>
       <c r="B94" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10164,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458175</v>
+        <v>458224</v>
       </c>
       <c r="R94" t="n">
-        <v>6901690</v>
+        <v>6901685</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10200,11 +10205,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10231,32 +10231,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632850</v>
+        <v>125633222</v>
       </c>
       <c r="B95" t="n">
-        <v>98343</v>
+        <v>79980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458285</v>
+        <v>458233</v>
       </c>
       <c r="R95" t="n">
-        <v>6901673</v>
+        <v>6901669</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10328,32 +10328,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125632993</v>
+        <v>125634050</v>
       </c>
       <c r="B96" t="n">
-        <v>98343</v>
+        <v>98366</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>458270</v>
+        <v>458161</v>
       </c>
       <c r="R96" t="n">
-        <v>6901687</v>
+        <v>6901715</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10428,7 +10428,7 @@
         <v>125632788</v>
       </c>
       <c r="B97" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10527,32 +10527,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125634050</v>
+        <v>125632993</v>
       </c>
       <c r="B98" t="n">
-        <v>98364</v>
+        <v>98345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10562,10 +10562,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>458161</v>
+        <v>458270</v>
       </c>
       <c r="R98" t="n">
-        <v>6901715</v>
+        <v>6901687</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10627,7 +10627,7 @@
         <v>125633306</v>
       </c>
       <c r="B99" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>125632572</v>
       </c>
       <c r="B100" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>125633262</v>
       </c>
       <c r="B101" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11017,32 +11017,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125634785</v>
+        <v>125632670</v>
       </c>
       <c r="B103" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>458123</v>
+        <v>458288</v>
       </c>
       <c r="R103" t="n">
-        <v>6901748</v>
+        <v>6901663</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11211,32 +11211,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125632670</v>
+        <v>125634785</v>
       </c>
       <c r="B105" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458288</v>
+        <v>458123</v>
       </c>
       <c r="R105" t="n">
-        <v>6901663</v>
+        <v>6901748</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>125633234</v>
       </c>
       <c r="B107" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>125634932</v>
       </c>
       <c r="B108" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11793,10 +11793,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125632950</v>
+        <v>125633081</v>
       </c>
       <c r="B111" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458282</v>
+        <v>458252</v>
       </c>
       <c r="R111" t="n">
-        <v>6901706</v>
+        <v>6901694</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11893,7 +11893,7 @@
         <v>125633151</v>
       </c>
       <c r="B112" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125633081</v>
+        <v>125632950</v>
       </c>
       <c r="B113" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12027,10 +12027,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458252</v>
+        <v>458282</v>
       </c>
       <c r="R113" t="n">
-        <v>6901694</v>
+        <v>6901706</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12089,10 +12089,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125633201</v>
+        <v>125635101</v>
       </c>
       <c r="B114" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12120,14 +12120,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458238</v>
+        <v>458152</v>
       </c>
       <c r="R114" t="n">
-        <v>6901671</v>
+        <v>6901693</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12186,10 +12186,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125635101</v>
+        <v>125633201</v>
       </c>
       <c r="B115" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12217,14 +12217,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458152</v>
+        <v>458238</v>
       </c>
       <c r="R115" t="n">
-        <v>6901693</v>
+        <v>6901671</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12383,7 +12383,7 @@
         <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>125886318</v>
       </c>
       <c r="B124" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>125886385</v>
       </c>
       <c r="B125" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B127" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R127" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B128" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R128" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13862,10 +13862,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125886299</v>
+        <v>125886879</v>
       </c>
       <c r="B132" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13906,10 +13906,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>458182</v>
+        <v>458051</v>
       </c>
       <c r="R132" t="n">
-        <v>6901855</v>
+        <v>6901935</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13968,10 +13968,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125886879</v>
+        <v>125886299</v>
       </c>
       <c r="B133" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14012,10 +14012,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>458051</v>
+        <v>458182</v>
       </c>
       <c r="R133" t="n">
-        <v>6901935</v>
+        <v>6901855</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9935,32 +9935,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125633679</v>
+        <v>125633222</v>
       </c>
       <c r="B92" t="n">
-        <v>98345</v>
+        <v>79980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>458175</v>
+        <v>458233</v>
       </c>
       <c r="R92" t="n">
-        <v>6901690</v>
+        <v>6901669</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10006,11 +10006,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10037,7 +10032,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125632850</v>
+        <v>125633245</v>
       </c>
       <c r="B93" t="n">
         <v>98345</v>
@@ -10072,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458285</v>
+        <v>458224</v>
       </c>
       <c r="R93" t="n">
-        <v>6901673</v>
+        <v>6901685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10134,7 +10129,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125633245</v>
+        <v>125633679</v>
       </c>
       <c r="B94" t="n">
         <v>98345</v>
@@ -10169,10 +10164,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458224</v>
+        <v>458175</v>
       </c>
       <c r="R94" t="n">
-        <v>6901685</v>
+        <v>6901690</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10205,6 +10200,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10231,32 +10231,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125633222</v>
+        <v>125632850</v>
       </c>
       <c r="B95" t="n">
-        <v>79980</v>
+        <v>98345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458233</v>
+        <v>458285</v>
       </c>
       <c r="R95" t="n">
-        <v>6901669</v>
+        <v>6901673</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13765,7 +13765,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125886855</v>
+        <v>125886299</v>
       </c>
       <c r="B131" t="n">
         <v>98345</v>
@@ -13793,17 +13793,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>458106</v>
+        <v>458182</v>
       </c>
       <c r="R131" t="n">
-        <v>6901940</v>
+        <v>6901855</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13862,7 +13871,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125886879</v>
+        <v>125886855</v>
       </c>
       <c r="B132" t="n">
         <v>98345</v>
@@ -13890,26 +13899,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>458051</v>
+        <v>458106</v>
       </c>
       <c r="R132" t="n">
-        <v>6901935</v>
+        <v>6901940</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13968,7 +13968,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125886299</v>
+        <v>125886879</v>
       </c>
       <c r="B133" t="n">
         <v>98345</v>
@@ -14012,10 +14012,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>458182</v>
+        <v>458051</v>
       </c>
       <c r="R133" t="n">
-        <v>6901855</v>
+        <v>6901935</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -9065,7 +9065,7 @@
         <v>125632589</v>
       </c>
       <c r="B83" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>125633316</v>
       </c>
       <c r="B84" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125634843</v>
+        <v>125634921</v>
       </c>
       <c r="B85" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>458100</v>
+        <v>458109</v>
       </c>
       <c r="R85" t="n">
-        <v>6901727</v>
+        <v>6901715</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125634921</v>
+        <v>125634843</v>
       </c>
       <c r="B86" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>458109</v>
+        <v>458100</v>
       </c>
       <c r="R86" t="n">
-        <v>6901715</v>
+        <v>6901727</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
         <v>125634700</v>
       </c>
       <c r="B87" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>125635066</v>
       </c>
       <c r="B88" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>125634527</v>
       </c>
       <c r="B89" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>125632818</v>
       </c>
       <c r="B90" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>125634585</v>
       </c>
       <c r="B91" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>125633222</v>
       </c>
       <c r="B92" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125633245</v>
+        <v>125633679</v>
       </c>
       <c r="B93" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>458224</v>
+        <v>458175</v>
       </c>
       <c r="R93" t="n">
-        <v>6901685</v>
+        <v>6901690</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10103,6 +10103,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10129,10 +10134,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125633679</v>
+        <v>125632850</v>
       </c>
       <c r="B94" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10164,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>458175</v>
+        <v>458285</v>
       </c>
       <c r="R94" t="n">
-        <v>6901690</v>
+        <v>6901673</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10200,11 +10205,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 100 rosetter på 5 kvadratmeter.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10231,10 +10231,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125632850</v>
+        <v>125633245</v>
       </c>
       <c r="B95" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10266,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>458285</v>
+        <v>458224</v>
       </c>
       <c r="R95" t="n">
-        <v>6901673</v>
+        <v>6901685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10331,7 +10331,7 @@
         <v>125634050</v>
       </c>
       <c r="B96" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125632788</v>
+        <v>125632993</v>
       </c>
       <c r="B97" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10460,10 +10460,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>458290</v>
+        <v>458270</v>
       </c>
       <c r="R97" t="n">
-        <v>6901669</v>
+        <v>6901687</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10496,11 +10496,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10527,10 +10522,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125632993</v>
+        <v>125632788</v>
       </c>
       <c r="B98" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10562,10 +10557,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>458270</v>
+        <v>458290</v>
       </c>
       <c r="R98" t="n">
-        <v>6901687</v>
+        <v>6901669</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10598,6 +10593,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Vanlig i området.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10624,32 +10624,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125633306</v>
+        <v>125632572</v>
       </c>
       <c r="B99" t="n">
-        <v>98345</v>
+        <v>98370</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>458200</v>
+        <v>458275</v>
       </c>
       <c r="R99" t="n">
-        <v>6901697</v>
+        <v>6901664</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10695,6 +10695,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10721,32 +10726,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125632572</v>
+        <v>125633306</v>
       </c>
       <c r="B100" t="n">
-        <v>98366</v>
+        <v>98349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10756,10 +10761,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>458275</v>
+        <v>458200</v>
       </c>
       <c r="R100" t="n">
-        <v>6901664</v>
+        <v>6901697</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10792,11 +10797,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>10 exemplar.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10826,7 +10826,7 @@
         <v>125633262</v>
       </c>
       <c r="B101" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>125633045</v>
       </c>
       <c r="B102" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>125632670</v>
       </c>
       <c r="B103" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11114,10 +11114,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125634677</v>
+        <v>125634785</v>
       </c>
       <c r="B104" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11149,10 +11149,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>458159</v>
+        <v>458123</v>
       </c>
       <c r="R104" t="n">
-        <v>6901759</v>
+        <v>6901748</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,10 +11211,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125634785</v>
+        <v>125634677</v>
       </c>
       <c r="B105" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11246,10 +11246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>458123</v>
+        <v>458159</v>
       </c>
       <c r="R105" t="n">
-        <v>6901748</v>
+        <v>6901759</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11311,7 +11311,7 @@
         <v>125633982</v>
       </c>
       <c r="B106" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>125633234</v>
       </c>
       <c r="B107" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>125634932</v>
       </c>
       <c r="B108" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>125634596</v>
       </c>
       <c r="B109" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>125633359</v>
       </c>
       <c r="B110" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11793,10 +11793,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125633081</v>
+        <v>125633151</v>
       </c>
       <c r="B111" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>458252</v>
+        <v>458249</v>
       </c>
       <c r="R111" t="n">
-        <v>6901694</v>
+        <v>6901668</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11864,6 +11864,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11890,10 +11895,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125633151</v>
+        <v>125632950</v>
       </c>
       <c r="B112" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11925,10 +11930,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>458249</v>
+        <v>458282</v>
       </c>
       <c r="R112" t="n">
-        <v>6901668</v>
+        <v>6901706</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11961,11 +11966,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>50 exemplar.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11992,10 +11992,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125632950</v>
+        <v>125633081</v>
       </c>
       <c r="B113" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12027,10 +12027,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>458282</v>
+        <v>458252</v>
       </c>
       <c r="R113" t="n">
-        <v>6901706</v>
+        <v>6901694</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12089,10 +12089,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125635101</v>
+        <v>125633201</v>
       </c>
       <c r="B114" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12120,14 +12120,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
+          <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>458152</v>
+        <v>458238</v>
       </c>
       <c r="R114" t="n">
-        <v>6901693</v>
+        <v>6901671</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12186,10 +12186,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125633201</v>
+        <v>125635101</v>
       </c>
       <c r="B115" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12217,14 +12217,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Tönninghållan, Tönninghållan, Hjd</t>
+          <t>Tönninghållan N, Tönninghållan N, Hjd</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>458238</v>
+        <v>458152</v>
       </c>
       <c r="R115" t="n">
-        <v>6901671</v>
+        <v>6901693</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12286,7 +12286,7 @@
         <v>125634627</v>
       </c>
       <c r="B116" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>125634763</v>
       </c>
       <c r="B117" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>125886605</v>
       </c>
       <c r="B123" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>125886318</v>
       </c>
       <c r="B124" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>125886385</v>
       </c>
       <c r="B125" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B127" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R127" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B128" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R128" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13765,10 +13765,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125886299</v>
+        <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13793,26 +13793,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>458182</v>
+        <v>458106</v>
       </c>
       <c r="R131" t="n">
-        <v>6901855</v>
+        <v>6901940</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13871,10 +13862,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125886855</v>
+        <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13899,17 +13890,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>458106</v>
+        <v>458182</v>
       </c>
       <c r="R132" t="n">
-        <v>6901940</v>
+        <v>6901855</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>125886472</v>
       </c>
       <c r="B136" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12971,32 +12971,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125886605</v>
+        <v>125886318</v>
       </c>
       <c r="B123" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13006,10 +13006,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458150</v>
+        <v>458189</v>
       </c>
       <c r="R123" t="n">
-        <v>6901939</v>
+        <v>6901872</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13068,10 +13068,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125886318</v>
+        <v>125886385</v>
       </c>
       <c r="B124" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13096,17 +13096,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458189</v>
+        <v>458168</v>
       </c>
       <c r="R124" t="n">
-        <v>6901872</v>
+        <v>6901896</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13165,54 +13174,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886385</v>
+        <v>125886605</v>
       </c>
       <c r="B125" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458168</v>
+        <v>458150</v>
       </c>
       <c r="R125" t="n">
-        <v>6901896</v>
+        <v>6901939</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B127" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R127" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B128" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R128" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -12971,32 +12971,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125886318</v>
+        <v>125886605</v>
       </c>
       <c r="B123" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13006,10 +13006,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458189</v>
+        <v>458150</v>
       </c>
       <c r="R123" t="n">
-        <v>6901872</v>
+        <v>6901939</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13068,7 +13068,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125886385</v>
+        <v>125886318</v>
       </c>
       <c r="B124" t="n">
         <v>98352</v>
@@ -13096,26 +13096,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458168</v>
+        <v>458189</v>
       </c>
       <c r="R124" t="n">
-        <v>6901896</v>
+        <v>6901872</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13174,45 +13165,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886605</v>
+        <v>125886385</v>
       </c>
       <c r="B125" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458150</v>
+        <v>458168</v>
       </c>
       <c r="R125" t="n">
-        <v>6901939</v>
+        <v>6901896</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B127" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R127" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B128" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R128" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -12971,32 +12971,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125886605</v>
+        <v>125886318</v>
       </c>
       <c r="B123" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13006,10 +13006,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458150</v>
+        <v>458189</v>
       </c>
       <c r="R123" t="n">
-        <v>6901939</v>
+        <v>6901872</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13068,7 +13068,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125886318</v>
+        <v>125886385</v>
       </c>
       <c r="B124" t="n">
         <v>98352</v>
@@ -13096,17 +13096,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458189</v>
+        <v>458168</v>
       </c>
       <c r="R124" t="n">
-        <v>6901872</v>
+        <v>6901896</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13165,54 +13174,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886385</v>
+        <v>125886605</v>
       </c>
       <c r="B125" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458168</v>
+        <v>458150</v>
       </c>
       <c r="R125" t="n">
-        <v>6901896</v>
+        <v>6901939</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -12480,7 +12480,7 @@
         <v>125886795</v>
       </c>
       <c r="B118" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>125886362</v>
       </c>
       <c r="B119" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>125886789</v>
       </c>
       <c r="B120" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>125886858</v>
       </c>
       <c r="B121" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>125886889</v>
       </c>
       <c r="B122" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>125886318</v>
       </c>
       <c r="B123" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>125886385</v>
       </c>
       <c r="B124" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>125886605</v>
       </c>
       <c r="B125" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>125886497</v>
       </c>
       <c r="B126" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>125886761</v>
       </c>
       <c r="B127" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13468,7 +13468,7 @@
         <v>125886459</v>
       </c>
       <c r="B128" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>125886245</v>
       </c>
       <c r="B129" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>125886409</v>
       </c>
       <c r="B130" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>125886855</v>
       </c>
       <c r="B131" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>125886299</v>
       </c>
       <c r="B132" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>125886879</v>
       </c>
       <c r="B133" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>125886532</v>
       </c>
       <c r="B134" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>125886850</v>
       </c>
       <c r="B135" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>125886472</v>
       </c>
       <c r="B136" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -12971,32 +12971,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125886318</v>
+        <v>125886605</v>
       </c>
       <c r="B123" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13006,10 +13006,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>458189</v>
+        <v>458150</v>
       </c>
       <c r="R123" t="n">
-        <v>6901872</v>
+        <v>6901939</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13068,7 +13068,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125886385</v>
+        <v>125886318</v>
       </c>
       <c r="B124" t="n">
         <v>98361</v>
@@ -13096,26 +13096,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>458168</v>
+        <v>458189</v>
       </c>
       <c r="R124" t="n">
-        <v>6901896</v>
+        <v>6901872</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13174,45 +13165,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125886605</v>
+        <v>125886385</v>
       </c>
       <c r="B125" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Tönninghållan, Tönninghållan, Hjd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>458150</v>
+        <v>458168</v>
       </c>
       <c r="R125" t="n">
-        <v>6901939</v>
+        <v>6901896</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B127" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R127" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B128" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R128" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>

--- a/artfynd/A 37835-2024 artfynd.xlsx
+++ b/artfynd/A 37835-2024 artfynd.xlsx
@@ -13368,32 +13368,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125886459</v>
+        <v>125886761</v>
       </c>
       <c r="B127" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>458138</v>
+        <v>458101</v>
       </c>
       <c r="R127" t="n">
-        <v>6901895</v>
+        <v>6901974</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125886761</v>
+        <v>125886459</v>
       </c>
       <c r="B128" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>458101</v>
+        <v>458138</v>
       </c>
       <c r="R128" t="n">
-        <v>6901974</v>
+        <v>6901895</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
